--- a/config/checklist.xlsx
+++ b/config/checklist.xlsx
@@ -7,9 +7,9 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Accelerator - Bootstrap" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Accelerator - AKS Landing Zone" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="How to use" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bootstrap Decisions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Advanced Cluster Settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -501,16 +501,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A60"/>
+  <dimension ref="A1:A39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="80" customWidth="1" min="1" max="1"/>
+    <col width="110" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>AKS Application Landing Zone Accelerator - Planning Checklist</t>
+          <t>AKS Application Landing Zone — Planning Checklist</t>
         </is>
       </c>
     </row>
@@ -520,14 +520,14 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>This workbook helps you plan your AKS Application Landing Zone deployment.</t>
+          <t>This workbook is the planning sheet for `Deploy-AKSLandingZone`.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>It mirrors the Azure Landing Zone Accelerator Phase 0 planning process.</t>
+          <t>Fill it in with your team before you run the wizard, then keep it for the record.</t>
         </is>
       </c>
     </row>
@@ -537,7 +537,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>HOW TO USE THIS WORKBOOK</t>
+          <t>How to use it</t>
         </is>
       </c>
     </row>
@@ -547,21 +547,21 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>1. Start with the 'Accelerator - Bootstrap' tab.</t>
+          <t>1. Open the 'Bootstrap Decisions' tab and fill in every yellow cell.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Fill in the yellow 'Your Value' column for each decision.</t>
+          <t xml:space="preserve">   - Pick a scenario first (row 0a) — it sets sensible defaults for the rest.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Each decision number maps to a decision in config/inputs.yaml.</t>
+          <t xml:space="preserve">   - Don't put GitHub tokens in the workbook. The wizard asks for them with hidden input.</t>
         </is>
       </c>
     </row>
@@ -571,72 +571,72 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2. Then go to the 'Accelerator - AKS Landing Zone' tab.</t>
+          <t>2. Open 'Advanced Cluster Settings' only if you need to change cluster sizing, networking,</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Review and customize the AKS-specific settings.</t>
+          <t xml:space="preserve">   or upgrade behaviour. Most teams leave this tab alone.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   These map to settings in config/aks-landing-zone.tfvars.</t>
-        </is>
-      </c>
+      <c r="A14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr"/>
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>3. Run the wizard and use the workbook as your reference:</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>3. Use your completed checklist when running the bootstrap:</t>
+          <t xml:space="preserve">       Import-Module .\ALZ.AKS\ALZ.AKS.psd1 -Force</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   - Interactive mode: Use the values as reference while prompted</t>
+          <t xml:space="preserve">       Deploy-AKSLandingZone</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   - Advanced mode: Copy values directly into config/inputs.yaml</t>
-        </is>
-      </c>
+      <c r="A18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr"/>
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>What the wizard does</t>
+        </is>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>DEPLOYMENT PHASES</t>
-        </is>
-      </c>
+      <c r="A20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr"/>
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Phase A — asks you the questions in this workbook and writes config files.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Phase 0 - Planning (this checklist)</t>
+          <t>Phase B — creates the Azure resources, GitHub repos, runner, and pushes the Terraform code.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Choose bootstrapping options, AKS scenario, and customization options.</t>
+          <t>Phase C — your PRs in the new GitHub repo run plan/apply and deploy the cluster.</t>
         </is>
       </c>
     </row>
@@ -644,222 +644,95 @@
       <c r="A24" s="2" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>Phase 1 - Prerequisites</t>
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>GitHub tokens — scopes you need</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  - Azure CLI login (az login)</t>
-        </is>
-      </c>
+      <c r="A26" s="2" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - GitHub PATs set as environment variables</t>
+          <t>Main token (always):    repo, workflow, admin:org (Members Read &amp; Write)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - Entra ID admin group created for AKS cluster access</t>
+          <t>Runner token (if 9a is true):  admin:org (full)</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  - Subscriptions available (AKS landing zone + connectivity)</t>
-        </is>
-      </c>
+      <c r="A29" s="2" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr"/>
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>Resource names you will see</t>
+        </is>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>Phase 2 - Bootstrap</t>
-        </is>
-      </c>
+      <c r="A31" s="2" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Run: .\bootstrap\Deploy-AKSLandingZone.ps1</t>
+          <t>Pattern: {service}-{env}-{region-short}-{number}</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Or:  .\bootstrap\Deploy-AKSLandingZone.ps1 -InputConfigPath .\config\inputs.yaml</t>
+          <t>Example with defaults (aksapplz, prod, swedencentral, 1):</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr"/>
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Resource group for state:     rg-aksapplz-prod-sc-001</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>Phase 3 - Run</t>
+          <t xml:space="preserve">  Resource group for identity:  rg-aksapplz-prod-sc-identity</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Create PR → CI runs plan → Merge → CD runs plan → Approve → Apply</t>
+          <t xml:space="preserve">  Resource group for runner:    rg-aksapplz-prod-sc-agents     (only with self-hosted runners)</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr"/>
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  GitHub repository:            aksapplz-prod</t>
+        </is>
+      </c>
     </row>
     <row r="38">
-      <c r="A38" s="3" t="inlineStr">
-        <is>
-          <t>REQUIRED GITHUB PAT SCOPES</t>
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  GitHub templates repo:        aksapplz-prod-templates</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>github_personal_access_token:</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  - repo (Full control of private repositories)</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  - admin:org → Members (Read and Write)</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  - workflow (Update GitHub Action workflows)</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>github_runners_personal_access_token (only if use_self_hosted_runners = true):</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  - admin:org (Full control of orgs and teams)</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="3" t="inlineStr">
-        <is>
-          <t>NAMING CONVENTION</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>Bootstrap resources are named: {service_name}-{environment_name}-{location_shortcode}-{postfix}</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>Example: aksapplz-prod-sc-001</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>Resource Group:      rg-aksapplz-prod-sc-001</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>Storage Account:     staksapplzprodsc001</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>Managed Identity:    id-aksapplz-prod-sc-001</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>GitHub Repository:   aksapplz-prod</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>Templates Repo:      aksapplz-prod-templates</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>GitHub Team:          aksapplz-prod-approvers</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>Plan Environment:    aksapplz-plan</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>Apply Environment:   aksapplz-apply</t>
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Approver team:                aksapplz-prod-approvers</t>
         </is>
       </c>
     </row>
@@ -874,35 +747,35 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F49"/>
+  <dimension ref="A1:F57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="38" customWidth="1" min="2" max="2"/>
+    <col width="55" customWidth="1" min="3" max="3"/>
     <col width="55" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="28" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>AKS Application Landing Zone Accelerator - Bootstrap Decisions</t>
+          <t>AKS Application Landing Zone — Planning Checklist</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>Fill in the 'Your Value' column (yellow) for each decision. Each decision maps to a setting in config/inputs.yaml.</t>
+          <t>Fill in the yellow column. Each row matches one question the wizard will ask you.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Decision #</t>
+          <t>#</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
@@ -912,12 +785,12 @@
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>What it is</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>Options / Guidance</t>
+          <t>Example / options</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
@@ -927,7 +800,7 @@
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>Your Value</t>
+          <t>Your value</t>
         </is>
       </c>
     </row>
@@ -935,7 +808,7 @@
       <c r="A5" s="7" t="inlineStr"/>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>BOOTSTRAP CONFIGURATION</t>
+          <t>SCENARIO</t>
         </is>
       </c>
       <c r="C5" s="7" t="n"/>
@@ -946,27 +819,30 @@
     <row r="6">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0a</t>
         </is>
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>bootstrap_location</t>
+          <t>scenario</t>
         </is>
       </c>
       <c r="C6" s="9" t="inlineStr">
         <is>
-          <t>Azure region for bootstrap resources (state storage, managed identity).</t>
+          <t>Pick a starting point. Each one chooses sensible defaults for cluster size, security, and add-ons. You can still change anything afterwards.</t>
         </is>
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>Any valid Azure region. E.g.: swedencentral, westeurope, northeurope, eastus, eastus2</t>
+          <t>single_region_baseline  (standard, one region)
+multi_region_baseline   (two regions, GitOps)
+single_region_regulated (PCI / FIPS / Istio)
+multi_region_regulated  (PCI, two regions)</t>
         </is>
       </c>
       <c r="E6" s="9" t="inlineStr">
         <is>
-          <t>swedencentral</t>
+          <t>single_region_baseline</t>
         </is>
       </c>
       <c r="F6" s="10" t="inlineStr"/>
@@ -974,110 +850,115 @@
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0b</t>
         </is>
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>aks_landing_zone_subscription_id</t>
+          <t>secondary_location</t>
         </is>
       </c>
       <c r="C7" s="9" t="inlineStr">
         <is>
-          <t>The subscription where the AKS cluster and supporting resources will be deployed.</t>
+          <t>Second Azure region (only for multi-region scenarios). Leave blank otherwise.</t>
         </is>
       </c>
       <c r="D7" s="9" t="inlineStr">
         <is>
-          <t>Azure subscription ID (GUID format). Leave empty to use the subscription connected to Azure CLI.</t>
-        </is>
-      </c>
-      <c r="E7" s="9" t="inlineStr">
-        <is>
-          <t>(current CLI subscription)</t>
-        </is>
-      </c>
+          <t>westeurope, northeurope, eastus2 ...</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="inlineStr"/>
       <c r="F7" s="10" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B8" s="9" t="inlineStr">
-        <is>
-          <t>connectivity_subscription_id</t>
-        </is>
-      </c>
-      <c r="C8" s="9" t="inlineStr">
-        <is>
-          <t>The subscription containing the hub VNet and firewall (deployed by ALZ accelerator).</t>
-        </is>
-      </c>
-      <c r="D8" s="9" t="inlineStr">
-        <is>
-          <t>Azure subscription ID (GUID). This is the connectivity subscription from your ALZ deployment.</t>
-        </is>
-      </c>
-      <c r="E8" s="9" t="inlineStr"/>
-      <c r="F8" s="10" t="inlineStr"/>
+      <c r="A8" s="7" t="inlineStr"/>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>WHERE TO DEPLOY</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="n"/>
+      <c r="D8" s="7" t="n"/>
+      <c r="E8" s="7" t="n"/>
+      <c r="F8" s="7" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="inlineStr"/>
-      <c r="B9" s="7" t="inlineStr">
-        <is>
-          <t>HUB NETWORKING</t>
-        </is>
-      </c>
-      <c r="C9" s="7" t="n"/>
-      <c r="D9" s="7" t="n"/>
-      <c r="E9" s="7" t="n"/>
-      <c r="F9" s="7" t="n"/>
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>bootstrap_location</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>Main Azure region for the cluster and supporting resources.</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>swedencentral, westeurope, eastus2 ...</t>
+        </is>
+      </c>
+      <c r="E9" s="9" t="inlineStr">
+        <is>
+          <t>swedencentral</t>
+        </is>
+      </c>
+      <c r="F9" s="10" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>4a</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>hub_vnet_resource_id</t>
+          <t>aks_landing_zone_subscription_id</t>
         </is>
       </c>
       <c r="C10" s="9" t="inlineStr">
         <is>
-          <t>Full ARM resource ID of the hub VNet for VNet peering.</t>
+          <t>Subscription where the AKS cluster will be created.</t>
         </is>
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>/subscriptions/{sub}/resourceGroups/{rg}/providers/Microsoft.Network/virtualNetworks/{name}</t>
-        </is>
-      </c>
-      <c r="E10" s="9" t="inlineStr"/>
+          <t>Subscription ID (GUID).
+Leave blank to use whatever `az` is logged into.</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="inlineStr">
+        <is>
+          <t>(current az subscription)</t>
+        </is>
+      </c>
       <c r="F10" s="10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>4b</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>hub_firewall_private_ip</t>
+          <t>connectivity_subscription_id</t>
         </is>
       </c>
       <c r="C11" s="9" t="inlineStr">
         <is>
-          <t>Private IP of the hub firewall. Used for UDR to route egress from AKS nodes.</t>
+          <t>Subscription that holds your existing hub network (firewall, VPN).</t>
         </is>
       </c>
       <c r="D11" s="9" t="inlineStr">
         <is>
-          <t>IP address. E.g.: 10.0.0.4</t>
+          <t>Subscription ID (GUID).</t>
         </is>
       </c>
       <c r="E11" s="9" t="inlineStr"/>
@@ -1087,7 +968,7 @@
       <c r="A12" s="7" t="inlineStr"/>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>SPOKE NETWORKING</t>
+          <t>HUB NETWORK (you already have this)</t>
         </is>
       </c>
       <c r="C12" s="7" t="n"/>
@@ -1098,111 +979,91 @@
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>5a</t>
+          <t>4a</t>
         </is>
       </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>spoke_vnet_address_space</t>
+          <t>hub_vnet_resource_id</t>
         </is>
       </c>
       <c r="C13" s="9" t="inlineStr">
         <is>
-          <t>Address space for the spoke VNet. Must not overlap with hub or other spokes.</t>
+          <t>Full ID of your hub VNet. The wizard lists hubs found in Decision 3 and fills this in.</t>
         </is>
       </c>
       <c r="D13" s="9" t="inlineStr">
         <is>
-          <t>CIDR notation. Ensure /16 or larger for AKS scalability.</t>
-        </is>
-      </c>
-      <c r="E13" s="9" t="inlineStr">
-        <is>
-          <t>10.10.0.0/16</t>
-        </is>
-      </c>
+          <t>/subscriptions/&lt;id&gt;/resourceGroups/&lt;rg&gt;/providers/Microsoft.Network/virtualNetworks/&lt;name&gt;</t>
+        </is>
+      </c>
+      <c r="E13" s="9" t="inlineStr"/>
       <c r="F13" s="10" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t>5b</t>
+          <t>4b</t>
         </is>
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>subnet_address_prefix_aks_nodes</t>
+          <t>hub_firewall_private_ip</t>
         </is>
       </c>
       <c r="C14" s="9" t="inlineStr">
         <is>
-          <t>Subnet for AKS node pools. Needs to be large enough for max node count.</t>
+          <t>Private IP of your hub firewall. Traffic leaving the cluster routes through this.</t>
         </is>
       </c>
       <c r="D14" s="9" t="inlineStr">
         <is>
-          <t>CIDR notation. /20 supports ~4000 nodes with Azure CNI Overlay.</t>
+          <t>10.0.0.4</t>
         </is>
       </c>
       <c r="E14" s="9" t="inlineStr">
         <is>
-          <t>10.10.0.0/20</t>
+          <t>10.0.0.4</t>
         </is>
       </c>
       <c r="F14" s="10" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="8" t="inlineStr">
-        <is>
-          <t>5c</t>
-        </is>
-      </c>
-      <c r="B15" s="9" t="inlineStr">
-        <is>
-          <t>subnet_address_prefix_aks_api_server</t>
-        </is>
-      </c>
-      <c r="C15" s="9" t="inlineStr">
-        <is>
-          <t>Subnet for AKS API Server VNet Integration (private API server access).</t>
-        </is>
-      </c>
-      <c r="D15" s="9" t="inlineStr">
-        <is>
-          <t>CIDR notation. Minimum /28 required by Azure.</t>
-        </is>
-      </c>
-      <c r="E15" s="9" t="inlineStr">
-        <is>
-          <t>10.10.16.0/28</t>
-        </is>
-      </c>
-      <c r="F15" s="10" t="inlineStr"/>
+      <c r="A15" s="7" t="inlineStr"/>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>SPOKE NETWORK (the new VNet for AKS)</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="n"/>
+      <c r="D15" s="7" t="n"/>
+      <c r="E15" s="7" t="n"/>
+      <c r="F15" s="7" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="8" t="inlineStr">
         <is>
-          <t>5d</t>
+          <t>5a</t>
         </is>
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>subnet_address_prefix_app_gateway</t>
+          <t>spoke_vnet_address_space</t>
         </is>
       </c>
       <c r="C16" s="9" t="inlineStr">
         <is>
-          <t>Subnet for Application Gateway WAF v2. Dedicated subnet required by Azure.</t>
+          <t>Address range for the new spoke VNet. Must not overlap with any other VNet.</t>
         </is>
       </c>
       <c r="D16" s="9" t="inlineStr">
         <is>
-          <t>CIDR notation. /24 recommended.</t>
+          <t>10.10.0.0/16</t>
         </is>
       </c>
       <c r="E16" s="9" t="inlineStr">
         <is>
-          <t>10.10.17.0/24</t>
+          <t>10.10.0.0/16</t>
         </is>
       </c>
       <c r="F16" s="10" t="inlineStr"/>
@@ -1210,27 +1071,27 @@
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>5e</t>
+          <t>5b</t>
         </is>
       </c>
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>subnet_address_prefix_private_endpoints</t>
+          <t>subnet_address_prefix_aks_system_nodes</t>
         </is>
       </c>
       <c r="C17" s="9" t="inlineStr">
         <is>
-          <t>Subnet for private endpoints (ACR, Key Vault).</t>
+          <t>Small subnet for the system node pool (runs cluster add-ons only).</t>
         </is>
       </c>
       <c r="D17" s="9" t="inlineStr">
         <is>
-          <t>CIDR notation. /24 recommended.</t>
+          <t>10.10.0.0/24  (256 addresses)</t>
         </is>
       </c>
       <c r="E17" s="9" t="inlineStr">
         <is>
-          <t>10.10.18.0/24</t>
+          <t>10.10.0.0/24</t>
         </is>
       </c>
       <c r="F17" s="10" t="inlineStr"/>
@@ -1238,67 +1099,83 @@
     <row r="18">
       <c r="A18" s="8" t="inlineStr">
         <is>
-          <t>5f</t>
+          <t>5c</t>
         </is>
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>subnet_address_prefix_ingress</t>
+          <t>subnet_address_prefix_aks_user_nodes</t>
         </is>
       </c>
       <c r="C18" s="9" t="inlineStr">
         <is>
-          <t>Subnet for ingress controller internal load balancer.</t>
+          <t>Bigger subnet for your application workloads.</t>
         </is>
       </c>
       <c r="D18" s="9" t="inlineStr">
         <is>
-          <t>CIDR notation. /24 recommended.</t>
+          <t>10.10.16.0/22  (1024 addresses)</t>
         </is>
       </c>
       <c r="E18" s="9" t="inlineStr">
         <is>
-          <t>10.10.19.0/24</t>
+          <t>10.10.16.0/22</t>
         </is>
       </c>
       <c r="F18" s="10" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="7" t="inlineStr"/>
-      <c r="B19" s="7" t="inlineStr">
-        <is>
-          <t>AKS CONFIGURATION</t>
-        </is>
-      </c>
-      <c r="C19" s="7" t="n"/>
-      <c r="D19" s="7" t="n"/>
-      <c r="E19" s="7" t="n"/>
-      <c r="F19" s="7" t="n"/>
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t>5d</t>
+        </is>
+      </c>
+      <c r="B19" s="9" t="inlineStr">
+        <is>
+          <t>subnet_address_prefix_aks_api_server</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>Subnet for the private Kubernetes API server.</t>
+        </is>
+      </c>
+      <c r="D19" s="9" t="inlineStr">
+        <is>
+          <t>10.10.20.0/28  (Azure requires at least /28)</t>
+        </is>
+      </c>
+      <c r="E19" s="9" t="inlineStr">
+        <is>
+          <t>10.10.20.0/28</t>
+        </is>
+      </c>
+      <c r="F19" s="10" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="8" t="inlineStr">
         <is>
-          <t>6a</t>
+          <t>5e</t>
         </is>
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>kubernetes_version</t>
+          <t>subnet_address_prefix_app_gateway</t>
         </is>
       </c>
       <c r="C20" s="9" t="inlineStr">
         <is>
-          <t>Kubernetes version for the AKS cluster.</t>
+          <t>Subnet for Application Gateway (web traffic in).</t>
         </is>
       </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
-          <t>Check available versions: az aks get-versions -l &lt;region&gt; -o table</t>
+          <t>10.10.21.0/24</t>
         </is>
       </c>
       <c r="E20" s="9" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>10.10.21.0/24</t>
         </is>
       </c>
       <c r="F20" s="10" t="inlineStr"/>
@@ -1306,27 +1183,27 @@
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>6b</t>
+          <t>5f</t>
         </is>
       </c>
       <c r="B21" s="9" t="inlineStr">
         <is>
-          <t>aks_sku_tier</t>
+          <t>subnet_address_prefix_private_endpoints</t>
         </is>
       </c>
       <c r="C21" s="9" t="inlineStr">
         <is>
-          <t>AKS pricing tier. Standard includes SLA, Premium adds more features.</t>
+          <t>Subnet for private endpoints (ACR, Key Vault, storage).</t>
         </is>
       </c>
       <c r="D21" s="9" t="inlineStr">
         <is>
-          <t>Free | Standard | Premium</t>
+          <t>10.10.22.0/24</t>
         </is>
       </c>
       <c r="E21" s="9" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>10.10.22.0/24</t>
         </is>
       </c>
       <c r="F21" s="10" t="inlineStr"/>
@@ -1334,193 +1211,192 @@
     <row r="22">
       <c r="A22" s="8" t="inlineStr">
         <is>
-          <t>6c</t>
+          <t>5g</t>
         </is>
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>aks_private_cluster</t>
+          <t>subnet_address_prefix_ingress</t>
         </is>
       </c>
       <c r="C22" s="9" t="inlineStr">
         <is>
-          <t>Enable private cluster with API Server VNet Integration.</t>
+          <t>Subnet for the internal load balancer that fronts your apps.</t>
         </is>
       </c>
       <c r="D22" s="9" t="inlineStr">
         <is>
-          <t>true = API server accessible only via private network.
-false = API server has public endpoint.</t>
+          <t>10.10.23.0/24</t>
         </is>
       </c>
       <c r="E22" s="9" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>10.10.23.0/24</t>
         </is>
       </c>
       <c r="F22" s="10" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="8" t="inlineStr">
-        <is>
-          <t>6d</t>
-        </is>
-      </c>
-      <c r="B23" s="9" t="inlineStr">
-        <is>
-          <t>aks_admin_group_object_ids</t>
-        </is>
-      </c>
-      <c r="C23" s="9" t="inlineStr">
-        <is>
-          <t>Entra ID group Object ID(s) for Kubernetes cluster admin RBAC binding.</t>
-        </is>
-      </c>
-      <c r="D23" s="9" t="inlineStr">
-        <is>
-          <t>List of GUIDs. E.g.: ["xxxxxxxx-xxxx-xxxx-xxxx-xxxxxxxxxxxx"].
-Create group in Entra ID first.</t>
-        </is>
-      </c>
-      <c r="E23" s="9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="F23" s="10" t="inlineStr"/>
+      <c r="A23" s="7" t="inlineStr"/>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>CLUSTER SETTINGS</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="n"/>
+      <c r="D23" s="7" t="n"/>
+      <c r="E23" s="7" t="n"/>
+      <c r="F23" s="7" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="7" t="inlineStr"/>
-      <c r="B24" s="7" t="inlineStr">
-        <is>
-          <t>BOOTSTRAP RESOURCE SUBSCRIPTION</t>
-        </is>
-      </c>
-      <c r="C24" s="7" t="n"/>
-      <c r="D24" s="7" t="n"/>
-      <c r="E24" s="7" t="n"/>
-      <c r="F24" s="7" t="n"/>
+      <c r="A24" s="8" t="inlineStr">
+        <is>
+          <t>6a</t>
+        </is>
+      </c>
+      <c r="B24" s="9" t="inlineStr">
+        <is>
+          <t>kubernetes_version</t>
+        </is>
+      </c>
+      <c r="C24" s="9" t="inlineStr">
+        <is>
+          <t>Kubernetes version. The wizard lists the latest versions available in your region — usually just pick the top one.</t>
+        </is>
+      </c>
+      <c r="D24" s="9" t="inlineStr">
+        <is>
+          <t>Example: 1.33.6</t>
+        </is>
+      </c>
+      <c r="E24" s="9" t="inlineStr">
+        <is>
+          <t>(latest in region)</t>
+        </is>
+      </c>
+      <c r="F24" s="10" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="8" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6b</t>
         </is>
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>bootstrap_subscription_id</t>
+          <t>aks_sku_tier</t>
         </is>
       </c>
       <c r="C25" s="9" t="inlineStr">
         <is>
-          <t>Subscription for Terraform state storage and managed identity.</t>
+          <t>Cluster pricing tier. Standard is fine for most clusters; Premium adds long-term support and is required for regulated scenarios.</t>
         </is>
       </c>
       <c r="D25" s="9" t="inlineStr">
         <is>
-          <t>Azure subscription ID (GUID). Leave empty to use the AKS landing zone subscription.</t>
+          <t>Free | Standard | Premium</t>
         </is>
       </c>
       <c r="E25" s="9" t="inlineStr">
         <is>
-          <t>(same as Decision 2)</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="F25" s="10" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="7" t="inlineStr"/>
-      <c r="B26" s="7" t="inlineStr">
-        <is>
-          <t>BOOTSTRAP RESOURCE NAMING</t>
-        </is>
-      </c>
-      <c r="C26" s="7" t="n"/>
-      <c r="D26" s="7" t="n"/>
-      <c r="E26" s="7" t="n"/>
-      <c r="F26" s="7" t="n"/>
+      <c r="A26" s="8" t="inlineStr">
+        <is>
+          <t>6c</t>
+        </is>
+      </c>
+      <c r="B26" s="9" t="inlineStr">
+        <is>
+          <t>aks_private_cluster</t>
+        </is>
+      </c>
+      <c r="C26" s="9" t="inlineStr">
+        <is>
+          <t>Hide the Kubernetes API behind your private network (no public endpoint).</t>
+        </is>
+      </c>
+      <c r="D26" s="9" t="inlineStr">
+        <is>
+          <t>true  (recommended)
+false (only for internet-facing demos)</t>
+        </is>
+      </c>
+      <c r="E26" s="9" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="F26" s="10" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="8" t="inlineStr">
         <is>
-          <t>8a</t>
+          <t>6d</t>
         </is>
       </c>
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>service_name</t>
+          <t>aks_admin_group_object_ids</t>
         </is>
       </c>
       <c r="C27" s="9" t="inlineStr">
         <is>
-          <t>Service name used in resource naming convention: {service_name}-{environment_name}-{postfix}.</t>
+          <t>Entra ID group(s) whose members can manage the cluster. Create the group in Entra ID first and paste the object ID.</t>
         </is>
       </c>
       <c r="D27" s="9" t="inlineStr">
         <is>
-          <t>Short alphanumeric string. E.g.: aksapplz, myapp, workload1</t>
+          <t>["00000000-0000-0000-0000-000000000000"]</t>
         </is>
       </c>
       <c r="E27" s="9" t="inlineStr">
         <is>
-          <t>aksapplz</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="F27" s="10" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="8" t="inlineStr">
-        <is>
-          <t>8b</t>
-        </is>
-      </c>
-      <c r="B28" s="9" t="inlineStr">
-        <is>
-          <t>environment_name</t>
-        </is>
-      </c>
-      <c r="C28" s="9" t="inlineStr">
-        <is>
-          <t>Environment name used in resource naming convention.</t>
-        </is>
-      </c>
-      <c r="D28" s="9" t="inlineStr">
-        <is>
-          <t>E.g.: prod, staging, dev, test</t>
-        </is>
-      </c>
-      <c r="E28" s="9" t="inlineStr">
-        <is>
-          <t>prod</t>
-        </is>
-      </c>
-      <c r="F28" s="10" t="inlineStr"/>
+      <c r="A28" s="7" t="inlineStr"/>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>WHERE STATE LIVES</t>
+        </is>
+      </c>
+      <c r="C28" s="7" t="n"/>
+      <c r="D28" s="7" t="n"/>
+      <c r="E28" s="7" t="n"/>
+      <c r="F28" s="7" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
         <is>
-          <t>8c</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B29" s="9" t="inlineStr">
         <is>
-          <t>postfix_number</t>
+          <t>bootstrap_subscription_id</t>
         </is>
       </c>
       <c r="C29" s="9" t="inlineStr">
         <is>
-          <t>Numeric postfix for resource uniqueness. Formatted as 3-digit: 001, 002, etc.</t>
+          <t>Subscription that holds the Terraform state storage and the runner. Usually the same as Decision 2.</t>
         </is>
       </c>
       <c r="D29" s="9" t="inlineStr">
         <is>
-          <t>Integer. E.g.: 1, 2, 444</t>
+          <t>Subscription ID (GUID), or leave blank.</t>
         </is>
       </c>
       <c r="E29" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>(same as Decision 2)</t>
         </is>
       </c>
       <c r="F29" s="10" t="inlineStr"/>
@@ -1529,7 +1405,7 @@
       <c r="A30" s="7" t="inlineStr"/>
       <c r="B30" s="7" t="inlineStr">
         <is>
-          <t>BOOTSTRAP NETWORKING AND AGENTS</t>
+          <t>NAMING</t>
         </is>
       </c>
       <c r="C30" s="7" t="n"/>
@@ -1540,28 +1416,27 @@
     <row r="31">
       <c r="A31" s="8" t="inlineStr">
         <is>
-          <t>9a</t>
+          <t>8a</t>
         </is>
       </c>
       <c r="B31" s="9" t="inlineStr">
         <is>
-          <t>use_self_hosted_runners</t>
+          <t>service_name</t>
         </is>
       </c>
       <c r="C31" s="9" t="inlineStr">
         <is>
-          <t>Use self-hosted GitHub Actions runners instead of GitHub-hosted runners.</t>
+          <t>Short name of your workload. Used in every resource name.</t>
         </is>
       </c>
       <c r="D31" s="9" t="inlineStr">
         <is>
-          <t>true = Self-hosted (required for private clusters).
-false = GitHub-hosted (simpler, but no private network access).</t>
+          <t>aksapplz, payments, shop</t>
         </is>
       </c>
       <c r="E31" s="9" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>aksapplz</t>
         </is>
       </c>
       <c r="F31" s="10" t="inlineStr"/>
@@ -1569,99 +1444,96 @@
     <row r="32">
       <c r="A32" s="8" t="inlineStr">
         <is>
-          <t>9b</t>
+          <t>8b</t>
         </is>
       </c>
       <c r="B32" s="9" t="inlineStr">
         <is>
-          <t>use_private_networking</t>
+          <t>environment_name</t>
         </is>
       </c>
       <c r="C32" s="9" t="inlineStr">
         <is>
-          <t>Deploy runners with private networking (VNet-connected).</t>
+          <t>Environment label. Used in every resource name.</t>
         </is>
       </c>
       <c r="D32" s="9" t="inlineStr">
         <is>
-          <t>true = Runners deployed in spoke VNet (required for private cluster).
-false = Runners use public networking.
-Only applies when use_self_hosted_runners = true.</t>
+          <t>prod, dev, test</t>
         </is>
       </c>
       <c r="E32" s="9" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>prod</t>
         </is>
       </c>
       <c r="F32" s="10" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="7" t="inlineStr"/>
-      <c r="B33" s="7" t="inlineStr">
-        <is>
-          <t>VERSION CONTROL SYSTEM SETTINGS</t>
-        </is>
-      </c>
-      <c r="C33" s="7" t="n"/>
-      <c r="D33" s="7" t="n"/>
-      <c r="E33" s="7" t="n"/>
-      <c r="F33" s="7" t="n"/>
+      <c r="A33" s="8" t="inlineStr">
+        <is>
+          <t>8c</t>
+        </is>
+      </c>
+      <c r="B33" s="9" t="inlineStr">
+        <is>
+          <t>postfix_number</t>
+        </is>
+      </c>
+      <c r="C33" s="9" t="inlineStr">
+        <is>
+          <t>Number that makes resource names unique. Bump this if you redeploy.</t>
+        </is>
+      </c>
+      <c r="D33" s="9" t="inlineStr">
+        <is>
+          <t>1, 2, 3 ...</t>
+        </is>
+      </c>
+      <c r="E33" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F33" s="10" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="8" t="inlineStr">
-        <is>
-          <t>10a</t>
-        </is>
-      </c>
-      <c r="B34" s="9" t="inlineStr">
-        <is>
-          <t>github_personal_access_token</t>
-        </is>
-      </c>
-      <c r="C34" s="9" t="inlineStr">
-        <is>
-          <t>GitHub PAT for repository and team management. Set via environment variable.</t>
-        </is>
-      </c>
-      <c r="D34" s="9" t="inlineStr">
-        <is>
-          <t>Set $env:TF_VAR_github_personal_access_token = "ghp_..."
-Required scopes: repo, admin:org, workflow</t>
-        </is>
-      </c>
-      <c r="E34" s="9" t="inlineStr">
-        <is>
-          <t>(environment variable)</t>
-        </is>
-      </c>
-      <c r="F34" s="10" t="inlineStr"/>
+      <c r="A34" s="7" t="inlineStr"/>
+      <c r="B34" s="7" t="inlineStr">
+        <is>
+          <t>RUNNERS</t>
+        </is>
+      </c>
+      <c r="C34" s="7" t="n"/>
+      <c r="D34" s="7" t="n"/>
+      <c r="E34" s="7" t="n"/>
+      <c r="F34" s="7" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="8" t="inlineStr">
         <is>
-          <t>10b</t>
+          <t>9a</t>
         </is>
       </c>
       <c r="B35" s="9" t="inlineStr">
         <is>
-          <t>github_runners_personal_access_token</t>
+          <t>use_self_hosted_runners</t>
         </is>
       </c>
       <c r="C35" s="9" t="inlineStr">
         <is>
-          <t>GitHub PAT for self-hosted runner registration. Only needed if use_self_hosted_runners = true.</t>
+          <t>Run GitHub Actions on a small container inside Azure (needed for private clusters so CI/CD can reach the API).</t>
         </is>
       </c>
       <c r="D35" s="9" t="inlineStr">
         <is>
-          <t>Set $env:TF_VAR_github_runners_personal_access_token = "ghp_..."
-Required scopes: admin:org</t>
+          <t>true  (required for private clusters)
+false (use GitHub-hosted runners)</t>
         </is>
       </c>
       <c r="E35" s="9" t="inlineStr">
         <is>
-          <t>(environment variable)</t>
+          <t>true</t>
         </is>
       </c>
       <c r="F35" s="10" t="inlineStr"/>
@@ -1669,91 +1541,96 @@
     <row r="36">
       <c r="A36" s="8" t="inlineStr">
         <is>
-          <t>10c</t>
+          <t>9b</t>
         </is>
       </c>
       <c r="B36" s="9" t="inlineStr">
         <is>
-          <t>github_organization_name</t>
+          <t>use_private_networking</t>
         </is>
       </c>
       <c r="C36" s="9" t="inlineStr">
         <is>
-          <t>GitHub organization where repositories will be created.</t>
+          <t>Put the runner and Container Registry on a private network. Recommended.</t>
         </is>
       </c>
       <c r="D36" s="9" t="inlineStr">
         <is>
-          <t>Your GitHub org name. E.g.: abengtss-max-org, contoso</t>
-        </is>
-      </c>
-      <c r="E36" s="9" t="inlineStr"/>
+          <t>true  (recommended)
+false (public networking, ACR Basic)</t>
+        </is>
+      </c>
+      <c r="E36" s="9" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
       <c r="F36" s="10" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="8" t="inlineStr">
-        <is>
-          <t>10d</t>
-        </is>
-      </c>
-      <c r="B37" s="9" t="inlineStr">
-        <is>
-          <t>apply_approvers</t>
-        </is>
-      </c>
-      <c r="C37" s="9" t="inlineStr">
-        <is>
-          <t>GitHub usernames who can approve deployments in the apply environment.</t>
-        </is>
-      </c>
-      <c r="D37" s="9" t="inlineStr">
-        <is>
-          <t>List format: ["user1", "user2"]. These users are added to the approver team.</t>
-        </is>
-      </c>
-      <c r="E37" s="9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="F37" s="10" t="inlineStr"/>
+      <c r="A37" s="7" t="inlineStr"/>
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>GITHUB</t>
+        </is>
+      </c>
+      <c r="C37" s="7" t="n"/>
+      <c r="D37" s="7" t="n"/>
+      <c r="E37" s="7" t="n"/>
+      <c r="F37" s="7" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="7" t="inlineStr"/>
-      <c r="B38" s="7" t="inlineStr">
-        <is>
-          <t>FEATURES</t>
-        </is>
-      </c>
-      <c r="C38" s="7" t="n"/>
-      <c r="D38" s="7" t="n"/>
-      <c r="E38" s="7" t="n"/>
-      <c r="F38" s="7" t="n"/>
+      <c r="A38" s="8" t="inlineStr">
+        <is>
+          <t>10a</t>
+        </is>
+      </c>
+      <c r="B38" s="9" t="inlineStr">
+        <is>
+          <t>github_personal_access_token</t>
+        </is>
+      </c>
+      <c r="C38" s="9" t="inlineStr">
+        <is>
+          <t>GitHub token used to create the repos. You will be prompted (input is hidden); you do NOT need to put it here.</t>
+        </is>
+      </c>
+      <c r="D38" s="9" t="inlineStr">
+        <is>
+          <t>Scopes needed: repo, workflow, admin:org (Read &amp; Write members).</t>
+        </is>
+      </c>
+      <c r="E38" s="9" t="inlineStr">
+        <is>
+          <t>(prompted in wizard)</t>
+        </is>
+      </c>
+      <c r="F38" s="10" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="8" t="inlineStr">
         <is>
-          <t>11a</t>
+          <t>10b</t>
         </is>
       </c>
       <c r="B39" s="9" t="inlineStr">
         <is>
-          <t>enable_defender</t>
+          <t>github_runners_personal_access_token</t>
         </is>
       </c>
       <c r="C39" s="9" t="inlineStr">
         <is>
-          <t>Enable Microsoft Defender for Containers on the AKS cluster.</t>
+          <t>Second token used to register the self-hosted runner. Also prompted; only asked when 9a is true.</t>
         </is>
       </c>
       <c r="D39" s="9" t="inlineStr">
         <is>
-          <t>true | false</t>
+          <t>Scope needed: admin:org (full).</t>
         </is>
       </c>
       <c r="E39" s="9" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>(prompted in wizard)</t>
         </is>
       </c>
       <c r="F39" s="10" t="inlineStr"/>
@@ -1761,101 +1638,81 @@
     <row r="40">
       <c r="A40" s="8" t="inlineStr">
         <is>
-          <t>11b</t>
+          <t>10c</t>
         </is>
       </c>
       <c r="B40" s="9" t="inlineStr">
         <is>
-          <t>enable_keda</t>
+          <t>github_organization_name</t>
         </is>
       </c>
       <c r="C40" s="9" t="inlineStr">
         <is>
-          <t>Enable KEDA (Kubernetes Event-Driven Autoscaling) addon.</t>
+          <t>GitHub organisation name where the two repos will be created.</t>
         </is>
       </c>
       <c r="D40" s="9" t="inlineStr">
         <is>
-          <t>true | false</t>
-        </is>
-      </c>
-      <c r="E40" s="9" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
+          <t>contoso</t>
+        </is>
+      </c>
+      <c r="E40" s="9" t="inlineStr"/>
       <c r="F40" s="10" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="8" t="inlineStr">
         <is>
-          <t>11c</t>
+          <t>10d</t>
         </is>
       </c>
       <c r="B41" s="9" t="inlineStr">
         <is>
-          <t>enable_prometheus</t>
+          <t>apply_approvers</t>
         </is>
       </c>
       <c r="C41" s="9" t="inlineStr">
         <is>
-          <t>Enable Azure Managed Prometheus for metrics collection.</t>
+          <t>GitHub usernames who must approve before a deployment goes live.</t>
         </is>
       </c>
       <c r="D41" s="9" t="inlineStr">
         <is>
-          <t>true | false</t>
+          <t>["alice", "bob"]</t>
         </is>
       </c>
       <c r="E41" s="9" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="F41" s="10" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="8" t="inlineStr">
-        <is>
-          <t>11d</t>
-        </is>
-      </c>
-      <c r="B42" s="9" t="inlineStr">
-        <is>
-          <t>enable_grafana</t>
-        </is>
-      </c>
-      <c r="C42" s="9" t="inlineStr">
-        <is>
-          <t>Enable Azure Managed Grafana for dashboards and visualization.</t>
-        </is>
-      </c>
-      <c r="D42" s="9" t="inlineStr">
-        <is>
-          <t>true | false</t>
-        </is>
-      </c>
-      <c r="E42" s="9" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="F42" s="10" t="inlineStr"/>
+      <c r="A42" s="7" t="inlineStr"/>
+      <c r="B42" s="7" t="inlineStr">
+        <is>
+          <t>ADD-ONS (turn things on or off)</t>
+        </is>
+      </c>
+      <c r="C42" s="7" t="n"/>
+      <c r="D42" s="7" t="n"/>
+      <c r="E42" s="7" t="n"/>
+      <c r="F42" s="7" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="8" t="inlineStr">
         <is>
-          <t>11e</t>
+          <t>11a</t>
         </is>
       </c>
       <c r="B43" s="9" t="inlineStr">
         <is>
-          <t>enable_app_gateway</t>
+          <t>enable_defender</t>
         </is>
       </c>
       <c r="C43" s="9" t="inlineStr">
         <is>
-          <t>Enable Application Gateway with WAF v2 (OWASP 3.2 + Bot Manager rules).</t>
+          <t>Scans the cluster for security threats in real time.</t>
         </is>
       </c>
       <c r="D43" s="9" t="inlineStr">
@@ -1873,17 +1730,17 @@
     <row r="44">
       <c r="A44" s="8" t="inlineStr">
         <is>
-          <t>11f</t>
+          <t>11b</t>
         </is>
       </c>
       <c r="B44" s="9" t="inlineStr">
         <is>
-          <t>enable_acr</t>
+          <t>enable_workload_identity</t>
         </is>
       </c>
       <c r="C44" s="9" t="inlineStr">
         <is>
-          <t>Enable Azure Container Registry (Premium SKU with private endpoint).</t>
+          <t>Lets pods talk to Azure services without passwords.</t>
         </is>
       </c>
       <c r="D44" s="9" t="inlineStr">
@@ -1901,17 +1758,17 @@
     <row r="45">
       <c r="A45" s="8" t="inlineStr">
         <is>
-          <t>11g</t>
+          <t>11c</t>
         </is>
       </c>
       <c r="B45" s="9" t="inlineStr">
         <is>
-          <t>enable_key_vault</t>
+          <t>enable_azure_policy</t>
         </is>
       </c>
       <c r="C45" s="9" t="inlineStr">
         <is>
-          <t>Enable Azure Key Vault (RBAC mode with private endpoint and purge protection).</t>
+          <t>Enforces rules in the cluster (e.g. block containers running as root).</t>
         </is>
       </c>
       <c r="D45" s="9" t="inlineStr">
@@ -1927,41 +1784,57 @@
       <c r="F45" s="10" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="7" t="inlineStr"/>
-      <c r="B46" s="7" t="inlineStr">
-        <is>
-          <t>BASIC INPUTS (DO NOT MODIFY)</t>
-        </is>
-      </c>
-      <c r="C46" s="7" t="n"/>
-      <c r="D46" s="7" t="n"/>
-      <c r="E46" s="7" t="n"/>
-      <c r="F46" s="7" t="n"/>
+      <c r="A46" s="8" t="inlineStr">
+        <is>
+          <t>11d</t>
+        </is>
+      </c>
+      <c r="B46" s="9" t="inlineStr">
+        <is>
+          <t>enable_prometheus</t>
+        </is>
+      </c>
+      <c r="C46" s="9" t="inlineStr">
+        <is>
+          <t>Collects cluster metrics.</t>
+        </is>
+      </c>
+      <c r="D46" s="9" t="inlineStr">
+        <is>
+          <t>true | false</t>
+        </is>
+      </c>
+      <c r="E46" s="9" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="F46" s="10" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>11e</t>
         </is>
       </c>
       <c r="B47" s="9" t="inlineStr">
         <is>
-          <t>iac_type</t>
+          <t>enable_grafana</t>
         </is>
       </c>
       <c r="C47" s="9" t="inlineStr">
         <is>
-          <t>Infrastructure as Code type. Fixed to terraform.</t>
+          <t>Dashboards for the metrics above.</t>
         </is>
       </c>
       <c r="D47" s="9" t="inlineStr">
         <is>
-          <t>terraform</t>
+          <t>true | false</t>
         </is>
       </c>
       <c r="E47" s="9" t="inlineStr">
         <is>
-          <t>terraform</t>
+          <t>true</t>
         </is>
       </c>
       <c r="F47" s="10" t="inlineStr"/>
@@ -1969,27 +1842,27 @@
     <row r="48">
       <c r="A48" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>11f</t>
         </is>
       </c>
       <c r="B48" s="9" t="inlineStr">
         <is>
-          <t>bootstrap_module_name</t>
+          <t>enable_app_gateway</t>
         </is>
       </c>
       <c r="C48" s="9" t="inlineStr">
         <is>
-          <t>Bootstrap module identifier.</t>
+          <t>Application Gateway with a Web Application Firewall in front of the cluster.</t>
         </is>
       </c>
       <c r="D48" s="9" t="inlineStr">
         <is>
-          <t>aksapplz_github</t>
+          <t>true | false</t>
         </is>
       </c>
       <c r="E48" s="9" t="inlineStr">
         <is>
-          <t>aksapplz_github</t>
+          <t>true</t>
         </is>
       </c>
       <c r="F48" s="10" t="inlineStr"/>
@@ -1997,69 +1870,284 @@
     <row r="49">
       <c r="A49" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>11g</t>
         </is>
       </c>
       <c r="B49" s="9" t="inlineStr">
         <is>
-          <t>starter_module_name</t>
+          <t>enable_keda</t>
         </is>
       </c>
       <c r="C49" s="9" t="inlineStr">
         <is>
-          <t>Starter module identifier.</t>
+          <t>Auto-scales pods based on events (queue length, HTTP requests, etc.).</t>
         </is>
       </c>
       <c r="D49" s="9" t="inlineStr">
         <is>
-          <t>aks_landing_zone</t>
+          <t>true | false</t>
         </is>
       </c>
       <c r="E49" s="9" t="inlineStr">
         <is>
-          <t>aks_landing_zone</t>
+          <t>true</t>
         </is>
       </c>
       <c r="F49" s="10" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="8" t="inlineStr">
+        <is>
+          <t>11h</t>
+        </is>
+      </c>
+      <c r="B50" s="9" t="inlineStr">
+        <is>
+          <t>enable_vpa</t>
+        </is>
+      </c>
+      <c r="C50" s="9" t="inlineStr">
+        <is>
+          <t>Auto-adjusts CPU and memory requests for pods.</t>
+        </is>
+      </c>
+      <c r="D50" s="9" t="inlineStr">
+        <is>
+          <t>true | false</t>
+        </is>
+      </c>
+      <c r="E50" s="9" t="inlineStr">
+        <is>
+          <t>false  (true for regulated / multi-region)</t>
+        </is>
+      </c>
+      <c r="F50" s="10" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="8" t="inlineStr">
+        <is>
+          <t>11i</t>
+        </is>
+      </c>
+      <c r="B51" s="9" t="inlineStr">
+        <is>
+          <t>enable_node_auto_provisioning</t>
+        </is>
+      </c>
+      <c r="C51" s="9" t="inlineStr">
+        <is>
+          <t>Cluster creates new node sizes on demand instead of using fixed pools.</t>
+        </is>
+      </c>
+      <c r="D51" s="9" t="inlineStr">
+        <is>
+          <t>true | false</t>
+        </is>
+      </c>
+      <c r="E51" s="9" t="inlineStr">
+        <is>
+          <t>false  (true for multi-region)</t>
+        </is>
+      </c>
+      <c r="F51" s="10" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="8" t="inlineStr">
+        <is>
+          <t>11j</t>
+        </is>
+      </c>
+      <c r="B52" s="9" t="inlineStr">
+        <is>
+          <t>enable_istio</t>
+        </is>
+      </c>
+      <c r="C52" s="9" t="inlineStr">
+        <is>
+          <t>Service mesh with mTLS between pods. Needed for some compliance standards.</t>
+        </is>
+      </c>
+      <c r="D52" s="9" t="inlineStr">
+        <is>
+          <t>true | false</t>
+        </is>
+      </c>
+      <c r="E52" s="9" t="inlineStr">
+        <is>
+          <t>false  (true for regulated)</t>
+        </is>
+      </c>
+      <c r="F52" s="10" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="8" t="inlineStr">
+        <is>
+          <t>11k</t>
+        </is>
+      </c>
+      <c r="B53" s="9" t="inlineStr">
+        <is>
+          <t>enable_flux</t>
+        </is>
+      </c>
+      <c r="C53" s="9" t="inlineStr">
+        <is>
+          <t>GitOps — the cluster pulls its configuration from a Git repo.</t>
+        </is>
+      </c>
+      <c r="D53" s="9" t="inlineStr">
+        <is>
+          <t>true | false</t>
+        </is>
+      </c>
+      <c r="E53" s="9" t="inlineStr">
+        <is>
+          <t>false  (true for multi-region)</t>
+        </is>
+      </c>
+      <c r="F53" s="10" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="8" t="inlineStr">
+        <is>
+          <t>11l</t>
+        </is>
+      </c>
+      <c r="B54" s="9" t="inlineStr">
+        <is>
+          <t>enable_dapr</t>
+        </is>
+      </c>
+      <c r="C54" s="9" t="inlineStr">
+        <is>
+          <t>Building blocks for microservices (pub/sub, state, secrets).</t>
+        </is>
+      </c>
+      <c r="D54" s="9" t="inlineStr">
+        <is>
+          <t>true | false</t>
+        </is>
+      </c>
+      <c r="E54" s="9" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="F54" s="10" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="8" t="inlineStr">
+        <is>
+          <t>11m</t>
+        </is>
+      </c>
+      <c r="B55" s="9" t="inlineStr">
+        <is>
+          <t>enable_fips</t>
+        </is>
+      </c>
+      <c r="C55" s="9" t="inlineStr">
+        <is>
+          <t>Use FIPS 140-2 compliant node OS (US Federal / PCI).</t>
+        </is>
+      </c>
+      <c r="D55" s="9" t="inlineStr">
+        <is>
+          <t>true | false</t>
+        </is>
+      </c>
+      <c r="E55" s="9" t="inlineStr">
+        <is>
+          <t>false  (true for regulated)</t>
+        </is>
+      </c>
+      <c r="F55" s="10" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="8" t="inlineStr">
+        <is>
+          <t>11n</t>
+        </is>
+      </c>
+      <c r="B56" s="9" t="inlineStr">
+        <is>
+          <t>enable_backup</t>
+        </is>
+      </c>
+      <c r="C56" s="9" t="inlineStr">
+        <is>
+          <t>Azure Backup for cluster resources and persistent volumes.</t>
+        </is>
+      </c>
+      <c r="D56" s="9" t="inlineStr">
+        <is>
+          <t>true | false</t>
+        </is>
+      </c>
+      <c r="E56" s="9" t="inlineStr">
+        <is>
+          <t>false  (true for regulated / multi-region)</t>
+        </is>
+      </c>
+      <c r="F56" s="10" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="8" t="inlineStr">
+        <is>
+          <t>11o</t>
+        </is>
+      </c>
+      <c r="B57" s="9" t="inlineStr">
+        <is>
+          <t>enable_cost_analysis</t>
+        </is>
+      </c>
+      <c r="C57" s="9" t="inlineStr">
+        <is>
+          <t>Cost breakdown per namespace in the Azure portal.</t>
+        </is>
+      </c>
+      <c r="D57" s="9" t="inlineStr">
+        <is>
+          <t>true | false</t>
+        </is>
+      </c>
+      <c r="E57" s="9" t="inlineStr">
+        <is>
+          <t>false  (true for regulated)</t>
+        </is>
+      </c>
+      <c r="F57" s="10" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="12">
     <mergeCell ref="B30:F30"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B24:F24"/>
-    <mergeCell ref="B38:F38"/>
-    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B34:F34"/>
+    <mergeCell ref="B15:F15"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="B28:F28"/>
+    <mergeCell ref="B42:F42"/>
     <mergeCell ref="B5:F5"/>
-    <mergeCell ref="B19:F19"/>
-    <mergeCell ref="B46:F46"/>
-    <mergeCell ref="B26:F26"/>
-    <mergeCell ref="B9:F9"/>
+    <mergeCell ref="B37:F37"/>
+    <mergeCell ref="B23:F23"/>
+    <mergeCell ref="B8:F8"/>
   </mergeCells>
-  <dataValidations count="11">
-    <dataValidation sqref="F21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid SKU" error="Please select Free, Standard, or Premium" type="list">
+  <dataValidations count="20">
+    <dataValidation sqref="F6" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"single_region_baseline,multi_region_baseline,single_region_regulated,multi_region_regulated"</formula1>
+    </dataValidation>
+    <dataValidation sqref="F25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Free,Standard,Premium"</formula1>
     </dataValidation>
-    <dataValidation sqref="F22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"true,false"</formula1>
     </dataValidation>
-    <dataValidation sqref="F31" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"true,false"</formula1>
     </dataValidation>
-    <dataValidation sqref="F32" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"true,false"</formula1>
-    </dataValidation>
-    <dataValidation sqref="F39" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"true,false"</formula1>
-    </dataValidation>
-    <dataValidation sqref="F40" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"true,false"</formula1>
-    </dataValidation>
-    <dataValidation sqref="F41" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"true,false"</formula1>
-    </dataValidation>
-    <dataValidation sqref="F42" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F36" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"true,false"</formula1>
     </dataValidation>
     <dataValidation sqref="F43" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
@@ -2069,6 +2157,42 @@
       <formula1>"true,false"</formula1>
     </dataValidation>
     <dataValidation sqref="F45" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"true,false"</formula1>
+    </dataValidation>
+    <dataValidation sqref="F46" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"true,false"</formula1>
+    </dataValidation>
+    <dataValidation sqref="F47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"true,false"</formula1>
+    </dataValidation>
+    <dataValidation sqref="F48" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"true,false"</formula1>
+    </dataValidation>
+    <dataValidation sqref="F49" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"true,false"</formula1>
+    </dataValidation>
+    <dataValidation sqref="F50" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"true,false"</formula1>
+    </dataValidation>
+    <dataValidation sqref="F51" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"true,false"</formula1>
+    </dataValidation>
+    <dataValidation sqref="F52" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"true,false"</formula1>
+    </dataValidation>
+    <dataValidation sqref="F53" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"true,false"</formula1>
+    </dataValidation>
+    <dataValidation sqref="F54" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"true,false"</formula1>
+    </dataValidation>
+    <dataValidation sqref="F55" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"true,false"</formula1>
+    </dataValidation>
+    <dataValidation sqref="F56" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"true,false"</formula1>
+    </dataValidation>
+    <dataValidation sqref="F57" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"true,false"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2082,1082 +2206,516 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F43"/>
+  <dimension ref="A1:E26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="38" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
-    <col width="55" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="55" customWidth="1" min="2" max="2"/>
+    <col width="45" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>AKS Application Landing Zone - Scenario and Options Decisions</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
+          <t>Advanced Cluster Settings</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>Choose your AKS landing zone scenario and configure options. These map to settings in config/aks-landing-zone.tfvars.</t>
+          <t>These come from the scenario you picked (see Tab 1, Decision 0a). Only change them if you have a specific reason. Edit `aks-landing-zone.auto.tfvars` in the generated repo to override.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>Setting</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>Setting</t>
+          <t>What it does</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Example / options</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>Options / Guidance</t>
+          <t>Default</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>Default</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>Your Value</t>
+          <t>Your value</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr"/>
-      <c r="B5" s="7" t="inlineStr">
-        <is>
-          <t>SCENARIO</t>
-        </is>
-      </c>
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>SYSTEM NODE POOL  (small pool that runs Kubernetes itself)</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="n"/>
       <c r="C5" s="7" t="n"/>
       <c r="D5" s="7" t="n"/>
       <c r="E5" s="7" t="n"/>
-      <c r="F5" s="7" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="9" t="inlineStr">
         <is>
-          <t>Scenario</t>
+          <t>system_node_pool.vm_size</t>
         </is>
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>deployment_topology</t>
+          <t>Size of each system node.</t>
         </is>
       </c>
       <c r="C6" s="9" t="inlineStr">
         <is>
-          <t>The network topology for the AKS landing zone.</t>
+          <t>Standard_D4ds_v5 (4 vCPU)
+Standard_D8ds_v5 (8 vCPU)</t>
         </is>
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>hub_spoke = Spoke VNet peered to existing ALZ hub with UDR to firewall.
-This is the only supported scenario for aksapplz.</t>
-        </is>
-      </c>
-      <c r="E6" s="9" t="inlineStr">
-        <is>
-          <t>hub_spoke</t>
-        </is>
-      </c>
-      <c r="F6" s="10" t="inlineStr"/>
+          <t>Standard_D4ds_v5</t>
+        </is>
+      </c>
+      <c r="E6" s="10" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="inlineStr"/>
-      <c r="B7" s="7" t="inlineStr">
-        <is>
-          <t>COMPUTE - SYSTEM NODE POOL</t>
-        </is>
-      </c>
-      <c r="C7" s="7" t="n"/>
-      <c r="D7" s="7" t="n"/>
-      <c r="E7" s="7" t="n"/>
-      <c r="F7" s="7" t="n"/>
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>system_node_pool.min_count</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>Smallest number of system nodes.</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>2 keeps the cluster healthy if one node fails.</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E7" s="10" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="9" t="inlineStr">
         <is>
-          <t>Compute</t>
+          <t>system_node_pool.max_count</t>
         </is>
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>system_node_pool_vm_size</t>
+          <t>Largest number of system nodes.</t>
         </is>
       </c>
       <c r="C8" s="9" t="inlineStr">
         <is>
-          <t>VM SKU for the system node pool (runs critical system pods).</t>
+          <t>3–5 is plenty for system pods.</t>
         </is>
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
-          <t>Standard_D4ds_v5, Standard_D8ds_v5, Standard_D4s_v5, etc.
-Must support ephemeral OS disks.</t>
-        </is>
-      </c>
-      <c r="E8" s="9" t="inlineStr">
-        <is>
-          <t>Standard_D4ds_v5</t>
-        </is>
-      </c>
-      <c r="F8" s="10" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E8" s="10" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>Compute</t>
-        </is>
-      </c>
-      <c r="B9" s="9" t="inlineStr">
-        <is>
-          <t>system_node_pool_min_count</t>
-        </is>
-      </c>
-      <c r="C9" s="9" t="inlineStr">
-        <is>
-          <t>Minimum number of nodes in the system pool (autoscaler lower bound).</t>
-        </is>
-      </c>
-      <c r="D9" s="9" t="inlineStr">
-        <is>
-          <t>Integer &gt;= 2 for production high availability.</t>
-        </is>
-      </c>
-      <c r="E9" s="9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F9" s="10" t="inlineStr"/>
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>USER NODE POOL  (where your apps actually run)</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="n"/>
+      <c r="C9" s="7" t="n"/>
+      <c r="D9" s="7" t="n"/>
+      <c r="E9" s="7" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t>Compute</t>
+          <t>user_node_pool.vm_size</t>
         </is>
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>system_node_pool_max_count</t>
+          <t>Size of each application node.</t>
         </is>
       </c>
       <c r="C10" s="9" t="inlineStr">
         <is>
-          <t>Maximum number of nodes in the system pool.</t>
+          <t>Standard_D4ds_v5, Standard_D8ds_v5, Standard_D16ds_v5</t>
         </is>
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>Integer. Typically 3-5 for system workloads.</t>
-        </is>
-      </c>
-      <c r="E10" s="9" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="F10" s="10" t="inlineStr"/>
+          <t>Standard_D4ds_v5</t>
+        </is>
+      </c>
+      <c r="E10" s="10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="9" t="inlineStr">
         <is>
-          <t>Compute</t>
+          <t>user_node_pool.min_count</t>
         </is>
       </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>system_node_pool_os_disk_type</t>
+          <t>Smallest number of application nodes.</t>
         </is>
       </c>
       <c r="C11" s="9" t="inlineStr">
         <is>
-          <t>OS disk type for system nodes.</t>
+          <t>2 or more for production.</t>
         </is>
       </c>
       <c r="D11" s="9" t="inlineStr">
         <is>
-          <t>Ephemeral = Local SSD (faster, no cost).
-Managed = Azure managed disk.</t>
-        </is>
-      </c>
-      <c r="E11" s="9" t="inlineStr">
-        <is>
-          <t>Ephemeral</t>
-        </is>
-      </c>
-      <c r="F11" s="10" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E11" s="10" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="7" t="inlineStr"/>
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>COMPUTE - USER NODE POOL</t>
-        </is>
-      </c>
-      <c r="C12" s="7" t="n"/>
-      <c r="D12" s="7" t="n"/>
-      <c r="E12" s="7" t="n"/>
-      <c r="F12" s="7" t="n"/>
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>user_node_pool.max_count</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>Largest number of application nodes (autoscaler limit).</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>Size to your peak traffic.</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E12" s="10" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="9" t="inlineStr">
-        <is>
-          <t>Compute</t>
-        </is>
-      </c>
-      <c r="B13" s="9" t="inlineStr">
-        <is>
-          <t>user_node_pool_vm_size</t>
-        </is>
-      </c>
-      <c r="C13" s="9" t="inlineStr">
-        <is>
-          <t>VM SKU for the user node pool (runs application workloads).</t>
-        </is>
-      </c>
-      <c r="D13" s="9" t="inlineStr">
-        <is>
-          <t>Standard_D4ds_v5, Standard_D8ds_v5, Standard_D16ds_v5, etc.
-Choose based on application requirements.</t>
-        </is>
-      </c>
-      <c r="E13" s="9" t="inlineStr">
-        <is>
-          <t>Standard_D4ds_v5</t>
-        </is>
-      </c>
-      <c r="F13" s="10" t="inlineStr"/>
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>NETWORKING</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="n"/>
+      <c r="C13" s="7" t="n"/>
+      <c r="D13" s="7" t="n"/>
+      <c r="E13" s="7" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t>Compute</t>
+          <t>network_policy</t>
         </is>
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>user_node_pool_min_count</t>
+          <t>Which pod-to-pod firewall to use inside the cluster.</t>
         </is>
       </c>
       <c r="C14" s="9" t="inlineStr">
         <is>
-          <t>Minimum number of nodes in the user pool.</t>
+          <t>calico  (baseline)
+azure   (regulated; NPM)</t>
         </is>
       </c>
       <c r="D14" s="9" t="inlineStr">
         <is>
-          <t>Integer &gt;= 2 for production. KEDA/HPA will autoscale above this.</t>
-        </is>
-      </c>
-      <c r="E14" s="9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F14" s="10" t="inlineStr"/>
+          <t>calico (azure for regulated)</t>
+        </is>
+      </c>
+      <c r="E14" s="10" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t>Compute</t>
+          <t>service_cidr</t>
         </is>
       </c>
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>user_node_pool_max_count</t>
+          <t>IP range Kubernetes uses for its internal services. Must not overlap any VNet.</t>
         </is>
       </c>
       <c r="C15" s="9" t="inlineStr">
         <is>
-          <t>Maximum number of nodes in the user pool (autoscaler upper bound).</t>
+          <t>172.16.0.0/16</t>
         </is>
       </c>
       <c r="D15" s="9" t="inlineStr">
         <is>
-          <t>Integer. Set based on peak workload requirements.</t>
-        </is>
-      </c>
-      <c r="E15" s="9" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="F15" s="10" t="inlineStr"/>
+          <t>172.16.0.0/16</t>
+        </is>
+      </c>
+      <c r="E15" s="10" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="9" t="inlineStr">
         <is>
-          <t>Compute</t>
+          <t>dns_service_ip</t>
         </is>
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>user_node_pool_os_disk_type</t>
+          <t>IP of the cluster DNS. Must sit inside service_cidr.</t>
         </is>
       </c>
       <c r="C16" s="9" t="inlineStr">
         <is>
-          <t>OS disk type for user nodes.</t>
+          <t>172.16.0.10</t>
         </is>
       </c>
       <c r="D16" s="9" t="inlineStr">
         <is>
-          <t>Ephemeral | Managed</t>
-        </is>
-      </c>
-      <c r="E16" s="9" t="inlineStr">
-        <is>
-          <t>Ephemeral</t>
-        </is>
-      </c>
-      <c r="F16" s="10" t="inlineStr"/>
+          <t>172.16.0.10</t>
+        </is>
+      </c>
+      <c r="E16" s="10" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="7" t="inlineStr"/>
-      <c r="B17" s="7" t="inlineStr">
-        <is>
-          <t>NETWORKING</t>
-        </is>
-      </c>
-      <c r="C17" s="7" t="n"/>
-      <c r="D17" s="7" t="n"/>
-      <c r="E17" s="7" t="n"/>
-      <c r="F17" s="7" t="n"/>
+      <c r="A17" s="9" t="inlineStr">
+        <is>
+          <t>pod_cidr</t>
+        </is>
+      </c>
+      <c r="B17" s="9" t="inlineStr">
+        <is>
+          <t>IP range for pods (used by Azure CNI Overlay).</t>
+        </is>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>192.168.0.0/16</t>
+        </is>
+      </c>
+      <c r="D17" s="9" t="inlineStr">
+        <is>
+          <t>192.168.0.0/16</t>
+        </is>
+      </c>
+      <c r="E17" s="10" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="9" t="inlineStr">
-        <is>
-          <t>Networking</t>
-        </is>
-      </c>
-      <c r="B18" s="9" t="inlineStr">
-        <is>
-          <t>network_plugin</t>
-        </is>
-      </c>
-      <c r="C18" s="9" t="inlineStr">
-        <is>
-          <t>Kubernetes network plugin for pod networking.</t>
-        </is>
-      </c>
-      <c r="D18" s="9" t="inlineStr">
-        <is>
-          <t>azure (Azure CNI Overlay) = Pods get overlay IPs, no VNet IP exhaustion.
-kubenet = Basic networking (not recommended for production).</t>
-        </is>
-      </c>
-      <c r="E18" s="9" t="inlineStr">
-        <is>
-          <t>azure</t>
-        </is>
-      </c>
-      <c r="F18" s="10" t="inlineStr"/>
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>UPGRADES</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="n"/>
+      <c r="C18" s="7" t="n"/>
+      <c r="D18" s="7" t="n"/>
+      <c r="E18" s="7" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="9" t="inlineStr">
         <is>
-          <t>Networking</t>
+          <t>automatic_upgrade_channel</t>
         </is>
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>network_plugin_mode</t>
+          <t>When AKS should auto-install Kubernetes patches.</t>
         </is>
       </c>
       <c r="C19" s="9" t="inlineStr">
         <is>
-          <t>Network plugin mode when using Azure CNI.</t>
+          <t>patch | stable | rapid | node-image | none</t>
         </is>
       </c>
       <c r="D19" s="9" t="inlineStr">
         <is>
-          <t>overlay = Recommended. Separates pod IPs from VNet IPs.</t>
-        </is>
-      </c>
-      <c r="E19" s="9" t="inlineStr">
-        <is>
-          <t>overlay</t>
-        </is>
-      </c>
-      <c r="F19" s="10" t="inlineStr"/>
+          <t>patch</t>
+        </is>
+      </c>
+      <c r="E19" s="10" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="9" t="inlineStr">
         <is>
-          <t>Networking</t>
+          <t>node_os_upgrade_channel</t>
         </is>
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>network_dataplane</t>
+          <t>When AKS should auto-patch the node OS.</t>
         </is>
       </c>
       <c r="C20" s="9" t="inlineStr">
         <is>
-          <t>Network dataplane technology.</t>
+          <t>NodeImage | SecurityPatch | None</t>
         </is>
       </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
-          <t>cilium = eBPF-based (better performance, network policies).
-azure = Standard Azure networking.</t>
-        </is>
-      </c>
-      <c r="E20" s="9" t="inlineStr">
-        <is>
-          <t>azure</t>
-        </is>
-      </c>
-      <c r="F20" s="10" t="inlineStr"/>
+          <t>NodeImage</t>
+        </is>
+      </c>
+      <c r="E20" s="10" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="9" t="inlineStr">
-        <is>
-          <t>Networking</t>
-        </is>
-      </c>
-      <c r="B21" s="9" t="inlineStr">
-        <is>
-          <t>service_cidr</t>
-        </is>
-      </c>
-      <c r="C21" s="9" t="inlineStr">
-        <is>
-          <t>CIDR for Kubernetes services. Must not overlap with any VNet ranges.</t>
-        </is>
-      </c>
-      <c r="D21" s="9" t="inlineStr">
-        <is>
-          <t>CIDR notation. E.g.: 172.16.0.0/16</t>
-        </is>
-      </c>
-      <c r="E21" s="9" t="inlineStr">
-        <is>
-          <t>172.16.0.0/16</t>
-        </is>
-      </c>
-      <c r="F21" s="10" t="inlineStr"/>
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>APPLICATION GATEWAY (web traffic + WAF)</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="n"/>
+      <c r="C21" s="7" t="n"/>
+      <c r="D21" s="7" t="n"/>
+      <c r="E21" s="7" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="9" t="inlineStr">
         <is>
-          <t>Networking</t>
+          <t>app_gateway_sku</t>
         </is>
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>dns_service_ip</t>
+          <t>Application Gateway tier. WAF_v2 includes the Web Application Firewall.</t>
         </is>
       </c>
       <c r="C22" s="9" t="inlineStr">
         <is>
-          <t>IP for the Kubernetes DNS service. Must be within service_cidr.</t>
+          <t>WAF_v2 | Standard_v2</t>
         </is>
       </c>
       <c r="D22" s="9" t="inlineStr">
         <is>
-          <t>IP address. E.g.: 172.16.0.10</t>
-        </is>
-      </c>
-      <c r="E22" s="9" t="inlineStr">
-        <is>
-          <t>172.16.0.10</t>
-        </is>
-      </c>
-      <c r="F22" s="10" t="inlineStr"/>
+          <t>WAF_v2</t>
+        </is>
+      </c>
+      <c r="E22" s="10" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="7" t="inlineStr"/>
-      <c r="B23" s="7" t="inlineStr">
-        <is>
-          <t>SECURITY</t>
-        </is>
-      </c>
-      <c r="C23" s="7" t="n"/>
-      <c r="D23" s="7" t="n"/>
-      <c r="E23" s="7" t="n"/>
-      <c r="F23" s="7" t="n"/>
+      <c r="A23" s="9" t="inlineStr">
+        <is>
+          <t>app_gateway_min_capacity</t>
+        </is>
+      </c>
+      <c r="B23" s="9" t="inlineStr">
+        <is>
+          <t>Always-on capacity.</t>
+        </is>
+      </c>
+      <c r="C23" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D23" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E23" s="10" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="9" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>app_gateway_max_capacity</t>
         </is>
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>acr_sku</t>
+          <t>Maximum capacity under load.</t>
         </is>
       </c>
       <c r="C24" s="9" t="inlineStr">
         <is>
-          <t>Azure Container Registry SKU. Premium required for private endpoints and geo-replication.</t>
+          <t>Pick based on expected traffic.</t>
         </is>
       </c>
       <c r="D24" s="9" t="inlineStr">
         <is>
-          <t>Premium (recommended) | Standard | Basic</t>
-        </is>
-      </c>
-      <c r="E24" s="9" t="inlineStr">
-        <is>
-          <t>Premium</t>
-        </is>
-      </c>
-      <c r="F24" s="10" t="inlineStr"/>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E24" s="10" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="9" t="inlineStr">
-        <is>
-          <t>Security</t>
-        </is>
-      </c>
-      <c r="B25" s="9" t="inlineStr">
-        <is>
-          <t>acr_zone_redundancy</t>
-        </is>
-      </c>
-      <c r="C25" s="9" t="inlineStr">
-        <is>
-          <t>Enable zone redundancy for ACR. Premium SKU only.</t>
-        </is>
-      </c>
-      <c r="D25" s="9" t="inlineStr">
-        <is>
-          <t>true | false</t>
-        </is>
-      </c>
-      <c r="E25" s="9" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="F25" s="10" t="inlineStr"/>
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>LOGS &amp; DASHBOARDS</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="n"/>
+      <c r="C25" s="7" t="n"/>
+      <c r="D25" s="7" t="n"/>
+      <c r="E25" s="7" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="9" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>log_analytics_retention_days</t>
         </is>
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>key_vault_purge_protection</t>
+          <t>How long to keep cluster logs. Longer = more cost.</t>
         </is>
       </c>
       <c r="C26" s="9" t="inlineStr">
         <is>
-          <t>Enable purge protection on Key Vault. Prevents permanent deletion.</t>
+          <t>30, 90, 365 ...</t>
         </is>
       </c>
       <c r="D26" s="9" t="inlineStr">
         <is>
-          <t>true (recommended for production) | false</t>
-        </is>
-      </c>
-      <c r="E26" s="9" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="F26" s="10" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="9" t="inlineStr">
-        <is>
-          <t>Security</t>
-        </is>
-      </c>
-      <c r="B27" s="9" t="inlineStr">
-        <is>
-          <t>key_vault_soft_delete_days</t>
-        </is>
-      </c>
-      <c r="C27" s="9" t="inlineStr">
-        <is>
-          <t>Number of days to retain soft-deleted Key Vault items.</t>
-        </is>
-      </c>
-      <c r="D27" s="9" t="inlineStr">
-        <is>
-          <t>7 - 90 days.</t>
-        </is>
-      </c>
-      <c r="E27" s="9" t="inlineStr">
-        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="F27" s="10" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="7" t="inlineStr"/>
-      <c r="B28" s="7" t="inlineStr">
-        <is>
-          <t>APPLICATION GATEWAY WAF</t>
-        </is>
-      </c>
-      <c r="C28" s="7" t="n"/>
-      <c r="D28" s="7" t="n"/>
-      <c r="E28" s="7" t="n"/>
-      <c r="F28" s="7" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="9" t="inlineStr">
-        <is>
-          <t>App Gateway</t>
-        </is>
-      </c>
-      <c r="B29" s="9" t="inlineStr">
-        <is>
-          <t>app_gateway_sku</t>
-        </is>
-      </c>
-      <c r="C29" s="9" t="inlineStr">
-        <is>
-          <t>Application Gateway SKU.</t>
-        </is>
-      </c>
-      <c r="D29" s="9" t="inlineStr">
-        <is>
-          <t>WAF_v2 (recommended — includes Web Application Firewall).
-Standard_v2 (no WAF).</t>
-        </is>
-      </c>
-      <c r="E29" s="9" t="inlineStr">
-        <is>
-          <t>WAF_v2</t>
-        </is>
-      </c>
-      <c r="F29" s="10" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="9" t="inlineStr">
-        <is>
-          <t>App Gateway</t>
-        </is>
-      </c>
-      <c r="B30" s="9" t="inlineStr">
-        <is>
-          <t>app_gateway_min_capacity</t>
-        </is>
-      </c>
-      <c r="C30" s="9" t="inlineStr">
-        <is>
-          <t>Minimum autoscale capacity for Application Gateway.</t>
-        </is>
-      </c>
-      <c r="D30" s="9" t="inlineStr">
-        <is>
-          <t>Integer &gt;= 1.</t>
-        </is>
-      </c>
-      <c r="E30" s="9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F30" s="10" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="9" t="inlineStr">
-        <is>
-          <t>App Gateway</t>
-        </is>
-      </c>
-      <c r="B31" s="9" t="inlineStr">
-        <is>
-          <t>app_gateway_max_capacity</t>
-        </is>
-      </c>
-      <c r="C31" s="9" t="inlineStr">
-        <is>
-          <t>Maximum autoscale capacity for Application Gateway.</t>
-        </is>
-      </c>
-      <c r="D31" s="9" t="inlineStr">
-        <is>
-          <t>Integer. Set based on expected traffic.</t>
-        </is>
-      </c>
-      <c r="E31" s="9" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="F31" s="10" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="9" t="inlineStr">
-        <is>
-          <t>App Gateway</t>
-        </is>
-      </c>
-      <c r="B32" s="9" t="inlineStr">
-        <is>
-          <t>waf_rule_set_type</t>
-        </is>
-      </c>
-      <c r="C32" s="9" t="inlineStr">
-        <is>
-          <t>WAF managed rule set type.</t>
-        </is>
-      </c>
-      <c r="D32" s="9" t="inlineStr">
-        <is>
-          <t>OWASP (standard web protection rules).</t>
-        </is>
-      </c>
-      <c r="E32" s="9" t="inlineStr">
-        <is>
-          <t>OWASP</t>
-        </is>
-      </c>
-      <c r="F32" s="10" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="9" t="inlineStr">
-        <is>
-          <t>App Gateway</t>
-        </is>
-      </c>
-      <c r="B33" s="9" t="inlineStr">
-        <is>
-          <t>waf_rule_set_version</t>
-        </is>
-      </c>
-      <c r="C33" s="9" t="inlineStr">
-        <is>
-          <t>WAF managed rule set version.</t>
-        </is>
-      </c>
-      <c r="D33" s="9" t="inlineStr">
-        <is>
-          <t>3.2 (latest recommended) | 3.1 | 3.0</t>
-        </is>
-      </c>
-      <c r="E33" s="9" t="inlineStr">
-        <is>
-          <t>3.2</t>
-        </is>
-      </c>
-      <c r="F33" s="10" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="7" t="inlineStr"/>
-      <c r="B34" s="7" t="inlineStr">
-        <is>
-          <t>MONITORING</t>
-        </is>
-      </c>
-      <c r="C34" s="7" t="n"/>
-      <c r="D34" s="7" t="n"/>
-      <c r="E34" s="7" t="n"/>
-      <c r="F34" s="7" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="9" t="inlineStr">
-        <is>
-          <t>Monitoring</t>
-        </is>
-      </c>
-      <c r="B35" s="9" t="inlineStr">
-        <is>
-          <t>log_analytics_retention_days</t>
-        </is>
-      </c>
-      <c r="C35" s="9" t="inlineStr">
-        <is>
-          <t>Log retention period in Log Analytics workspace.</t>
-        </is>
-      </c>
-      <c r="D35" s="9" t="inlineStr">
-        <is>
-          <t>30 - 730 days. Longer retention increases cost.</t>
-        </is>
-      </c>
-      <c r="E35" s="9" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="F35" s="10" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="9" t="inlineStr">
-        <is>
-          <t>Monitoring</t>
-        </is>
-      </c>
-      <c r="B36" s="9" t="inlineStr">
-        <is>
-          <t>grafana_sku</t>
-        </is>
-      </c>
-      <c r="C36" s="9" t="inlineStr">
-        <is>
-          <t>Azure Managed Grafana SKU.</t>
-        </is>
-      </c>
-      <c r="D36" s="9" t="inlineStr">
-        <is>
-          <t>Standard (includes all features, 10 users free).</t>
-        </is>
-      </c>
-      <c r="E36" s="9" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="F36" s="10" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="7" t="inlineStr"/>
-      <c r="B37" s="7" t="inlineStr">
-        <is>
-          <t>AKS ADVANCED</t>
-        </is>
-      </c>
-      <c r="C37" s="7" t="n"/>
-      <c r="D37" s="7" t="n"/>
-      <c r="E37" s="7" t="n"/>
-      <c r="F37" s="7" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="9" t="inlineStr">
-        <is>
-          <t>AKS</t>
-        </is>
-      </c>
-      <c r="B38" s="9" t="inlineStr">
-        <is>
-          <t>auto_upgrade_channel</t>
-        </is>
-      </c>
-      <c r="C38" s="9" t="inlineStr">
-        <is>
-          <t>AKS auto-upgrade channel for Kubernetes patches.</t>
-        </is>
-      </c>
-      <c r="D38" s="9" t="inlineStr">
-        <is>
-          <t>patch = Auto-apply patch versions (e.g., 1.31.1 → 1.31.2).
-stable = Auto-apply stable versions.
-none = Manual upgrades only.</t>
-        </is>
-      </c>
-      <c r="E38" s="9" t="inlineStr">
-        <is>
-          <t>patch</t>
-        </is>
-      </c>
-      <c r="F38" s="10" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="9" t="inlineStr">
-        <is>
-          <t>AKS</t>
-        </is>
-      </c>
-      <c r="B39" s="9" t="inlineStr">
-        <is>
-          <t>image_cleaner_enabled</t>
-        </is>
-      </c>
-      <c r="C39" s="9" t="inlineStr">
-        <is>
-          <t>Enable Image Cleaner to remove unused container images from nodes.</t>
-        </is>
-      </c>
-      <c r="D39" s="9" t="inlineStr">
-        <is>
-          <t>true | false</t>
-        </is>
-      </c>
-      <c r="E39" s="9" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="F39" s="10" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="9" t="inlineStr">
-        <is>
-          <t>AKS</t>
-        </is>
-      </c>
-      <c r="B40" s="9" t="inlineStr">
-        <is>
-          <t>image_cleaner_interval_hours</t>
-        </is>
-      </c>
-      <c r="C40" s="9" t="inlineStr">
-        <is>
-          <t>How often Image Cleaner runs (in hours).</t>
-        </is>
-      </c>
-      <c r="D40" s="9" t="inlineStr">
-        <is>
-          <t>Integer. E.g.: 48, 24, 168</t>
-        </is>
-      </c>
-      <c r="E40" s="9" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="F40" s="10" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="9" t="inlineStr">
-        <is>
-          <t>AKS</t>
-        </is>
-      </c>
-      <c r="B41" s="9" t="inlineStr">
-        <is>
-          <t>azure_policy_enabled</t>
-        </is>
-      </c>
-      <c r="C41" s="9" t="inlineStr">
-        <is>
-          <t>Enable Azure Policy addon for AKS governance.</t>
-        </is>
-      </c>
-      <c r="D41" s="9" t="inlineStr">
-        <is>
-          <t>true (recommended) | false</t>
-        </is>
-      </c>
-      <c r="E41" s="9" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="F41" s="10" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="9" t="inlineStr">
-        <is>
-          <t>AKS</t>
-        </is>
-      </c>
-      <c r="B42" s="9" t="inlineStr">
-        <is>
-          <t>workload_identity_enabled</t>
-        </is>
-      </c>
-      <c r="C42" s="9" t="inlineStr">
-        <is>
-          <t>Enable Workload Identity for pod-level Azure authentication.</t>
-        </is>
-      </c>
-      <c r="D42" s="9" t="inlineStr">
-        <is>
-          <t>true (recommended — eliminates stored credentials) | false</t>
-        </is>
-      </c>
-      <c r="E42" s="9" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="F42" s="10" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="9" t="inlineStr">
-        <is>
-          <t>AKS</t>
-        </is>
-      </c>
-      <c r="B43" s="9" t="inlineStr">
-        <is>
-          <t>oidc_issuer_enabled</t>
-        </is>
-      </c>
-      <c r="C43" s="9" t="inlineStr">
-        <is>
-          <t>Enable OIDC issuer for federated identity scenarios.</t>
-        </is>
-      </c>
-      <c r="D43" s="9" t="inlineStr">
-        <is>
-          <t>true (required for Workload Identity) | false</t>
-        </is>
-      </c>
-      <c r="E43" s="9" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="F43" s="10" t="inlineStr"/>
+      <c r="E26" s="10" t="inlineStr"/>
     </row>
   </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B7:F7"/>
-    <mergeCell ref="B34:F34"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="B28:F28"/>
-    <mergeCell ref="B5:F5"/>
-    <mergeCell ref="B37:F37"/>
-    <mergeCell ref="B23:F23"/>
-    <mergeCell ref="B17:F17"/>
+  <mergeCells count="8">
+    <mergeCell ref="A21:E21"/>
+    <mergeCell ref="A18:E18"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A13:E13"/>
+    <mergeCell ref="A9:E9"/>
   </mergeCells>
-  <dataValidations count="11">
-    <dataValidation sqref="F11" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Ephemeral,Managed"</formula1>
+  <dataValidations count="4">
+    <dataValidation sqref="E14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"calico,azure,cilium"</formula1>
     </dataValidation>
-    <dataValidation sqref="F16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Ephemeral,Managed"</formula1>
+    <dataValidation sqref="E19" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"patch,stable,rapid,node-image,none"</formula1>
     </dataValidation>
-    <dataValidation sqref="F24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Premium,Standard,Basic"</formula1>
+    <dataValidation sqref="E20" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"NodeImage,SecurityPatch,None"</formula1>
     </dataValidation>
-    <dataValidation sqref="F25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"true,false"</formula1>
-    </dataValidation>
-    <dataValidation sqref="F26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"true,false"</formula1>
-    </dataValidation>
-    <dataValidation sqref="F29" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"WAF_v2,Standard_v2"</formula1>
-    </dataValidation>
-    <dataValidation sqref="F38" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"patch,stable,none"</formula1>
-    </dataValidation>
-    <dataValidation sqref="F39" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"true,false"</formula1>
-    </dataValidation>
-    <dataValidation sqref="F41" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"true,false"</formula1>
-    </dataValidation>
-    <dataValidation sqref="F42" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"true,false"</formula1>
-    </dataValidation>
-    <dataValidation sqref="F43" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"true,false"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/config/checklist.xlsx
+++ b/config/checklist.xlsx
@@ -501,7 +501,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A39"/>
+  <dimension ref="A1:A40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -561,176 +561,183 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">   - Pick a topology (row 0c) — 'spoke' if you already have an ALZ hub, 'standalone' for an isolated subscription. Standalone skips Decisions 3 and 4.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">   - Don't put GitHub tokens in the workbook. The wizard asks for them with hidden input.</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr"/>
-    </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>2. Open 'Advanced Cluster Settings' only if you need to change cluster sizing, networking,</t>
-        </is>
-      </c>
+      <c r="A12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>2. Open 'Advanced Cluster Settings' only if you need to change cluster sizing, networking,</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">   or upgrade behaviour. Most teams leave this tab alone.</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr"/>
-    </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>3. Run the wizard and use the workbook as your reference:</t>
-        </is>
-      </c>
+      <c r="A15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">       Import-Module .\ALZ.AKS\ALZ.AKS.psd1 -Force</t>
+          <t>3. Run the wizard and use the workbook as your reference:</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">       Import-Module .\ALZ.AKS\ALZ.AKS.psd1 -Force</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">       Deploy-AKSLandingZone</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr"/>
-    </row>
     <row r="19">
-      <c r="A19" s="3" t="inlineStr">
+      <c r="A19" s="2" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
         <is>
           <t>What the wizard does</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr"/>
-    </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>Phase A — asks you the questions in this workbook and writes config files.</t>
-        </is>
-      </c>
+      <c r="A21" s="2" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Phase B — creates the Azure resources, GitHub repos, runner, and pushes the Terraform code.</t>
+          <t>Phase A — asks you the questions in this workbook and writes config files.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
+          <t>Phase B — creates the Azure resources, GitHub repos, runner, and pushes the Terraform code.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
           <t>Phase C — your PRs in the new GitHub repo run plan/apply and deploy the cluster.</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr"/>
-    </row>
     <row r="25">
-      <c r="A25" s="3" t="inlineStr">
+      <c r="A25" s="2" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
         <is>
           <t>GitHub tokens — scopes you need</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr"/>
-    </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>Main token (always):    repo, workflow, admin:org (Members Read &amp; Write)</t>
-        </is>
-      </c>
+      <c r="A27" s="2" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>Main token (always):    repo, workflow, admin:org (Members Read &amp; Write)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
           <t>Runner token (if 9a is true):  admin:org (full)</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr"/>
-    </row>
     <row r="30">
-      <c r="A30" s="3" t="inlineStr">
+      <c r="A30" s="2" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
         <is>
           <t>Resource names you will see</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr"/>
-    </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>Pattern: {service}-{env}-{region-short}-{number}</t>
-        </is>
-      </c>
+      <c r="A32" s="2" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>Example with defaults (aksapplz, prod, swedencentral, 1):</t>
+          <t>Pattern: {service}-{env}-{region-short}-{number}</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Resource group for state:     rg-aksapplz-prod-sc-001</t>
+          <t>Example with defaults (aksapplz, prod, swedencentral, 1):</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Resource group for identity:  rg-aksapplz-prod-sc-identity</t>
+          <t xml:space="preserve">  Resource group for state:     rg-aksapplz-prod-sc-001</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Resource group for runner:    rg-aksapplz-prod-sc-agents     (only with self-hosted runners)</t>
+          <t xml:space="preserve">  Resource group for identity:  rg-aksapplz-prod-sc-identity</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  GitHub repository:            aksapplz-prod</t>
+          <t xml:space="preserve">  Resource group for runner:    rg-aksapplz-prod-sc-agents     (only with self-hosted runners)</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  GitHub templates repo:        aksapplz-prod-templates</t>
+          <t xml:space="preserve">  GitHub repository:            aksapplz-prod</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  GitHub templates repo:        aksapplz-prod-templates</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">  Approver team:                aksapplz-prod-approvers</t>
         </is>
@@ -747,7 +754,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F57"/>
+  <dimension ref="A1:F58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -872,226 +879,227 @@
       <c r="F7" s="10" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr"/>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>0c</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>topology</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>How the AKS landing zone connects to the network. 'spoke' peers to an existing ALZ hub and routes egress through the hub firewall; 'standalone' has no hub, no peering, and uses a NAT gateway for egress (Decisions 3 and 4 are ignored).</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>spoke      (default; peer to existing ALZ hub)
+standalone (no hub, NAT egress only)</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>spoke</t>
+        </is>
+      </c>
+      <c r="F8" s="10" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr"/>
+      <c r="B9" s="7" t="inlineStr">
         <is>
           <t>WHERE TO DEPLOY</t>
         </is>
       </c>
-      <c r="C8" s="7" t="n"/>
-      <c r="D8" s="7" t="n"/>
-      <c r="E8" s="7" t="n"/>
-      <c r="F8" s="7" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B9" s="9" t="inlineStr">
-        <is>
-          <t>bootstrap_location</t>
-        </is>
-      </c>
-      <c r="C9" s="9" t="inlineStr">
-        <is>
-          <t>Main Azure region for the cluster and supporting resources.</t>
-        </is>
-      </c>
-      <c r="D9" s="9" t="inlineStr">
-        <is>
-          <t>swedencentral, westeurope, eastus2 ...</t>
-        </is>
-      </c>
-      <c r="E9" s="9" t="inlineStr">
-        <is>
-          <t>swedencentral</t>
-        </is>
-      </c>
-      <c r="F9" s="10" t="inlineStr"/>
+      <c r="C9" s="7" t="n"/>
+      <c r="D9" s="7" t="n"/>
+      <c r="E9" s="7" t="n"/>
+      <c r="F9" s="7" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>bootstrap_location</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>Main Azure region for the cluster and supporting resources.</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="inlineStr">
+        <is>
+          <t>swedencentral, westeurope, eastus2 ...</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="inlineStr">
+        <is>
+          <t>swedencentral</t>
+        </is>
+      </c>
+      <c r="F10" s="10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B10" s="9" t="inlineStr">
+      <c r="B11" s="9" t="inlineStr">
         <is>
           <t>aks_landing_zone_subscription_id</t>
         </is>
       </c>
-      <c r="C10" s="9" t="inlineStr">
+      <c r="C11" s="9" t="inlineStr">
         <is>
           <t>Subscription where the AKS cluster will be created.</t>
         </is>
       </c>
-      <c r="D10" s="9" t="inlineStr">
+      <c r="D11" s="9" t="inlineStr">
         <is>
           <t>Subscription ID (GUID).
 Leave blank to use whatever `az` is logged into.</t>
         </is>
       </c>
-      <c r="E10" s="9" t="inlineStr">
+      <c r="E11" s="9" t="inlineStr">
         <is>
           <t>(current az subscription)</t>
         </is>
       </c>
-      <c r="F10" s="10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="8" t="inlineStr">
+      <c r="F11" s="10" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B11" s="9" t="inlineStr">
+      <c r="B12" s="9" t="inlineStr">
         <is>
           <t>connectivity_subscription_id</t>
         </is>
       </c>
-      <c r="C11" s="9" t="inlineStr">
-        <is>
-          <t>Subscription that holds your existing hub network (firewall, VPN).</t>
-        </is>
-      </c>
-      <c r="D11" s="9" t="inlineStr">
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>Subscription that holds your existing hub network (firewall, VPN). Only required when topology = spoke; leave blank for standalone.</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="inlineStr">
         <is>
           <t>Subscription ID (GUID).</t>
         </is>
       </c>
-      <c r="E11" s="9" t="inlineStr"/>
-      <c r="F11" s="10" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="7" t="inlineStr"/>
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>HUB NETWORK (you already have this)</t>
-        </is>
-      </c>
-      <c r="C12" s="7" t="n"/>
-      <c r="D12" s="7" t="n"/>
-      <c r="E12" s="7" t="n"/>
-      <c r="F12" s="7" t="n"/>
+      <c r="E12" s="9" t="inlineStr"/>
+      <c r="F12" s="10" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="8" t="inlineStr">
-        <is>
-          <t>4a</t>
-        </is>
-      </c>
-      <c r="B13" s="9" t="inlineStr">
-        <is>
-          <t>hub_vnet_resource_id</t>
-        </is>
-      </c>
-      <c r="C13" s="9" t="inlineStr">
-        <is>
-          <t>Full ID of your hub VNet. The wizard lists hubs found in Decision 3 and fills this in.</t>
-        </is>
-      </c>
-      <c r="D13" s="9" t="inlineStr">
-        <is>
-          <t>/subscriptions/&lt;id&gt;/resourceGroups/&lt;rg&gt;/providers/Microsoft.Network/virtualNetworks/&lt;name&gt;</t>
-        </is>
-      </c>
-      <c r="E13" s="9" t="inlineStr"/>
-      <c r="F13" s="10" t="inlineStr"/>
+      <c r="A13" s="7" t="inlineStr"/>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>HUB NETWORK (only when topology = spoke)</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="n"/>
+      <c r="D13" s="7" t="n"/>
+      <c r="E13" s="7" t="n"/>
+      <c r="F13" s="7" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
         <is>
+          <t>4a</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>hub_vnet_resource_id</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>Full ID of your hub VNet. The wizard lists hubs found in Decision 3 and fills this in. Leave blank when topology = standalone.</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="inlineStr">
+        <is>
+          <t>/subscriptions/&lt;id&gt;/resourceGroups/&lt;rg&gt;/providers/Microsoft.Network/virtualNetworks/&lt;name&gt;</t>
+        </is>
+      </c>
+      <c r="E14" s="9" t="inlineStr"/>
+      <c r="F14" s="10" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
           <t>4b</t>
         </is>
       </c>
-      <c r="B14" s="9" t="inlineStr">
+      <c r="B15" s="9" t="inlineStr">
         <is>
           <t>hub_firewall_private_ip</t>
         </is>
       </c>
-      <c r="C14" s="9" t="inlineStr">
-        <is>
-          <t>Private IP of your hub firewall. Traffic leaving the cluster routes through this.</t>
-        </is>
-      </c>
-      <c r="D14" s="9" t="inlineStr">
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>Private IP of your hub firewall. Traffic leaving the cluster routes through this. Leave blank when topology = standalone.</t>
+        </is>
+      </c>
+      <c r="D15" s="9" t="inlineStr">
         <is>
           <t>10.0.0.4</t>
         </is>
       </c>
-      <c r="E14" s="9" t="inlineStr">
+      <c r="E15" s="9" t="inlineStr">
         <is>
           <t>10.0.0.4</t>
         </is>
       </c>
-      <c r="F14" s="10" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="7" t="inlineStr"/>
-      <c r="B15" s="7" t="inlineStr">
+      <c r="F15" s="10" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr"/>
+      <c r="B16" s="7" t="inlineStr">
         <is>
           <t>SPOKE NETWORK (the new VNet for AKS)</t>
         </is>
       </c>
-      <c r="C15" s="7" t="n"/>
-      <c r="D15" s="7" t="n"/>
-      <c r="E15" s="7" t="n"/>
-      <c r="F15" s="7" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="8" t="inlineStr">
-        <is>
-          <t>5a</t>
-        </is>
-      </c>
-      <c r="B16" s="9" t="inlineStr">
-        <is>
-          <t>spoke_vnet_address_space</t>
-        </is>
-      </c>
-      <c r="C16" s="9" t="inlineStr">
-        <is>
-          <t>Address range for the new spoke VNet. Must not overlap with any other VNet.</t>
-        </is>
-      </c>
-      <c r="D16" s="9" t="inlineStr">
-        <is>
-          <t>10.10.0.0/16</t>
-        </is>
-      </c>
-      <c r="E16" s="9" t="inlineStr">
-        <is>
-          <t>10.10.0.0/16</t>
-        </is>
-      </c>
-      <c r="F16" s="10" t="inlineStr"/>
+      <c r="C16" s="7" t="n"/>
+      <c r="D16" s="7" t="n"/>
+      <c r="E16" s="7" t="n"/>
+      <c r="F16" s="7" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>5b</t>
+          <t>5a</t>
         </is>
       </c>
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>subnet_address_prefix_aks_system_nodes</t>
+          <t>spoke_vnet_address_space</t>
         </is>
       </c>
       <c r="C17" s="9" t="inlineStr">
         <is>
-          <t>Small subnet for the system node pool (runs cluster add-ons only).</t>
+          <t>Address range for the new spoke VNet. Must not overlap with any other VNet.</t>
         </is>
       </c>
       <c r="D17" s="9" t="inlineStr">
         <is>
-          <t>10.10.0.0/24  (256 addresses)</t>
+          <t>10.10.0.0/16</t>
         </is>
       </c>
       <c r="E17" s="9" t="inlineStr">
         <is>
-          <t>10.10.0.0/24</t>
+          <t>10.10.0.0/16</t>
         </is>
       </c>
       <c r="F17" s="10" t="inlineStr"/>
@@ -1099,27 +1107,27 @@
     <row r="18">
       <c r="A18" s="8" t="inlineStr">
         <is>
-          <t>5c</t>
+          <t>5b</t>
         </is>
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>subnet_address_prefix_aks_user_nodes</t>
+          <t>subnet_address_prefix_aks_system_nodes</t>
         </is>
       </c>
       <c r="C18" s="9" t="inlineStr">
         <is>
-          <t>Bigger subnet for your application workloads.</t>
+          <t>Small subnet for the system node pool (runs cluster add-ons only).</t>
         </is>
       </c>
       <c r="D18" s="9" t="inlineStr">
         <is>
-          <t>10.10.16.0/22  (1024 addresses)</t>
+          <t>10.10.0.0/24  (256 addresses)</t>
         </is>
       </c>
       <c r="E18" s="9" t="inlineStr">
         <is>
-          <t>10.10.16.0/22</t>
+          <t>10.10.0.0/24</t>
         </is>
       </c>
       <c r="F18" s="10" t="inlineStr"/>
@@ -1127,27 +1135,27 @@
     <row r="19">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>5d</t>
+          <t>5c</t>
         </is>
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>subnet_address_prefix_aks_api_server</t>
+          <t>subnet_address_prefix_aks_user_nodes</t>
         </is>
       </c>
       <c r="C19" s="9" t="inlineStr">
         <is>
-          <t>Subnet for the private Kubernetes API server.</t>
+          <t>Bigger subnet for your application workloads.</t>
         </is>
       </c>
       <c r="D19" s="9" t="inlineStr">
         <is>
-          <t>10.10.20.0/28  (Azure requires at least /28)</t>
+          <t>10.10.16.0/22  (1024 addresses)</t>
         </is>
       </c>
       <c r="E19" s="9" t="inlineStr">
         <is>
-          <t>10.10.20.0/28</t>
+          <t>10.10.16.0/22</t>
         </is>
       </c>
       <c r="F19" s="10" t="inlineStr"/>
@@ -1155,27 +1163,27 @@
     <row r="20">
       <c r="A20" s="8" t="inlineStr">
         <is>
-          <t>5e</t>
+          <t>5d</t>
         </is>
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>subnet_address_prefix_app_gateway</t>
+          <t>subnet_address_prefix_aks_api_server</t>
         </is>
       </c>
       <c r="C20" s="9" t="inlineStr">
         <is>
-          <t>Subnet for Application Gateway (web traffic in).</t>
+          <t>Subnet for the private Kubernetes API server.</t>
         </is>
       </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
-          <t>10.10.21.0/24</t>
+          <t>10.10.20.0/28  (Azure requires at least /28)</t>
         </is>
       </c>
       <c r="E20" s="9" t="inlineStr">
         <is>
-          <t>10.10.21.0/24</t>
+          <t>10.10.20.0/28</t>
         </is>
       </c>
       <c r="F20" s="10" t="inlineStr"/>
@@ -1183,27 +1191,27 @@
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>5f</t>
+          <t>5e</t>
         </is>
       </c>
       <c r="B21" s="9" t="inlineStr">
         <is>
-          <t>subnet_address_prefix_private_endpoints</t>
+          <t>subnet_address_prefix_app_gateway</t>
         </is>
       </c>
       <c r="C21" s="9" t="inlineStr">
         <is>
-          <t>Subnet for private endpoints (ACR, Key Vault, storage).</t>
+          <t>Subnet for Application Gateway (web traffic in).</t>
         </is>
       </c>
       <c r="D21" s="9" t="inlineStr">
         <is>
-          <t>10.10.22.0/24</t>
+          <t>10.10.21.0/24</t>
         </is>
       </c>
       <c r="E21" s="9" t="inlineStr">
         <is>
-          <t>10.10.22.0/24</t>
+          <t>10.10.21.0/24</t>
         </is>
       </c>
       <c r="F21" s="10" t="inlineStr"/>
@@ -1211,95 +1219,95 @@
     <row r="22">
       <c r="A22" s="8" t="inlineStr">
         <is>
+          <t>5f</t>
+        </is>
+      </c>
+      <c r="B22" s="9" t="inlineStr">
+        <is>
+          <t>subnet_address_prefix_private_endpoints</t>
+        </is>
+      </c>
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>Subnet for private endpoints (ACR, Key Vault, storage).</t>
+        </is>
+      </c>
+      <c r="D22" s="9" t="inlineStr">
+        <is>
+          <t>10.10.22.0/24</t>
+        </is>
+      </c>
+      <c r="E22" s="9" t="inlineStr">
+        <is>
+          <t>10.10.22.0/24</t>
+        </is>
+      </c>
+      <c r="F22" s="10" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="8" t="inlineStr">
+        <is>
           <t>5g</t>
         </is>
       </c>
-      <c r="B22" s="9" t="inlineStr">
+      <c r="B23" s="9" t="inlineStr">
         <is>
           <t>subnet_address_prefix_ingress</t>
         </is>
       </c>
-      <c r="C22" s="9" t="inlineStr">
+      <c r="C23" s="9" t="inlineStr">
         <is>
           <t>Subnet for the internal load balancer that fronts your apps.</t>
         </is>
       </c>
-      <c r="D22" s="9" t="inlineStr">
+      <c r="D23" s="9" t="inlineStr">
         <is>
           <t>10.10.23.0/24</t>
         </is>
       </c>
-      <c r="E22" s="9" t="inlineStr">
+      <c r="E23" s="9" t="inlineStr">
         <is>
           <t>10.10.23.0/24</t>
         </is>
       </c>
-      <c r="F22" s="10" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="7" t="inlineStr"/>
-      <c r="B23" s="7" t="inlineStr">
+      <c r="F23" s="10" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr"/>
+      <c r="B24" s="7" t="inlineStr">
         <is>
           <t>CLUSTER SETTINGS</t>
         </is>
       </c>
-      <c r="C23" s="7" t="n"/>
-      <c r="D23" s="7" t="n"/>
-      <c r="E23" s="7" t="n"/>
-      <c r="F23" s="7" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="8" t="inlineStr">
-        <is>
-          <t>6a</t>
-        </is>
-      </c>
-      <c r="B24" s="9" t="inlineStr">
-        <is>
-          <t>kubernetes_version</t>
-        </is>
-      </c>
-      <c r="C24" s="9" t="inlineStr">
-        <is>
-          <t>Kubernetes version. The wizard lists the latest versions available in your region — usually just pick the top one.</t>
-        </is>
-      </c>
-      <c r="D24" s="9" t="inlineStr">
-        <is>
-          <t>Example: 1.33.6</t>
-        </is>
-      </c>
-      <c r="E24" s="9" t="inlineStr">
-        <is>
-          <t>(latest in region)</t>
-        </is>
-      </c>
-      <c r="F24" s="10" t="inlineStr"/>
+      <c r="C24" s="7" t="n"/>
+      <c r="D24" s="7" t="n"/>
+      <c r="E24" s="7" t="n"/>
+      <c r="F24" s="7" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="8" t="inlineStr">
         <is>
-          <t>6b</t>
+          <t>6a</t>
         </is>
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>aks_sku_tier</t>
+          <t>kubernetes_version</t>
         </is>
       </c>
       <c r="C25" s="9" t="inlineStr">
         <is>
-          <t>Cluster pricing tier. Standard is fine for most clusters; Premium adds long-term support and is required for regulated scenarios.</t>
+          <t>Kubernetes version. The wizard lists the latest versions available in your region — usually just pick the top one.</t>
         </is>
       </c>
       <c r="D25" s="9" t="inlineStr">
         <is>
-          <t>Free | Standard | Premium</t>
+          <t>Example: 1.33.6</t>
         </is>
       </c>
       <c r="E25" s="9" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>(latest in region)</t>
         </is>
       </c>
       <c r="F25" s="10" t="inlineStr"/>
@@ -1307,164 +1315,164 @@
     <row r="26">
       <c r="A26" s="8" t="inlineStr">
         <is>
+          <t>6b</t>
+        </is>
+      </c>
+      <c r="B26" s="9" t="inlineStr">
+        <is>
+          <t>aks_sku_tier</t>
+        </is>
+      </c>
+      <c r="C26" s="9" t="inlineStr">
+        <is>
+          <t>Cluster pricing tier. Standard is fine for most clusters; Premium adds long-term support and is required for regulated scenarios.</t>
+        </is>
+      </c>
+      <c r="D26" s="9" t="inlineStr">
+        <is>
+          <t>Free | Standard | Premium</t>
+        </is>
+      </c>
+      <c r="E26" s="9" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="F26" s="10" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="8" t="inlineStr">
+        <is>
           <t>6c</t>
         </is>
       </c>
-      <c r="B26" s="9" t="inlineStr">
+      <c r="B27" s="9" t="inlineStr">
         <is>
           <t>aks_private_cluster</t>
         </is>
       </c>
-      <c r="C26" s="9" t="inlineStr">
+      <c r="C27" s="9" t="inlineStr">
         <is>
           <t>Hide the Kubernetes API behind your private network (no public endpoint).</t>
         </is>
       </c>
-      <c r="D26" s="9" t="inlineStr">
+      <c r="D27" s="9" t="inlineStr">
         <is>
           <t>true  (recommended)
 false (only for internet-facing demos)</t>
         </is>
       </c>
-      <c r="E26" s="9" t="inlineStr">
+      <c r="E27" s="9" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="F26" s="10" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="8" t="inlineStr">
+      <c r="F27" s="10" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="8" t="inlineStr">
         <is>
           <t>6d</t>
         </is>
       </c>
-      <c r="B27" s="9" t="inlineStr">
+      <c r="B28" s="9" t="inlineStr">
         <is>
           <t>aks_admin_group_object_ids</t>
         </is>
       </c>
-      <c r="C27" s="9" t="inlineStr">
+      <c r="C28" s="9" t="inlineStr">
         <is>
           <t>Entra ID group(s) whose members can manage the cluster. Create the group in Entra ID first and paste the object ID.</t>
         </is>
       </c>
-      <c r="D27" s="9" t="inlineStr">
+      <c r="D28" s="9" t="inlineStr">
         <is>
           <t>["00000000-0000-0000-0000-000000000000"]</t>
         </is>
       </c>
-      <c r="E27" s="9" t="inlineStr">
+      <c r="E28" s="9" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="F27" s="10" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="7" t="inlineStr"/>
-      <c r="B28" s="7" t="inlineStr">
+      <c r="F28" s="10" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="inlineStr"/>
+      <c r="B29" s="7" t="inlineStr">
         <is>
           <t>WHERE STATE LIVES</t>
         </is>
       </c>
-      <c r="C28" s="7" t="n"/>
-      <c r="D28" s="7" t="n"/>
-      <c r="E28" s="7" t="n"/>
-      <c r="F28" s="7" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="8" t="inlineStr">
+      <c r="C29" s="7" t="n"/>
+      <c r="D29" s="7" t="n"/>
+      <c r="E29" s="7" t="n"/>
+      <c r="F29" s="7" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="8" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B29" s="9" t="inlineStr">
+      <c r="B30" s="9" t="inlineStr">
         <is>
           <t>bootstrap_subscription_id</t>
         </is>
       </c>
-      <c r="C29" s="9" t="inlineStr">
+      <c r="C30" s="9" t="inlineStr">
         <is>
           <t>Subscription that holds the Terraform state storage and the runner. Usually the same as Decision 2.</t>
         </is>
       </c>
-      <c r="D29" s="9" t="inlineStr">
+      <c r="D30" s="9" t="inlineStr">
         <is>
           <t>Subscription ID (GUID), or leave blank.</t>
         </is>
       </c>
-      <c r="E29" s="9" t="inlineStr">
+      <c r="E30" s="9" t="inlineStr">
         <is>
           <t>(same as Decision 2)</t>
         </is>
       </c>
-      <c r="F29" s="10" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="7" t="inlineStr"/>
-      <c r="B30" s="7" t="inlineStr">
+      <c r="F30" s="10" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="7" t="inlineStr"/>
+      <c r="B31" s="7" t="inlineStr">
         <is>
           <t>NAMING</t>
         </is>
       </c>
-      <c r="C30" s="7" t="n"/>
-      <c r="D30" s="7" t="n"/>
-      <c r="E30" s="7" t="n"/>
-      <c r="F30" s="7" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="8" t="inlineStr">
-        <is>
-          <t>8a</t>
-        </is>
-      </c>
-      <c r="B31" s="9" t="inlineStr">
-        <is>
-          <t>service_name</t>
-        </is>
-      </c>
-      <c r="C31" s="9" t="inlineStr">
-        <is>
-          <t>Short name of your workload. Used in every resource name.</t>
-        </is>
-      </c>
-      <c r="D31" s="9" t="inlineStr">
-        <is>
-          <t>aksapplz, payments, shop</t>
-        </is>
-      </c>
-      <c r="E31" s="9" t="inlineStr">
-        <is>
-          <t>aksapplz</t>
-        </is>
-      </c>
-      <c r="F31" s="10" t="inlineStr"/>
+      <c r="C31" s="7" t="n"/>
+      <c r="D31" s="7" t="n"/>
+      <c r="E31" s="7" t="n"/>
+      <c r="F31" s="7" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="8" t="inlineStr">
         <is>
-          <t>8b</t>
+          <t>8a</t>
         </is>
       </c>
       <c r="B32" s="9" t="inlineStr">
         <is>
-          <t>environment_name</t>
+          <t>service_name</t>
         </is>
       </c>
       <c r="C32" s="9" t="inlineStr">
         <is>
-          <t>Environment label. Used in every resource name.</t>
+          <t>Short name of your workload. Used in every resource name.</t>
         </is>
       </c>
       <c r="D32" s="9" t="inlineStr">
         <is>
-          <t>prod, dev, test</t>
+          <t>aksapplz, payments, shop</t>
         </is>
       </c>
       <c r="E32" s="9" t="inlineStr">
         <is>
-          <t>prod</t>
+          <t>aksapplz</t>
         </is>
       </c>
       <c r="F32" s="10" t="inlineStr"/>
@@ -1472,160 +1480,160 @@
     <row r="33">
       <c r="A33" s="8" t="inlineStr">
         <is>
+          <t>8b</t>
+        </is>
+      </c>
+      <c r="B33" s="9" t="inlineStr">
+        <is>
+          <t>environment_name</t>
+        </is>
+      </c>
+      <c r="C33" s="9" t="inlineStr">
+        <is>
+          <t>Environment label. Used in every resource name.</t>
+        </is>
+      </c>
+      <c r="D33" s="9" t="inlineStr">
+        <is>
+          <t>prod, dev, test</t>
+        </is>
+      </c>
+      <c r="E33" s="9" t="inlineStr">
+        <is>
+          <t>prod</t>
+        </is>
+      </c>
+      <c r="F33" s="10" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="8" t="inlineStr">
+        <is>
           <t>8c</t>
         </is>
       </c>
-      <c r="B33" s="9" t="inlineStr">
+      <c r="B34" s="9" t="inlineStr">
         <is>
           <t>postfix_number</t>
         </is>
       </c>
-      <c r="C33" s="9" t="inlineStr">
+      <c r="C34" s="9" t="inlineStr">
         <is>
           <t>Number that makes resource names unique. Bump this if you redeploy.</t>
         </is>
       </c>
-      <c r="D33" s="9" t="inlineStr">
+      <c r="D34" s="9" t="inlineStr">
         <is>
           <t>1, 2, 3 ...</t>
         </is>
       </c>
-      <c r="E33" s="9" t="inlineStr">
+      <c r="E34" s="9" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F33" s="10" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="7" t="inlineStr"/>
-      <c r="B34" s="7" t="inlineStr">
+      <c r="F34" s="10" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="7" t="inlineStr"/>
+      <c r="B35" s="7" t="inlineStr">
         <is>
           <t>RUNNERS</t>
         </is>
       </c>
-      <c r="C34" s="7" t="n"/>
-      <c r="D34" s="7" t="n"/>
-      <c r="E34" s="7" t="n"/>
-      <c r="F34" s="7" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="8" t="inlineStr">
+      <c r="C35" s="7" t="n"/>
+      <c r="D35" s="7" t="n"/>
+      <c r="E35" s="7" t="n"/>
+      <c r="F35" s="7" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="8" t="inlineStr">
         <is>
           <t>9a</t>
         </is>
       </c>
-      <c r="B35" s="9" t="inlineStr">
+      <c r="B36" s="9" t="inlineStr">
         <is>
           <t>use_self_hosted_runners</t>
         </is>
       </c>
-      <c r="C35" s="9" t="inlineStr">
+      <c r="C36" s="9" t="inlineStr">
         <is>
           <t>Run GitHub Actions on a small container inside Azure (needed for private clusters so CI/CD can reach the API).</t>
         </is>
       </c>
-      <c r="D35" s="9" t="inlineStr">
+      <c r="D36" s="9" t="inlineStr">
         <is>
           <t>true  (required for private clusters)
 false (use GitHub-hosted runners)</t>
         </is>
       </c>
-      <c r="E35" s="9" t="inlineStr">
+      <c r="E36" s="9" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="F35" s="10" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="8" t="inlineStr">
+      <c r="F36" s="10" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="8" t="inlineStr">
         <is>
           <t>9b</t>
         </is>
       </c>
-      <c r="B36" s="9" t="inlineStr">
+      <c r="B37" s="9" t="inlineStr">
         <is>
           <t>use_private_networking</t>
         </is>
       </c>
-      <c r="C36" s="9" t="inlineStr">
+      <c r="C37" s="9" t="inlineStr">
         <is>
           <t>Put the runner and Container Registry on a private network. Recommended.</t>
         </is>
       </c>
-      <c r="D36" s="9" t="inlineStr">
+      <c r="D37" s="9" t="inlineStr">
         <is>
           <t>true  (recommended)
 false (public networking, ACR Basic)</t>
         </is>
       </c>
-      <c r="E36" s="9" t="inlineStr">
+      <c r="E37" s="9" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="F36" s="10" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="7" t="inlineStr"/>
-      <c r="B37" s="7" t="inlineStr">
+      <c r="F37" s="10" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="7" t="inlineStr"/>
+      <c r="B38" s="7" t="inlineStr">
         <is>
           <t>GITHUB</t>
         </is>
       </c>
-      <c r="C37" s="7" t="n"/>
-      <c r="D37" s="7" t="n"/>
-      <c r="E37" s="7" t="n"/>
-      <c r="F37" s="7" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="8" t="inlineStr">
-        <is>
-          <t>10a</t>
-        </is>
-      </c>
-      <c r="B38" s="9" t="inlineStr">
-        <is>
-          <t>github_personal_access_token</t>
-        </is>
-      </c>
-      <c r="C38" s="9" t="inlineStr">
-        <is>
-          <t>GitHub token used to create the repos. You will be prompted (input is hidden); you do NOT need to put it here.</t>
-        </is>
-      </c>
-      <c r="D38" s="9" t="inlineStr">
-        <is>
-          <t>Scopes needed: repo, workflow, admin:org (Read &amp; Write members).</t>
-        </is>
-      </c>
-      <c r="E38" s="9" t="inlineStr">
-        <is>
-          <t>(prompted in wizard)</t>
-        </is>
-      </c>
-      <c r="F38" s="10" t="inlineStr"/>
+      <c r="C38" s="7" t="n"/>
+      <c r="D38" s="7" t="n"/>
+      <c r="E38" s="7" t="n"/>
+      <c r="F38" s="7" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="8" t="inlineStr">
         <is>
-          <t>10b</t>
+          <t>10a</t>
         </is>
       </c>
       <c r="B39" s="9" t="inlineStr">
         <is>
-          <t>github_runners_personal_access_token</t>
+          <t>github_personal_access_token</t>
         </is>
       </c>
       <c r="C39" s="9" t="inlineStr">
         <is>
-          <t>Second token used to register the self-hosted runner. Also prompted; only asked when 9a is true.</t>
+          <t>GitHub token used to create the repos. You will be prompted (input is hidden); you do NOT need to put it here.</t>
         </is>
       </c>
       <c r="D39" s="9" t="inlineStr">
         <is>
-          <t>Scope needed: admin:org (full).</t>
+          <t>Scopes needed: repo, workflow, admin:org (Read &amp; Write members).</t>
         </is>
       </c>
       <c r="E39" s="9" t="inlineStr">
@@ -1638,109 +1646,109 @@
     <row r="40">
       <c r="A40" s="8" t="inlineStr">
         <is>
-          <t>10c</t>
+          <t>10b</t>
         </is>
       </c>
       <c r="B40" s="9" t="inlineStr">
         <is>
-          <t>github_organization_name</t>
+          <t>github_runners_personal_access_token</t>
         </is>
       </c>
       <c r="C40" s="9" t="inlineStr">
         <is>
-          <t>GitHub organisation name where the two repos will be created.</t>
+          <t>Second token used to register the self-hosted runner. Also prompted; only asked when 9a is true.</t>
         </is>
       </c>
       <c r="D40" s="9" t="inlineStr">
         <is>
-          <t>contoso</t>
-        </is>
-      </c>
-      <c r="E40" s="9" t="inlineStr"/>
+          <t>Scope needed: admin:org (full).</t>
+        </is>
+      </c>
+      <c r="E40" s="9" t="inlineStr">
+        <is>
+          <t>(prompted in wizard)</t>
+        </is>
+      </c>
       <c r="F40" s="10" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="8" t="inlineStr">
         <is>
+          <t>10c</t>
+        </is>
+      </c>
+      <c r="B41" s="9" t="inlineStr">
+        <is>
+          <t>github_organization_name</t>
+        </is>
+      </c>
+      <c r="C41" s="9" t="inlineStr">
+        <is>
+          <t>GitHub organisation name where the two repos will be created.</t>
+        </is>
+      </c>
+      <c r="D41" s="9" t="inlineStr">
+        <is>
+          <t>contoso</t>
+        </is>
+      </c>
+      <c r="E41" s="9" t="inlineStr"/>
+      <c r="F41" s="10" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="8" t="inlineStr">
+        <is>
           <t>10d</t>
         </is>
       </c>
-      <c r="B41" s="9" t="inlineStr">
+      <c r="B42" s="9" t="inlineStr">
         <is>
           <t>apply_approvers</t>
         </is>
       </c>
-      <c r="C41" s="9" t="inlineStr">
+      <c r="C42" s="9" t="inlineStr">
         <is>
           <t>GitHub usernames who must approve before a deployment goes live.</t>
         </is>
       </c>
-      <c r="D41" s="9" t="inlineStr">
+      <c r="D42" s="9" t="inlineStr">
         <is>
           <t>["alice", "bob"]</t>
         </is>
       </c>
-      <c r="E41" s="9" t="inlineStr">
+      <c r="E42" s="9" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="F41" s="10" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="7" t="inlineStr"/>
-      <c r="B42" s="7" t="inlineStr">
+      <c r="F42" s="10" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="7" t="inlineStr"/>
+      <c r="B43" s="7" t="inlineStr">
         <is>
           <t>ADD-ONS (turn things on or off)</t>
         </is>
       </c>
-      <c r="C42" s="7" t="n"/>
-      <c r="D42" s="7" t="n"/>
-      <c r="E42" s="7" t="n"/>
-      <c r="F42" s="7" t="n"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="8" t="inlineStr">
-        <is>
-          <t>11a</t>
-        </is>
-      </c>
-      <c r="B43" s="9" t="inlineStr">
-        <is>
-          <t>enable_defender</t>
-        </is>
-      </c>
-      <c r="C43" s="9" t="inlineStr">
-        <is>
-          <t>Scans the cluster for security threats in real time.</t>
-        </is>
-      </c>
-      <c r="D43" s="9" t="inlineStr">
-        <is>
-          <t>true | false</t>
-        </is>
-      </c>
-      <c r="E43" s="9" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="F43" s="10" t="inlineStr"/>
+      <c r="C43" s="7" t="n"/>
+      <c r="D43" s="7" t="n"/>
+      <c r="E43" s="7" t="n"/>
+      <c r="F43" s="7" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="8" t="inlineStr">
         <is>
-          <t>11b</t>
+          <t>11a</t>
         </is>
       </c>
       <c r="B44" s="9" t="inlineStr">
         <is>
-          <t>enable_workload_identity</t>
+          <t>enable_defender</t>
         </is>
       </c>
       <c r="C44" s="9" t="inlineStr">
         <is>
-          <t>Lets pods talk to Azure services without passwords.</t>
+          <t>Scans the cluster for security threats in real time.</t>
         </is>
       </c>
       <c r="D44" s="9" t="inlineStr">
@@ -1758,17 +1766,17 @@
     <row r="45">
       <c r="A45" s="8" t="inlineStr">
         <is>
-          <t>11c</t>
+          <t>11b</t>
         </is>
       </c>
       <c r="B45" s="9" t="inlineStr">
         <is>
-          <t>enable_azure_policy</t>
+          <t>enable_workload_identity</t>
         </is>
       </c>
       <c r="C45" s="9" t="inlineStr">
         <is>
-          <t>Enforces rules in the cluster (e.g. block containers running as root).</t>
+          <t>Lets pods talk to Azure services without passwords.</t>
         </is>
       </c>
       <c r="D45" s="9" t="inlineStr">
@@ -1786,17 +1794,17 @@
     <row r="46">
       <c r="A46" s="8" t="inlineStr">
         <is>
-          <t>11d</t>
+          <t>11c</t>
         </is>
       </c>
       <c r="B46" s="9" t="inlineStr">
         <is>
-          <t>enable_prometheus</t>
+          <t>enable_azure_policy</t>
         </is>
       </c>
       <c r="C46" s="9" t="inlineStr">
         <is>
-          <t>Collects cluster metrics.</t>
+          <t>Enforces rules in the cluster (e.g. block containers running as root).</t>
         </is>
       </c>
       <c r="D46" s="9" t="inlineStr">
@@ -1814,17 +1822,17 @@
     <row r="47">
       <c r="A47" s="8" t="inlineStr">
         <is>
-          <t>11e</t>
+          <t>11d</t>
         </is>
       </c>
       <c r="B47" s="9" t="inlineStr">
         <is>
-          <t>enable_grafana</t>
+          <t>enable_prometheus</t>
         </is>
       </c>
       <c r="C47" s="9" t="inlineStr">
         <is>
-          <t>Dashboards for the metrics above.</t>
+          <t>Collects cluster metrics.</t>
         </is>
       </c>
       <c r="D47" s="9" t="inlineStr">
@@ -1842,17 +1850,17 @@
     <row r="48">
       <c r="A48" s="8" t="inlineStr">
         <is>
-          <t>11f</t>
+          <t>11e</t>
         </is>
       </c>
       <c r="B48" s="9" t="inlineStr">
         <is>
-          <t>enable_app_gateway</t>
+          <t>enable_grafana</t>
         </is>
       </c>
       <c r="C48" s="9" t="inlineStr">
         <is>
-          <t>Application Gateway with a Web Application Firewall in front of the cluster.</t>
+          <t>Dashboards for the metrics above.</t>
         </is>
       </c>
       <c r="D48" s="9" t="inlineStr">
@@ -1870,17 +1878,17 @@
     <row r="49">
       <c r="A49" s="8" t="inlineStr">
         <is>
-          <t>11g</t>
+          <t>11f</t>
         </is>
       </c>
       <c r="B49" s="9" t="inlineStr">
         <is>
-          <t>enable_keda</t>
+          <t>enable_app_gateway</t>
         </is>
       </c>
       <c r="C49" s="9" t="inlineStr">
         <is>
-          <t>Auto-scales pods based on events (queue length, HTTP requests, etc.).</t>
+          <t>Application Gateway with a Web Application Firewall in front of the cluster.</t>
         </is>
       </c>
       <c r="D49" s="9" t="inlineStr">
@@ -1898,17 +1906,17 @@
     <row r="50">
       <c r="A50" s="8" t="inlineStr">
         <is>
-          <t>11h</t>
+          <t>11g</t>
         </is>
       </c>
       <c r="B50" s="9" t="inlineStr">
         <is>
-          <t>enable_vpa</t>
+          <t>enable_keda</t>
         </is>
       </c>
       <c r="C50" s="9" t="inlineStr">
         <is>
-          <t>Auto-adjusts CPU and memory requests for pods.</t>
+          <t>Auto-scales pods based on events (queue length, HTTP requests, etc.).</t>
         </is>
       </c>
       <c r="D50" s="9" t="inlineStr">
@@ -1918,7 +1926,7 @@
       </c>
       <c r="E50" s="9" t="inlineStr">
         <is>
-          <t>false  (true for regulated / multi-region)</t>
+          <t>true</t>
         </is>
       </c>
       <c r="F50" s="10" t="inlineStr"/>
@@ -1926,17 +1934,17 @@
     <row r="51">
       <c r="A51" s="8" t="inlineStr">
         <is>
-          <t>11i</t>
+          <t>11h</t>
         </is>
       </c>
       <c r="B51" s="9" t="inlineStr">
         <is>
-          <t>enable_node_auto_provisioning</t>
+          <t>enable_vpa</t>
         </is>
       </c>
       <c r="C51" s="9" t="inlineStr">
         <is>
-          <t>Cluster creates new node sizes on demand instead of using fixed pools.</t>
+          <t>Auto-adjusts CPU and memory requests for pods.</t>
         </is>
       </c>
       <c r="D51" s="9" t="inlineStr">
@@ -1946,7 +1954,7 @@
       </c>
       <c r="E51" s="9" t="inlineStr">
         <is>
-          <t>false  (true for multi-region)</t>
+          <t>false  (true for regulated / multi-region)</t>
         </is>
       </c>
       <c r="F51" s="10" t="inlineStr"/>
@@ -1954,17 +1962,17 @@
     <row r="52">
       <c r="A52" s="8" t="inlineStr">
         <is>
-          <t>11j</t>
+          <t>11i</t>
         </is>
       </c>
       <c r="B52" s="9" t="inlineStr">
         <is>
-          <t>enable_istio</t>
+          <t>enable_node_auto_provisioning</t>
         </is>
       </c>
       <c r="C52" s="9" t="inlineStr">
         <is>
-          <t>Service mesh with mTLS between pods. Needed for some compliance standards.</t>
+          <t>Cluster creates new node sizes on demand instead of using fixed pools.</t>
         </is>
       </c>
       <c r="D52" s="9" t="inlineStr">
@@ -1974,7 +1982,7 @@
       </c>
       <c r="E52" s="9" t="inlineStr">
         <is>
-          <t>false  (true for regulated)</t>
+          <t>false  (true for multi-region)</t>
         </is>
       </c>
       <c r="F52" s="10" t="inlineStr"/>
@@ -1982,17 +1990,17 @@
     <row r="53">
       <c r="A53" s="8" t="inlineStr">
         <is>
-          <t>11k</t>
+          <t>11j</t>
         </is>
       </c>
       <c r="B53" s="9" t="inlineStr">
         <is>
-          <t>enable_flux</t>
+          <t>enable_istio</t>
         </is>
       </c>
       <c r="C53" s="9" t="inlineStr">
         <is>
-          <t>GitOps — the cluster pulls its configuration from a Git repo.</t>
+          <t>Service mesh with mTLS between pods. Needed for some compliance standards.</t>
         </is>
       </c>
       <c r="D53" s="9" t="inlineStr">
@@ -2002,7 +2010,7 @@
       </c>
       <c r="E53" s="9" t="inlineStr">
         <is>
-          <t>false  (true for multi-region)</t>
+          <t>false  (true for regulated)</t>
         </is>
       </c>
       <c r="F53" s="10" t="inlineStr"/>
@@ -2010,17 +2018,17 @@
     <row r="54">
       <c r="A54" s="8" t="inlineStr">
         <is>
-          <t>11l</t>
+          <t>11k</t>
         </is>
       </c>
       <c r="B54" s="9" t="inlineStr">
         <is>
-          <t>enable_dapr</t>
+          <t>enable_flux</t>
         </is>
       </c>
       <c r="C54" s="9" t="inlineStr">
         <is>
-          <t>Building blocks for microservices (pub/sub, state, secrets).</t>
+          <t>GitOps — the cluster pulls its configuration from a Git repo.</t>
         </is>
       </c>
       <c r="D54" s="9" t="inlineStr">
@@ -2030,7 +2038,7 @@
       </c>
       <c r="E54" s="9" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>false  (true for multi-region)</t>
         </is>
       </c>
       <c r="F54" s="10" t="inlineStr"/>
@@ -2038,17 +2046,17 @@
     <row r="55">
       <c r="A55" s="8" t="inlineStr">
         <is>
-          <t>11m</t>
+          <t>11l</t>
         </is>
       </c>
       <c r="B55" s="9" t="inlineStr">
         <is>
-          <t>enable_fips</t>
+          <t>enable_dapr</t>
         </is>
       </c>
       <c r="C55" s="9" t="inlineStr">
         <is>
-          <t>Use FIPS 140-2 compliant node OS (US Federal / PCI).</t>
+          <t>Building blocks for microservices (pub/sub, state, secrets).</t>
         </is>
       </c>
       <c r="D55" s="9" t="inlineStr">
@@ -2058,7 +2066,7 @@
       </c>
       <c r="E55" s="9" t="inlineStr">
         <is>
-          <t>false  (true for regulated)</t>
+          <t>false</t>
         </is>
       </c>
       <c r="F55" s="10" t="inlineStr"/>
@@ -2066,17 +2074,17 @@
     <row r="56">
       <c r="A56" s="8" t="inlineStr">
         <is>
-          <t>11n</t>
+          <t>11m</t>
         </is>
       </c>
       <c r="B56" s="9" t="inlineStr">
         <is>
-          <t>enable_backup</t>
+          <t>enable_fips</t>
         </is>
       </c>
       <c r="C56" s="9" t="inlineStr">
         <is>
-          <t>Azure Backup for cluster resources and persistent volumes.</t>
+          <t>Use FIPS 140-2 compliant node OS (US Federal / PCI).</t>
         </is>
       </c>
       <c r="D56" s="9" t="inlineStr">
@@ -2086,7 +2094,7 @@
       </c>
       <c r="E56" s="9" t="inlineStr">
         <is>
-          <t>false  (true for regulated / multi-region)</t>
+          <t>false  (true for regulated)</t>
         </is>
       </c>
       <c r="F56" s="10" t="inlineStr"/>
@@ -2094,63 +2102,91 @@
     <row r="57">
       <c r="A57" s="8" t="inlineStr">
         <is>
+          <t>11n</t>
+        </is>
+      </c>
+      <c r="B57" s="9" t="inlineStr">
+        <is>
+          <t>enable_backup</t>
+        </is>
+      </c>
+      <c r="C57" s="9" t="inlineStr">
+        <is>
+          <t>Azure Backup for cluster resources and persistent volumes.</t>
+        </is>
+      </c>
+      <c r="D57" s="9" t="inlineStr">
+        <is>
+          <t>true | false</t>
+        </is>
+      </c>
+      <c r="E57" s="9" t="inlineStr">
+        <is>
+          <t>false  (true for regulated / multi-region)</t>
+        </is>
+      </c>
+      <c r="F57" s="10" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="8" t="inlineStr">
+        <is>
           <t>11o</t>
         </is>
       </c>
-      <c r="B57" s="9" t="inlineStr">
+      <c r="B58" s="9" t="inlineStr">
         <is>
           <t>enable_cost_analysis</t>
         </is>
       </c>
-      <c r="C57" s="9" t="inlineStr">
+      <c r="C58" s="9" t="inlineStr">
         <is>
           <t>Cost breakdown per namespace in the Azure portal.</t>
         </is>
       </c>
-      <c r="D57" s="9" t="inlineStr">
+      <c r="D58" s="9" t="inlineStr">
         <is>
           <t>true | false</t>
         </is>
       </c>
-      <c r="E57" s="9" t="inlineStr">
+      <c r="E58" s="9" t="inlineStr">
         <is>
           <t>false  (true for regulated)</t>
         </is>
       </c>
-      <c r="F57" s="10" t="inlineStr"/>
+      <c r="F58" s="10" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B30:F30"/>
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B34:F34"/>
-    <mergeCell ref="B15:F15"/>
+    <mergeCell ref="B43:F43"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B24:F24"/>
+    <mergeCell ref="B16:F16"/>
+    <mergeCell ref="B38:F38"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="B28:F28"/>
-    <mergeCell ref="B42:F42"/>
     <mergeCell ref="B5:F5"/>
-    <mergeCell ref="B37:F37"/>
-    <mergeCell ref="B23:F23"/>
-    <mergeCell ref="B8:F8"/>
+    <mergeCell ref="B31:F31"/>
+    <mergeCell ref="B9:F9"/>
+    <mergeCell ref="B13:F13"/>
+    <mergeCell ref="B35:F35"/>
   </mergeCells>
-  <dataValidations count="20">
+  <dataValidations count="21">
     <dataValidation sqref="F6" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"single_region_baseline,multi_region_baseline,single_region_regulated,multi_region_regulated"</formula1>
     </dataValidation>
-    <dataValidation sqref="F25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F8" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"spoke,standalone"</formula1>
+    </dataValidation>
+    <dataValidation sqref="F26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Free,Standard,Premium"</formula1>
     </dataValidation>
-    <dataValidation sqref="F26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"true,false"</formula1>
-    </dataValidation>
-    <dataValidation sqref="F35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"true,false"</formula1>
     </dataValidation>
     <dataValidation sqref="F36" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"true,false"</formula1>
     </dataValidation>
-    <dataValidation sqref="F43" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F37" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"true,false"</formula1>
     </dataValidation>
     <dataValidation sqref="F44" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
@@ -2195,6 +2231,9 @@
     <dataValidation sqref="F57" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"true,false"</formula1>
     </dataValidation>
+    <dataValidation sqref="F58" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"true,false"</formula1>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/config/checklist.xlsx
+++ b/config/checklist.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -54,6 +54,12 @@
     <font>
       <name val="Segoe UI"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="000563C1"/>
+      <sz val="10"/>
+      <u val="single"/>
     </font>
   </fonts>
   <fills count="5">
@@ -108,7 +114,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -134,6 +140,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -501,7 +510,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A40"/>
+  <dimension ref="A1:A42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -561,65 +570,69 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   - Pick a topology (row 0c) — 'spoke' if you already have an ALZ hub, 'hub_and_spoke' to create a new hub this run, or 'standalone' for an isolated subscription. Standalone skips Decisions 3 and 4.</t>
+          <t xml:space="preserve">   - Use the 'Reference' column links to read the Microsoft Learn docs for any setting.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   - Don't put GitHub tokens in the workbook. The wizard asks for them with hidden input.</t>
+          <t xml:space="preserve">   - Use the 'Comments' column (yellow) to record why you chose a value — handy for your team and auditors.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr"/>
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - Pick a topology (row 0c) — 'spoke' if you already have an ALZ hub, 'hub_and_spoke' to create a new hub this run, or 'standalone' for an isolated subscription. Standalone skips Decisions 3 and 4.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">   - Don't put GitHub tokens in the workbook. The wizard asks for them with hidden input.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
           <t>2. Open 'Advanced Cluster Settings' only if you need to change cluster sizing, networking,</t>
         </is>
       </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   or upgrade behaviour. Most teams leave this tab alone.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>3. Run the wizard and use the workbook as your reference:</t>
+          <t xml:space="preserve">   or upgrade behaviour. Most teams leave this tab alone.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">       Import-Module .\ALZ.AKS\ALZ.AKS.psd1 -Force</t>
-        </is>
-      </c>
+      <c r="A17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>3. Run the wizard and use the workbook as your reference:</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">       Import-Module .\ALZ.AKS\ALZ.AKS.psd1 -Force</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">       Deploy-AKSLandingZone</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>What the wizard does</t>
         </is>
       </c>
     </row>
@@ -627,33 +640,33 @@
       <c r="A21" s="2" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>Phase A — asks you the questions in this workbook and writes config files.</t>
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>What the wizard does</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>Phase B — creates the Azure resources, GitHub repos, runner, and pushes the Terraform code.</t>
-        </is>
-      </c>
+      <c r="A23" s="2" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>Phase A — asks you the questions in this workbook and writes config files.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>Phase B — creates the Azure resources, GitHub repos, runner, and pushes the Terraform code.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
           <t>Phase C — your PRs in the new GitHub repo run plan/apply and deploy the cluster.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="3" t="inlineStr">
-        <is>
-          <t>GitHub tokens — scopes you need</t>
         </is>
       </c>
     </row>
@@ -661,26 +674,26 @@
       <c r="A27" s="2" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>GitHub tokens — scopes you need</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>Main token (always):    repo, workflow, admin:org (Members Read &amp; Write)</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>Runner token (if 9a is true):  admin:org (full)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="3" t="inlineStr">
-        <is>
-          <t>Resource names you will see</t>
         </is>
       </c>
     </row>
@@ -688,56 +701,66 @@
       <c r="A32" s="2" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>Pattern: {service}-{env}-{region-short}-{number}</t>
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>Resource names you will see</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>Example with defaults (aksapplz, prod, swedencentral, 1):</t>
-        </is>
-      </c>
+      <c r="A34" s="2" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Resource group for state:     rg-aksapplz-prod-sc-001</t>
+          <t>Pattern: {service}-{env}-{region-short}-{number}</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Resource group for identity:  rg-aksapplz-prod-sc-identity</t>
+          <t>Example with defaults (aksapplz, prod, swedencentral, 1):</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Resource group for runner:    rg-aksapplz-prod-sc-agents     (only with self-hosted runners)</t>
+          <t xml:space="preserve">  Resource group for state:     rg-aksapplz-prod-sc-001</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  GitHub repository:            aksapplz-prod</t>
+          <t xml:space="preserve">  Resource group for identity:  rg-aksapplz-prod-sc-identity</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  GitHub templates repo:        aksapplz-prod-templates</t>
+          <t xml:space="preserve">  Resource group for runner:    rg-aksapplz-prod-sc-agents     (only with self-hosted runners)</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  GitHub repository:            aksapplz-prod</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  GitHub templates repo:        aksapplz-prod-templates</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">  Approver team:                aksapplz-prod-approvers</t>
         </is>
@@ -754,7 +777,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F66"/>
+  <dimension ref="A1:H66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -763,6 +786,8 @@
     <col width="55" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
     <col width="28" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -775,7 +800,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>Fill in the yellow column. Each row matches one question the wizard will ask you.</t>
+          <t>Fill in the yellow columns. Each row matches one question the wizard will ask you. Use 'Reference' for the Microsoft Learn docs and 'Comments' for your own notes.</t>
         </is>
       </c>
     </row>
@@ -808,6 +833,16 @@
       <c r="F4" s="6" t="inlineStr">
         <is>
           <t>Your value</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>Comments</t>
         </is>
       </c>
     </row>
@@ -822,6 +857,8 @@
       <c r="D5" s="7" t="n"/>
       <c r="E5" s="7" t="n"/>
       <c r="F5" s="7" t="n"/>
+      <c r="G5" s="7" t="n"/>
+      <c r="H5" s="7" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="8" t="inlineStr">
@@ -853,6 +890,12 @@
         </is>
       </c>
       <c r="F6" s="10" t="inlineStr"/>
+      <c r="G6" s="11" t="inlineStr">
+        <is>
+          <t>Microsoft Learn ↗</t>
+        </is>
+      </c>
+      <c r="H6" s="10" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
@@ -877,6 +920,12 @@
       </c>
       <c r="E7" s="9" t="inlineStr"/>
       <c r="F7" s="10" t="inlineStr"/>
+      <c r="G7" s="11" t="inlineStr">
+        <is>
+          <t>Microsoft Learn ↗</t>
+        </is>
+      </c>
+      <c r="H7" s="10" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
@@ -907,6 +956,12 @@
         </is>
       </c>
       <c r="F8" s="10" t="inlineStr"/>
+      <c r="G8" s="11" t="inlineStr">
+        <is>
+          <t>Microsoft Learn ↗</t>
+        </is>
+      </c>
+      <c r="H8" s="10" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
@@ -937,6 +992,12 @@
         </is>
       </c>
       <c r="F9" s="10" t="inlineStr"/>
+      <c r="G9" s="11" t="inlineStr">
+        <is>
+          <t>Microsoft Learn ↗</t>
+        </is>
+      </c>
+      <c r="H9" s="10" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr"/>
@@ -949,6 +1010,8 @@
       <c r="D10" s="7" t="n"/>
       <c r="E10" s="7" t="n"/>
       <c r="F10" s="7" t="n"/>
+      <c r="G10" s="7" t="n"/>
+      <c r="H10" s="7" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
@@ -977,6 +1040,12 @@
         </is>
       </c>
       <c r="F11" s="10" t="inlineStr"/>
+      <c r="G11" s="11" t="inlineStr">
+        <is>
+          <t>Microsoft Learn ↗</t>
+        </is>
+      </c>
+      <c r="H11" s="10" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="8" t="inlineStr">
@@ -1006,6 +1075,12 @@
         </is>
       </c>
       <c r="F12" s="10" t="inlineStr"/>
+      <c r="G12" s="11" t="inlineStr">
+        <is>
+          <t>Microsoft Learn ↗</t>
+        </is>
+      </c>
+      <c r="H12" s="10" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
@@ -1030,6 +1105,12 @@
       </c>
       <c r="E13" s="9" t="inlineStr"/>
       <c r="F13" s="10" t="inlineStr"/>
+      <c r="G13" s="11" t="inlineStr">
+        <is>
+          <t>Microsoft Learn ↗</t>
+        </is>
+      </c>
+      <c r="H13" s="10" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr"/>
@@ -1042,6 +1123,8 @@
       <c r="D14" s="7" t="n"/>
       <c r="E14" s="7" t="n"/>
       <c r="F14" s="7" t="n"/>
+      <c r="G14" s="7" t="n"/>
+      <c r="H14" s="7" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
@@ -1066,6 +1149,12 @@
       </c>
       <c r="E15" s="9" t="inlineStr"/>
       <c r="F15" s="10" t="inlineStr"/>
+      <c r="G15" s="11" t="inlineStr">
+        <is>
+          <t>Microsoft Learn ↗</t>
+        </is>
+      </c>
+      <c r="H15" s="10" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="8" t="inlineStr">
@@ -1094,6 +1183,12 @@
         </is>
       </c>
       <c r="F16" s="10" t="inlineStr"/>
+      <c r="G16" s="11" t="inlineStr">
+        <is>
+          <t>Microsoft Learn ↗</t>
+        </is>
+      </c>
+      <c r="H16" s="10" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="7" t="inlineStr"/>
@@ -1106,6 +1201,8 @@
       <c r="D17" s="7" t="n"/>
       <c r="E17" s="7" t="n"/>
       <c r="F17" s="7" t="n"/>
+      <c r="G17" s="7" t="n"/>
+      <c r="H17" s="7" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="8" t="inlineStr">
@@ -1134,6 +1231,12 @@
         </is>
       </c>
       <c r="F18" s="10" t="inlineStr"/>
+      <c r="G18" s="11" t="inlineStr">
+        <is>
+          <t>Microsoft Learn ↗</t>
+        </is>
+      </c>
+      <c r="H18" s="10" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="8" t="inlineStr">
@@ -1162,6 +1265,12 @@
         </is>
       </c>
       <c r="F19" s="10" t="inlineStr"/>
+      <c r="G19" s="11" t="inlineStr">
+        <is>
+          <t>Microsoft Learn ↗</t>
+        </is>
+      </c>
+      <c r="H19" s="10" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="8" t="inlineStr">
@@ -1190,6 +1299,12 @@
         </is>
       </c>
       <c r="F20" s="10" t="inlineStr"/>
+      <c r="G20" s="11" t="inlineStr">
+        <is>
+          <t>Microsoft Learn ↗</t>
+        </is>
+      </c>
+      <c r="H20" s="10" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
@@ -1218,6 +1333,12 @@
         </is>
       </c>
       <c r="F21" s="10" t="inlineStr"/>
+      <c r="G21" s="11" t="inlineStr">
+        <is>
+          <t>Microsoft Learn ↗</t>
+        </is>
+      </c>
+      <c r="H21" s="10" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="7" t="inlineStr"/>
@@ -1230,6 +1351,8 @@
       <c r="D22" s="7" t="n"/>
       <c r="E22" s="7" t="n"/>
       <c r="F22" s="7" t="n"/>
+      <c r="G22" s="7" t="n"/>
+      <c r="H22" s="7" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
@@ -1258,6 +1381,12 @@
         </is>
       </c>
       <c r="F23" s="10" t="inlineStr"/>
+      <c r="G23" s="11" t="inlineStr">
+        <is>
+          <t>Microsoft Learn ↗</t>
+        </is>
+      </c>
+      <c r="H23" s="10" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="8" t="inlineStr">
@@ -1286,6 +1415,12 @@
         </is>
       </c>
       <c r="F24" s="10" t="inlineStr"/>
+      <c r="G24" s="11" t="inlineStr">
+        <is>
+          <t>Microsoft Learn ↗</t>
+        </is>
+      </c>
+      <c r="H24" s="10" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="8" t="inlineStr">
@@ -1314,6 +1449,12 @@
         </is>
       </c>
       <c r="F25" s="10" t="inlineStr"/>
+      <c r="G25" s="11" t="inlineStr">
+        <is>
+          <t>Microsoft Learn ↗</t>
+        </is>
+      </c>
+      <c r="H25" s="10" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="8" t="inlineStr">
@@ -1342,6 +1483,12 @@
         </is>
       </c>
       <c r="F26" s="10" t="inlineStr"/>
+      <c r="G26" s="11" t="inlineStr">
+        <is>
+          <t>Microsoft Learn ↗</t>
+        </is>
+      </c>
+      <c r="H26" s="10" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="8" t="inlineStr">
@@ -1370,6 +1517,12 @@
         </is>
       </c>
       <c r="F27" s="10" t="inlineStr"/>
+      <c r="G27" s="11" t="inlineStr">
+        <is>
+          <t>Microsoft Learn ↗</t>
+        </is>
+      </c>
+      <c r="H27" s="10" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="8" t="inlineStr">
@@ -1398,6 +1551,12 @@
         </is>
       </c>
       <c r="F28" s="10" t="inlineStr"/>
+      <c r="G28" s="11" t="inlineStr">
+        <is>
+          <t>Microsoft Learn ↗</t>
+        </is>
+      </c>
+      <c r="H28" s="10" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
@@ -1426,6 +1585,12 @@
         </is>
       </c>
       <c r="F29" s="10" t="inlineStr"/>
+      <c r="G29" s="11" t="inlineStr">
+        <is>
+          <t>Microsoft Learn ↗</t>
+        </is>
+      </c>
+      <c r="H29" s="10" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="8" t="inlineStr">
@@ -1454,6 +1619,12 @@
         </is>
       </c>
       <c r="F30" s="10" t="inlineStr"/>
+      <c r="G30" s="11" t="inlineStr">
+        <is>
+          <t>Microsoft Learn ↗</t>
+        </is>
+      </c>
+      <c r="H30" s="10" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="7" t="inlineStr"/>
@@ -1466,6 +1637,8 @@
       <c r="D31" s="7" t="n"/>
       <c r="E31" s="7" t="n"/>
       <c r="F31" s="7" t="n"/>
+      <c r="G31" s="7" t="n"/>
+      <c r="H31" s="7" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="8" t="inlineStr">
@@ -1494,6 +1667,12 @@
         </is>
       </c>
       <c r="F32" s="10" t="inlineStr"/>
+      <c r="G32" s="11" t="inlineStr">
+        <is>
+          <t>Microsoft Learn ↗</t>
+        </is>
+      </c>
+      <c r="H32" s="10" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="8" t="inlineStr">
@@ -1522,6 +1701,12 @@
         </is>
       </c>
       <c r="F33" s="10" t="inlineStr"/>
+      <c r="G33" s="11" t="inlineStr">
+        <is>
+          <t>Microsoft Learn ↗</t>
+        </is>
+      </c>
+      <c r="H33" s="10" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="8" t="inlineStr">
@@ -1551,6 +1736,12 @@
         </is>
       </c>
       <c r="F34" s="10" t="inlineStr"/>
+      <c r="G34" s="11" t="inlineStr">
+        <is>
+          <t>Microsoft Learn ↗</t>
+        </is>
+      </c>
+      <c r="H34" s="10" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="8" t="inlineStr">
@@ -1579,6 +1770,12 @@
         </is>
       </c>
       <c r="F35" s="10" t="inlineStr"/>
+      <c r="G35" s="11" t="inlineStr">
+        <is>
+          <t>Microsoft Learn ↗</t>
+        </is>
+      </c>
+      <c r="H35" s="10" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="7" t="inlineStr"/>
@@ -1591,6 +1788,8 @@
       <c r="D36" s="7" t="n"/>
       <c r="E36" s="7" t="n"/>
       <c r="F36" s="7" t="n"/>
+      <c r="G36" s="7" t="n"/>
+      <c r="H36" s="7" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="8" t="inlineStr">
@@ -1619,6 +1818,12 @@
         </is>
       </c>
       <c r="F37" s="10" t="inlineStr"/>
+      <c r="G37" s="11" t="inlineStr">
+        <is>
+          <t>Microsoft Learn ↗</t>
+        </is>
+      </c>
+      <c r="H37" s="10" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="7" t="inlineStr"/>
@@ -1631,6 +1836,8 @@
       <c r="D38" s="7" t="n"/>
       <c r="E38" s="7" t="n"/>
       <c r="F38" s="7" t="n"/>
+      <c r="G38" s="7" t="n"/>
+      <c r="H38" s="7" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="8" t="inlineStr">
@@ -1659,6 +1866,12 @@
         </is>
       </c>
       <c r="F39" s="10" t="inlineStr"/>
+      <c r="G39" s="11" t="inlineStr">
+        <is>
+          <t>Microsoft Learn ↗</t>
+        </is>
+      </c>
+      <c r="H39" s="10" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="8" t="inlineStr">
@@ -1687,6 +1900,12 @@
         </is>
       </c>
       <c r="F40" s="10" t="inlineStr"/>
+      <c r="G40" s="11" t="inlineStr">
+        <is>
+          <t>Microsoft Learn ↗</t>
+        </is>
+      </c>
+      <c r="H40" s="10" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="8" t="inlineStr">
@@ -1715,6 +1934,12 @@
         </is>
       </c>
       <c r="F41" s="10" t="inlineStr"/>
+      <c r="G41" s="11" t="inlineStr">
+        <is>
+          <t>Microsoft Learn ↗</t>
+        </is>
+      </c>
+      <c r="H41" s="10" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="7" t="inlineStr"/>
@@ -1727,6 +1952,8 @@
       <c r="D42" s="7" t="n"/>
       <c r="E42" s="7" t="n"/>
       <c r="F42" s="7" t="n"/>
+      <c r="G42" s="7" t="n"/>
+      <c r="H42" s="7" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="8" t="inlineStr">
@@ -1756,6 +1983,12 @@
         </is>
       </c>
       <c r="F43" s="10" t="inlineStr"/>
+      <c r="G43" s="11" t="inlineStr">
+        <is>
+          <t>Microsoft Learn ↗</t>
+        </is>
+      </c>
+      <c r="H43" s="10" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="8" t="inlineStr">
@@ -1785,6 +2018,12 @@
         </is>
       </c>
       <c r="F44" s="10" t="inlineStr"/>
+      <c r="G44" s="11" t="inlineStr">
+        <is>
+          <t>Microsoft Learn ↗</t>
+        </is>
+      </c>
+      <c r="H44" s="10" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="7" t="inlineStr"/>
@@ -1797,6 +2036,8 @@
       <c r="D45" s="7" t="n"/>
       <c r="E45" s="7" t="n"/>
       <c r="F45" s="7" t="n"/>
+      <c r="G45" s="7" t="n"/>
+      <c r="H45" s="7" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="8" t="inlineStr">
@@ -1825,6 +2066,12 @@
         </is>
       </c>
       <c r="F46" s="10" t="inlineStr"/>
+      <c r="G46" s="11" t="inlineStr">
+        <is>
+          <t>Microsoft Learn ↗</t>
+        </is>
+      </c>
+      <c r="H46" s="10" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="8" t="inlineStr">
@@ -1853,6 +2100,12 @@
         </is>
       </c>
       <c r="F47" s="10" t="inlineStr"/>
+      <c r="G47" s="11" t="inlineStr">
+        <is>
+          <t>Microsoft Learn ↗</t>
+        </is>
+      </c>
+      <c r="H47" s="10" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="8" t="inlineStr">
@@ -1877,6 +2130,12 @@
       </c>
       <c r="E48" s="9" t="inlineStr"/>
       <c r="F48" s="10" t="inlineStr"/>
+      <c r="G48" s="11" t="inlineStr">
+        <is>
+          <t>Microsoft Learn ↗</t>
+        </is>
+      </c>
+      <c r="H48" s="10" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="8" t="inlineStr">
@@ -1905,6 +2164,12 @@
         </is>
       </c>
       <c r="F49" s="10" t="inlineStr"/>
+      <c r="G49" s="11" t="inlineStr">
+        <is>
+          <t>Microsoft Learn ↗</t>
+        </is>
+      </c>
+      <c r="H49" s="10" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="7" t="inlineStr"/>
@@ -1917,6 +2182,8 @@
       <c r="D50" s="7" t="n"/>
       <c r="E50" s="7" t="n"/>
       <c r="F50" s="7" t="n"/>
+      <c r="G50" s="7" t="n"/>
+      <c r="H50" s="7" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="8" t="inlineStr">
@@ -1945,6 +2212,12 @@
         </is>
       </c>
       <c r="F51" s="10" t="inlineStr"/>
+      <c r="G51" s="11" t="inlineStr">
+        <is>
+          <t>Microsoft Learn ↗</t>
+        </is>
+      </c>
+      <c r="H51" s="10" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="8" t="inlineStr">
@@ -1973,6 +2246,12 @@
         </is>
       </c>
       <c r="F52" s="10" t="inlineStr"/>
+      <c r="G52" s="11" t="inlineStr">
+        <is>
+          <t>Microsoft Learn ↗</t>
+        </is>
+      </c>
+      <c r="H52" s="10" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="8" t="inlineStr">
@@ -2001,6 +2280,12 @@
         </is>
       </c>
       <c r="F53" s="10" t="inlineStr"/>
+      <c r="G53" s="11" t="inlineStr">
+        <is>
+          <t>Microsoft Learn ↗</t>
+        </is>
+      </c>
+      <c r="H53" s="10" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="8" t="inlineStr">
@@ -2029,6 +2314,12 @@
         </is>
       </c>
       <c r="F54" s="10" t="inlineStr"/>
+      <c r="G54" s="11" t="inlineStr">
+        <is>
+          <t>Microsoft Learn ↗</t>
+        </is>
+      </c>
+      <c r="H54" s="10" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="8" t="inlineStr">
@@ -2057,6 +2348,12 @@
         </is>
       </c>
       <c r="F55" s="10" t="inlineStr"/>
+      <c r="G55" s="11" t="inlineStr">
+        <is>
+          <t>Microsoft Learn ↗</t>
+        </is>
+      </c>
+      <c r="H55" s="10" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="8" t="inlineStr">
@@ -2085,6 +2382,12 @@
         </is>
       </c>
       <c r="F56" s="10" t="inlineStr"/>
+      <c r="G56" s="11" t="inlineStr">
+        <is>
+          <t>Microsoft Learn ↗</t>
+        </is>
+      </c>
+      <c r="H56" s="10" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="8" t="inlineStr">
@@ -2113,6 +2416,12 @@
         </is>
       </c>
       <c r="F57" s="10" t="inlineStr"/>
+      <c r="G57" s="11" t="inlineStr">
+        <is>
+          <t>Microsoft Learn ↗</t>
+        </is>
+      </c>
+      <c r="H57" s="10" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="8" t="inlineStr">
@@ -2141,6 +2450,12 @@
         </is>
       </c>
       <c r="F58" s="10" t="inlineStr"/>
+      <c r="G58" s="11" t="inlineStr">
+        <is>
+          <t>Microsoft Learn ↗</t>
+        </is>
+      </c>
+      <c r="H58" s="10" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="8" t="inlineStr">
@@ -2169,6 +2484,12 @@
         </is>
       </c>
       <c r="F59" s="10" t="inlineStr"/>
+      <c r="G59" s="11" t="inlineStr">
+        <is>
+          <t>Microsoft Learn ↗</t>
+        </is>
+      </c>
+      <c r="H59" s="10" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="8" t="inlineStr">
@@ -2197,6 +2518,12 @@
         </is>
       </c>
       <c r="F60" s="10" t="inlineStr"/>
+      <c r="G60" s="11" t="inlineStr">
+        <is>
+          <t>Microsoft Learn ↗</t>
+        </is>
+      </c>
+      <c r="H60" s="10" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="8" t="inlineStr">
@@ -2225,6 +2552,12 @@
         </is>
       </c>
       <c r="F61" s="10" t="inlineStr"/>
+      <c r="G61" s="11" t="inlineStr">
+        <is>
+          <t>Microsoft Learn ↗</t>
+        </is>
+      </c>
+      <c r="H61" s="10" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="8" t="inlineStr">
@@ -2253,6 +2586,12 @@
         </is>
       </c>
       <c r="F62" s="10" t="inlineStr"/>
+      <c r="G62" s="11" t="inlineStr">
+        <is>
+          <t>Microsoft Learn ↗</t>
+        </is>
+      </c>
+      <c r="H62" s="10" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="8" t="inlineStr">
@@ -2281,6 +2620,12 @@
         </is>
       </c>
       <c r="F63" s="10" t="inlineStr"/>
+      <c r="G63" s="11" t="inlineStr">
+        <is>
+          <t>Microsoft Learn ↗</t>
+        </is>
+      </c>
+      <c r="H63" s="10" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="8" t="inlineStr">
@@ -2309,6 +2654,12 @@
         </is>
       </c>
       <c r="F64" s="10" t="inlineStr"/>
+      <c r="G64" s="11" t="inlineStr">
+        <is>
+          <t>Microsoft Learn ↗</t>
+        </is>
+      </c>
+      <c r="H64" s="10" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="8" t="inlineStr">
@@ -2337,6 +2688,12 @@
         </is>
       </c>
       <c r="F65" s="10" t="inlineStr"/>
+      <c r="G65" s="11" t="inlineStr">
+        <is>
+          <t>Microsoft Learn ↗</t>
+        </is>
+      </c>
+      <c r="H65" s="10" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="8" t="inlineStr">
@@ -2365,22 +2722,28 @@
         </is>
       </c>
       <c r="F66" s="10" t="inlineStr"/>
+      <c r="G66" s="11" t="inlineStr">
+        <is>
+          <t>Microsoft Learn ↗</t>
+        </is>
+      </c>
+      <c r="H66" s="10" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="B38:F38"/>
-    <mergeCell ref="B10:F10"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="B42:F42"/>
-    <mergeCell ref="B5:F5"/>
-    <mergeCell ref="B31:F31"/>
-    <mergeCell ref="B45:F45"/>
-    <mergeCell ref="B22:F22"/>
-    <mergeCell ref="B14:F14"/>
-    <mergeCell ref="B36:F36"/>
-    <mergeCell ref="B50:F50"/>
-    <mergeCell ref="B17:F17"/>
+    <mergeCell ref="B22:H22"/>
+    <mergeCell ref="B14:H14"/>
+    <mergeCell ref="B36:H36"/>
+    <mergeCell ref="B50:H50"/>
+    <mergeCell ref="B17:H17"/>
+    <mergeCell ref="B42:H42"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="B45:H45"/>
+    <mergeCell ref="B38:H38"/>
+    <mergeCell ref="B10:H10"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="B5:H5"/>
+    <mergeCell ref="B31:H31"/>
   </mergeCells>
   <dataValidations count="25">
     <dataValidation sqref="F6" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
@@ -2459,6 +2822,59 @@
       <formula1>"true,false"</formula1>
     </dataValidation>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G6" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G7" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G8" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G9" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G11" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G12" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G13" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G15" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G16" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G18" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G19" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G20" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G21" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G23" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G24" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G25" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G26" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G27" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G28" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G29" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G30" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G32" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G33" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G34" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G35" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G37" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G39" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G40" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G41" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G43" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G44" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G46" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G47" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G48" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G49" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G51" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G52" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G53" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G54" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G55" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G56" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G57" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G58" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G59" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G60" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G61" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G62" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G63" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G64" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G65" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G66" r:id="rId51"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2469,7 +2885,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E26"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -2477,6 +2893,8 @@
     <col width="45" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
     <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -2519,6 +2937,16 @@
           <t>Your value</t>
         </is>
       </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>Comments</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
@@ -2530,6 +2958,8 @@
       <c r="C5" s="7" t="n"/>
       <c r="D5" s="7" t="n"/>
       <c r="E5" s="7" t="n"/>
+      <c r="F5" s="7" t="n"/>
+      <c r="G5" s="7" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="9" t="inlineStr">
@@ -2554,6 +2984,12 @@
         </is>
       </c>
       <c r="E6" s="10" t="inlineStr"/>
+      <c r="F6" s="11" t="inlineStr">
+        <is>
+          <t>Microsoft Learn ↗</t>
+        </is>
+      </c>
+      <c r="G6" s="10" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
@@ -2577,6 +3013,12 @@
         </is>
       </c>
       <c r="E7" s="10" t="inlineStr"/>
+      <c r="F7" s="11" t="inlineStr">
+        <is>
+          <t>Microsoft Learn ↗</t>
+        </is>
+      </c>
+      <c r="G7" s="10" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="9" t="inlineStr">
@@ -2600,6 +3042,12 @@
         </is>
       </c>
       <c r="E8" s="10" t="inlineStr"/>
+      <c r="F8" s="11" t="inlineStr">
+        <is>
+          <t>Microsoft Learn ↗</t>
+        </is>
+      </c>
+      <c r="G8" s="10" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
@@ -2611,6 +3059,8 @@
       <c r="C9" s="7" t="n"/>
       <c r="D9" s="7" t="n"/>
       <c r="E9" s="7" t="n"/>
+      <c r="F9" s="7" t="n"/>
+      <c r="G9" s="7" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
@@ -2634,6 +3084,12 @@
         </is>
       </c>
       <c r="E10" s="10" t="inlineStr"/>
+      <c r="F10" s="11" t="inlineStr">
+        <is>
+          <t>Microsoft Learn ↗</t>
+        </is>
+      </c>
+      <c r="G10" s="10" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="9" t="inlineStr">
@@ -2657,6 +3113,12 @@
         </is>
       </c>
       <c r="E11" s="10" t="inlineStr"/>
+      <c r="F11" s="11" t="inlineStr">
+        <is>
+          <t>Microsoft Learn ↗</t>
+        </is>
+      </c>
+      <c r="G11" s="10" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="9" t="inlineStr">
@@ -2680,6 +3142,12 @@
         </is>
       </c>
       <c r="E12" s="10" t="inlineStr"/>
+      <c r="F12" s="11" t="inlineStr">
+        <is>
+          <t>Microsoft Learn ↗</t>
+        </is>
+      </c>
+      <c r="G12" s="10" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
@@ -2691,6 +3159,8 @@
       <c r="C13" s="7" t="n"/>
       <c r="D13" s="7" t="n"/>
       <c r="E13" s="7" t="n"/>
+      <c r="F13" s="7" t="n"/>
+      <c r="G13" s="7" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
@@ -2715,6 +3185,12 @@
         </is>
       </c>
       <c r="E14" s="10" t="inlineStr"/>
+      <c r="F14" s="11" t="inlineStr">
+        <is>
+          <t>Microsoft Learn ↗</t>
+        </is>
+      </c>
+      <c r="G14" s="10" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
@@ -2738,6 +3214,12 @@
         </is>
       </c>
       <c r="E15" s="10" t="inlineStr"/>
+      <c r="F15" s="11" t="inlineStr">
+        <is>
+          <t>Microsoft Learn ↗</t>
+        </is>
+      </c>
+      <c r="G15" s="10" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="9" t="inlineStr">
@@ -2761,6 +3243,12 @@
         </is>
       </c>
       <c r="E16" s="10" t="inlineStr"/>
+      <c r="F16" s="11" t="inlineStr">
+        <is>
+          <t>Microsoft Learn ↗</t>
+        </is>
+      </c>
+      <c r="G16" s="10" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="9" t="inlineStr">
@@ -2784,6 +3272,12 @@
         </is>
       </c>
       <c r="E17" s="10" t="inlineStr"/>
+      <c r="F17" s="11" t="inlineStr">
+        <is>
+          <t>Microsoft Learn ↗</t>
+        </is>
+      </c>
+      <c r="G17" s="10" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
@@ -2795,6 +3289,8 @@
       <c r="C18" s="7" t="n"/>
       <c r="D18" s="7" t="n"/>
       <c r="E18" s="7" t="n"/>
+      <c r="F18" s="7" t="n"/>
+      <c r="G18" s="7" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="9" t="inlineStr">
@@ -2818,6 +3314,12 @@
         </is>
       </c>
       <c r="E19" s="10" t="inlineStr"/>
+      <c r="F19" s="11" t="inlineStr">
+        <is>
+          <t>Microsoft Learn ↗</t>
+        </is>
+      </c>
+      <c r="G19" s="10" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="9" t="inlineStr">
@@ -2841,6 +3343,12 @@
         </is>
       </c>
       <c r="E20" s="10" t="inlineStr"/>
+      <c r="F20" s="11" t="inlineStr">
+        <is>
+          <t>Microsoft Learn ↗</t>
+        </is>
+      </c>
+      <c r="G20" s="10" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
@@ -2852,6 +3360,8 @@
       <c r="C21" s="7" t="n"/>
       <c r="D21" s="7" t="n"/>
       <c r="E21" s="7" t="n"/>
+      <c r="F21" s="7" t="n"/>
+      <c r="G21" s="7" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="9" t="inlineStr">
@@ -2875,6 +3385,12 @@
         </is>
       </c>
       <c r="E22" s="10" t="inlineStr"/>
+      <c r="F22" s="11" t="inlineStr">
+        <is>
+          <t>Microsoft Learn ↗</t>
+        </is>
+      </c>
+      <c r="G22" s="10" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="9" t="inlineStr">
@@ -2898,6 +3414,12 @@
         </is>
       </c>
       <c r="E23" s="10" t="inlineStr"/>
+      <c r="F23" s="11" t="inlineStr">
+        <is>
+          <t>Microsoft Learn ↗</t>
+        </is>
+      </c>
+      <c r="G23" s="10" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="9" t="inlineStr">
@@ -2921,6 +3443,12 @@
         </is>
       </c>
       <c r="E24" s="10" t="inlineStr"/>
+      <c r="F24" s="11" t="inlineStr">
+        <is>
+          <t>Microsoft Learn ↗</t>
+        </is>
+      </c>
+      <c r="G24" s="10" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
@@ -2932,6 +3460,8 @@
       <c r="C25" s="7" t="n"/>
       <c r="D25" s="7" t="n"/>
       <c r="E25" s="7" t="n"/>
+      <c r="F25" s="7" t="n"/>
+      <c r="G25" s="7" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="9" t="inlineStr">
@@ -2955,17 +3485,23 @@
         </is>
       </c>
       <c r="E26" s="10" t="inlineStr"/>
+      <c r="F26" s="11" t="inlineStr">
+        <is>
+          <t>Microsoft Learn ↗</t>
+        </is>
+      </c>
+      <c r="G26" s="10" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A21:E21"/>
-    <mergeCell ref="A18:E18"/>
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A25:E25"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A5:E5"/>
-    <mergeCell ref="A13:E13"/>
-    <mergeCell ref="A9:E9"/>
+    <mergeCell ref="A13:G13"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A9:G9"/>
+    <mergeCell ref="A18:G18"/>
+    <mergeCell ref="A21:G21"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A25:G25"/>
+    <mergeCell ref="A5:G5"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation sqref="E14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
@@ -2981,6 +3517,24 @@
       <formula1>"WAF_v2,Standard_v2"</formula1>
     </dataValidation>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F6" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F7" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F8" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F10" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F11" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F12" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F14" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F15" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F16" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F17" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F19" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F20" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F22" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F23" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F24" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F26" r:id="rId16"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/config/checklist.xlsx
+++ b/config/checklist.xlsx
@@ -777,7 +777,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H69"/>
+  <dimension ref="A1:H70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2392,17 +2392,17 @@
     <row r="57">
       <c r="A57" s="8" t="inlineStr">
         <is>
-          <t>11f</t>
+          <t>11e2</t>
         </is>
       </c>
       <c r="B57" s="9" t="inlineStr">
         <is>
-          <t>enable_app_gateway</t>
+          <t>grafana_public_access</t>
         </is>
       </c>
       <c r="C57" s="9" t="inlineStr">
         <is>
-          <t>Application Gateway with a Web Application Firewall in front of the cluster.</t>
+          <t>Public network access to Managed Grafana. Recommended false (private via private endpoint); a Grafana private endpoint + private DNS zone are created automatically when private endpoints are enabled.</t>
         </is>
       </c>
       <c r="D57" s="9" t="inlineStr">
@@ -2412,7 +2412,7 @@
       </c>
       <c r="E57" s="9" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
       <c r="F57" s="10" t="inlineStr"/>
@@ -2426,27 +2426,27 @@
     <row r="58">
       <c r="A58" s="8" t="inlineStr">
         <is>
-          <t>11f2</t>
+          <t>11f</t>
         </is>
       </c>
       <c r="B58" s="9" t="inlineStr">
         <is>
-          <t>ingress_controller</t>
+          <t>enable_app_gateway</t>
         </is>
       </c>
       <c r="C58" s="9" t="inlineStr">
         <is>
-          <t>Only used when enable_app_gateway (11f) is true. Application Gateway acts as a reverse proxy in front of an INTERNAL in-cluster ingress controller: istio (managed Istio internal gateway — auto-selected when Istio 11j is on), traefik (deployed internally for you), or manual (you deploy your own). nginx is not offered (ingress-nginx is being retired). The CD pipeline auto-wires the controller's private IP into the gateway backend pool.</t>
+          <t>Application Gateway with a Web Application Firewall in front of the cluster.</t>
         </is>
       </c>
       <c r="D58" s="9" t="inlineStr">
         <is>
-          <t>istio | traefik | manual</t>
+          <t>true | false</t>
         </is>
       </c>
       <c r="E58" s="9" t="inlineStr">
         <is>
-          <t>traefik  (istio when enable_istio is true)</t>
+          <t>true</t>
         </is>
       </c>
       <c r="F58" s="10" t="inlineStr"/>
@@ -2460,27 +2460,27 @@
     <row r="59">
       <c r="A59" s="8" t="inlineStr">
         <is>
-          <t>11f3</t>
+          <t>11f2</t>
         </is>
       </c>
       <c r="B59" s="9" t="inlineStr">
         <is>
-          <t>appgw_tls_key_vault_secret_id</t>
+          <t>ingress_controller</t>
         </is>
       </c>
       <c r="C59" s="9" t="inlineStr">
         <is>
-          <t>Optional. Key Vault secret ID of the TLS certificate for the Application Gateway HTTPS:443 listener (also adds an HTTP→HTTPS redirect). The gateway reads it with the AKS identity. Leave blank to serve HTTP:80 only; you can add TLS later.</t>
+          <t>Only used when enable_app_gateway (11f) is true. Application Gateway acts as a reverse proxy in front of an INTERNAL in-cluster ingress controller: istio (managed Istio internal gateway — auto-selected when Istio 11j is on), traefik (deployed internally for you), or manual (you deploy your own). nginx is not offered (ingress-nginx is being retired). The CD pipeline auto-wires the controller's private IP into the gateway backend pool.</t>
         </is>
       </c>
       <c r="D59" s="9" t="inlineStr">
         <is>
-          <t>Key Vault secret URI, or blank</t>
+          <t>istio | traefik | manual</t>
         </is>
       </c>
       <c r="E59" s="9" t="inlineStr">
         <is>
-          <t>(blank = HTTP:80 only)</t>
+          <t>traefik  (istio when enable_istio is true)</t>
         </is>
       </c>
       <c r="F59" s="10" t="inlineStr"/>
@@ -2494,27 +2494,27 @@
     <row r="60">
       <c r="A60" s="8" t="inlineStr">
         <is>
-          <t>11p</t>
+          <t>11f3</t>
         </is>
       </c>
       <c r="B60" s="9" t="inlineStr">
         <is>
-          <t>enable_agc</t>
+          <t>appgw_tls_key_vault_secret_id</t>
         </is>
       </c>
       <c r="C60" s="9" t="inlineStr">
         <is>
-          <t>Application Gateway for Containers (ALB). Provisions a delegated subnet (5h) + NSG; the in-cluster ALB Controller manages the gateway. Coexists with enable_app_gateway.</t>
+          <t>Optional. Key Vault secret ID of the TLS certificate for the Application Gateway HTTPS:443 listener (also adds an HTTP→HTTPS redirect). The gateway reads it with the AKS identity. Leave blank to serve HTTP:80 only; you can add TLS later.</t>
         </is>
       </c>
       <c r="D60" s="9" t="inlineStr">
         <is>
-          <t>true | false</t>
+          <t>Key Vault secret URI, or blank</t>
         </is>
       </c>
       <c r="E60" s="9" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>(blank = HTTP:80 only)</t>
         </is>
       </c>
       <c r="F60" s="10" t="inlineStr"/>
@@ -2528,17 +2528,17 @@
     <row r="61">
       <c r="A61" s="8" t="inlineStr">
         <is>
-          <t>11g</t>
+          <t>11p</t>
         </is>
       </c>
       <c r="B61" s="9" t="inlineStr">
         <is>
-          <t>enable_keda</t>
+          <t>enable_agc</t>
         </is>
       </c>
       <c r="C61" s="9" t="inlineStr">
         <is>
-          <t>Auto-scales pods based on events (queue length, HTTP requests, etc.).</t>
+          <t>Application Gateway for Containers (ALB). Provisions a delegated subnet (5h) + NSG; the in-cluster ALB Controller manages the gateway. Coexists with enable_app_gateway.</t>
         </is>
       </c>
       <c r="D61" s="9" t="inlineStr">
@@ -2548,7 +2548,7 @@
       </c>
       <c r="E61" s="9" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
       <c r="F61" s="10" t="inlineStr"/>
@@ -2562,17 +2562,17 @@
     <row r="62">
       <c r="A62" s="8" t="inlineStr">
         <is>
-          <t>11h</t>
+          <t>11g</t>
         </is>
       </c>
       <c r="B62" s="9" t="inlineStr">
         <is>
-          <t>enable_vpa</t>
+          <t>enable_keda</t>
         </is>
       </c>
       <c r="C62" s="9" t="inlineStr">
         <is>
-          <t>Auto-adjusts CPU and memory requests for pods.</t>
+          <t>Auto-scales pods based on events (queue length, HTTP requests, etc.).</t>
         </is>
       </c>
       <c r="D62" s="9" t="inlineStr">
@@ -2582,7 +2582,7 @@
       </c>
       <c r="E62" s="9" t="inlineStr">
         <is>
-          <t>false  (true for regulated / multi-region)</t>
+          <t>true</t>
         </is>
       </c>
       <c r="F62" s="10" t="inlineStr"/>
@@ -2596,17 +2596,17 @@
     <row r="63">
       <c r="A63" s="8" t="inlineStr">
         <is>
-          <t>11i</t>
+          <t>11h</t>
         </is>
       </c>
       <c r="B63" s="9" t="inlineStr">
         <is>
-          <t>enable_node_auto_provisioning</t>
+          <t>enable_vpa</t>
         </is>
       </c>
       <c r="C63" s="9" t="inlineStr">
         <is>
-          <t>Cluster creates new node sizes on demand instead of using fixed pools.</t>
+          <t>Auto-adjusts CPU and memory requests for pods.</t>
         </is>
       </c>
       <c r="D63" s="9" t="inlineStr">
@@ -2616,7 +2616,7 @@
       </c>
       <c r="E63" s="9" t="inlineStr">
         <is>
-          <t>false  (true for multi-region)</t>
+          <t>false  (true for regulated / multi-region)</t>
         </is>
       </c>
       <c r="F63" s="10" t="inlineStr"/>
@@ -2630,17 +2630,17 @@
     <row r="64">
       <c r="A64" s="8" t="inlineStr">
         <is>
-          <t>11j</t>
+          <t>11i</t>
         </is>
       </c>
       <c r="B64" s="9" t="inlineStr">
         <is>
-          <t>enable_istio</t>
+          <t>enable_node_auto_provisioning</t>
         </is>
       </c>
       <c r="C64" s="9" t="inlineStr">
         <is>
-          <t>Service mesh with mTLS between pods. Needed for some compliance standards.</t>
+          <t>Cluster creates new node sizes on demand instead of using fixed pools.</t>
         </is>
       </c>
       <c r="D64" s="9" t="inlineStr">
@@ -2650,7 +2650,7 @@
       </c>
       <c r="E64" s="9" t="inlineStr">
         <is>
-          <t>false  (true for regulated)</t>
+          <t>false  (true for multi-region)</t>
         </is>
       </c>
       <c r="F64" s="10" t="inlineStr"/>
@@ -2664,17 +2664,17 @@
     <row r="65">
       <c r="A65" s="8" t="inlineStr">
         <is>
-          <t>11k</t>
+          <t>11j</t>
         </is>
       </c>
       <c r="B65" s="9" t="inlineStr">
         <is>
-          <t>enable_flux</t>
+          <t>enable_istio</t>
         </is>
       </c>
       <c r="C65" s="9" t="inlineStr">
         <is>
-          <t>GitOps — the cluster pulls its configuration from a Git repo.</t>
+          <t>Service mesh with mTLS between pods. Needed for some compliance standards.</t>
         </is>
       </c>
       <c r="D65" s="9" t="inlineStr">
@@ -2684,7 +2684,7 @@
       </c>
       <c r="E65" s="9" t="inlineStr">
         <is>
-          <t>false  (true for multi-region)</t>
+          <t>false  (true for regulated)</t>
         </is>
       </c>
       <c r="F65" s="10" t="inlineStr"/>
@@ -2698,17 +2698,17 @@
     <row r="66">
       <c r="A66" s="8" t="inlineStr">
         <is>
-          <t>11l</t>
+          <t>11k</t>
         </is>
       </c>
       <c r="B66" s="9" t="inlineStr">
         <is>
-          <t>enable_dapr</t>
+          <t>enable_flux</t>
         </is>
       </c>
       <c r="C66" s="9" t="inlineStr">
         <is>
-          <t>Building blocks for microservices (pub/sub, state, secrets).</t>
+          <t>GitOps — the cluster pulls its configuration from a Git repo.</t>
         </is>
       </c>
       <c r="D66" s="9" t="inlineStr">
@@ -2718,7 +2718,7 @@
       </c>
       <c r="E66" s="9" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>false  (true for multi-region)</t>
         </is>
       </c>
       <c r="F66" s="10" t="inlineStr"/>
@@ -2732,17 +2732,17 @@
     <row r="67">
       <c r="A67" s="8" t="inlineStr">
         <is>
-          <t>11m</t>
+          <t>11l</t>
         </is>
       </c>
       <c r="B67" s="9" t="inlineStr">
         <is>
-          <t>enable_fips</t>
+          <t>enable_dapr</t>
         </is>
       </c>
       <c r="C67" s="9" t="inlineStr">
         <is>
-          <t>Use FIPS 140-2 compliant node OS (US Federal / PCI).</t>
+          <t>Building blocks for microservices (pub/sub, state, secrets).</t>
         </is>
       </c>
       <c r="D67" s="9" t="inlineStr">
@@ -2752,7 +2752,7 @@
       </c>
       <c r="E67" s="9" t="inlineStr">
         <is>
-          <t>false  (true for regulated)</t>
+          <t>false</t>
         </is>
       </c>
       <c r="F67" s="10" t="inlineStr"/>
@@ -2766,17 +2766,17 @@
     <row r="68">
       <c r="A68" s="8" t="inlineStr">
         <is>
-          <t>11n</t>
+          <t>11m</t>
         </is>
       </c>
       <c r="B68" s="9" t="inlineStr">
         <is>
-          <t>enable_backup</t>
+          <t>enable_fips</t>
         </is>
       </c>
       <c r="C68" s="9" t="inlineStr">
         <is>
-          <t>Azure Backup for cluster resources and persistent volumes.</t>
+          <t>Use FIPS 140-2 compliant node OS (US Federal / PCI).</t>
         </is>
       </c>
       <c r="D68" s="9" t="inlineStr">
@@ -2786,7 +2786,7 @@
       </c>
       <c r="E68" s="9" t="inlineStr">
         <is>
-          <t>false  (true for regulated / multi-region)</t>
+          <t>false  (true for regulated)</t>
         </is>
       </c>
       <c r="F68" s="10" t="inlineStr"/>
@@ -2800,17 +2800,17 @@
     <row r="69">
       <c r="A69" s="8" t="inlineStr">
         <is>
-          <t>11o</t>
+          <t>11n</t>
         </is>
       </c>
       <c r="B69" s="9" t="inlineStr">
         <is>
-          <t>enable_cost_analysis</t>
+          <t>enable_backup</t>
         </is>
       </c>
       <c r="C69" s="9" t="inlineStr">
         <is>
-          <t>Cost breakdown per namespace in the Azure portal.</t>
+          <t>Azure Backup for cluster resources and persistent volumes.</t>
         </is>
       </c>
       <c r="D69" s="9" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="E69" s="9" t="inlineStr">
         <is>
-          <t>false  (true for regulated)</t>
+          <t>false  (true for regulated / multi-region)</t>
         </is>
       </c>
       <c r="F69" s="10" t="inlineStr"/>
@@ -2830,6 +2830,40 @@
         </is>
       </c>
       <c r="H69" s="10" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="8" t="inlineStr">
+        <is>
+          <t>11o</t>
+        </is>
+      </c>
+      <c r="B70" s="9" t="inlineStr">
+        <is>
+          <t>enable_cost_analysis</t>
+        </is>
+      </c>
+      <c r="C70" s="9" t="inlineStr">
+        <is>
+          <t>Cost breakdown per namespace in the Azure portal.</t>
+        </is>
+      </c>
+      <c r="D70" s="9" t="inlineStr">
+        <is>
+          <t>true | false</t>
+        </is>
+      </c>
+      <c r="E70" s="9" t="inlineStr">
+        <is>
+          <t>false  (true for regulated)</t>
+        </is>
+      </c>
+      <c r="F70" s="10" t="inlineStr"/>
+      <c r="G70" s="11" t="inlineStr">
+        <is>
+          <t>Microsoft Learn ↗</t>
+        </is>
+      </c>
+      <c r="H70" s="10" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="13">
@@ -2847,7 +2881,7 @@
     <mergeCell ref="B5:H5"/>
     <mergeCell ref="B31:H31"/>
   </mergeCells>
-  <dataValidations count="27">
+  <dataValidations count="28">
     <dataValidation sqref="F6" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"single_region_baseline,multi_region_baseline,single_region_regulated,multi_region_regulated"</formula1>
     </dataValidation>
@@ -2897,10 +2931,10 @@
       <formula1>"true,false"</formula1>
     </dataValidation>
     <dataValidation sqref="F58" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"true,false"</formula1>
+    </dataValidation>
+    <dataValidation sqref="F59" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"istio,traefik,manual"</formula1>
-    </dataValidation>
-    <dataValidation sqref="F60" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"true,false"</formula1>
     </dataValidation>
     <dataValidation sqref="F61" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"true,false"</formula1>
@@ -2927,6 +2961,9 @@
       <formula1>"true,false"</formula1>
     </dataValidation>
     <dataValidation sqref="F69" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"true,false"</formula1>
+    </dataValidation>
+    <dataValidation sqref="F70" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"true,false"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2985,6 +3022,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G67" r:id="rId52"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G68" r:id="rId53"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G69" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G70" r:id="rId55"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/config/checklist.xlsx
+++ b/config/checklist.xlsx
@@ -777,7 +777,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H70"/>
+  <dimension ref="A1:H71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2470,17 +2470,17 @@
       </c>
       <c r="C59" s="9" t="inlineStr">
         <is>
-          <t>Only used when enable_app_gateway (11f) is true. Application Gateway acts as a reverse proxy in front of an INTERNAL in-cluster ingress controller: istio (managed Istio internal gateway — auto-selected when Istio 11j is on), traefik (deployed internally for you), or manual (you deploy your own). nginx is not offered (ingress-nginx is being retired). The CD pipeline auto-wires the controller's private IP into the gateway backend pool.</t>
+          <t>Only used when enable_app_gateway (11f) is true. Application Gateway acts as a reverse proxy in front of an INTERNAL in-cluster ingress controller: istio (managed Istio internal gateway — set up and auto-wired for you; auto-selected when Istio 11j is on) or manual (baseline only — you install and wire your own open-source ingress controller). Only istio is wired by the CD pipeline; manual leaves the ingress controller and backend-pool wiring to you.</t>
         </is>
       </c>
       <c r="D59" s="9" t="inlineStr">
         <is>
-          <t>istio | traefik | manual</t>
+          <t>istio | manual</t>
         </is>
       </c>
       <c r="E59" s="9" t="inlineStr">
         <is>
-          <t>traefik  (istio when enable_istio is true)</t>
+          <t>manual  (istio when enable_istio is true)</t>
         </is>
       </c>
       <c r="F59" s="10" t="inlineStr"/>
@@ -2864,6 +2864,40 @@
         </is>
       </c>
       <c r="H70" s="10" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="8" t="inlineStr">
+        <is>
+          <t>11p</t>
+        </is>
+      </c>
+      <c r="B71" s="9" t="inlineStr">
+        <is>
+          <t>auto_scaler_profile</t>
+        </is>
+      </c>
+      <c r="C71" s="9" t="inlineStr">
+        <is>
+          <t>Day-2 (optional): fine-tune the cluster autoscaler for cost vs performance. Keep AKS defaults unless Azure Advisor flags idle nodes. See docs.</t>
+        </is>
+      </c>
+      <c r="D71" s="9" t="inlineStr">
+        <is>
+          <t>Keep AKS defaults | tune in tfvars</t>
+        </is>
+      </c>
+      <c r="E71" s="9" t="inlineStr">
+        <is>
+          <t>Keep AKS defaults</t>
+        </is>
+      </c>
+      <c r="F71" s="10" t="inlineStr"/>
+      <c r="G71" s="11" t="inlineStr">
+        <is>
+          <t>Microsoft Learn ↗</t>
+        </is>
+      </c>
+      <c r="H71" s="10" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="13">
@@ -2934,7 +2968,7 @@
       <formula1>"true,false"</formula1>
     </dataValidation>
     <dataValidation sqref="F59" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"istio,traefik,manual"</formula1>
+      <formula1>"istio,manual"</formula1>
     </dataValidation>
     <dataValidation sqref="F61" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"true,false"</formula1>
@@ -3023,6 +3057,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G68" r:id="rId53"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G69" r:id="rId54"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G70" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G71" r:id="rId56"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/config/checklist.xlsx
+++ b/config/checklist.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="How to use" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Bootstrap Decisions" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Advanced Cluster Settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="How to use" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bootstrap Decisions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Advanced Cluster Settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -777,7 +777,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H71"/>
+  <dimension ref="A1:H76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2494,27 +2494,27 @@
     <row r="60">
       <c r="A60" s="8" t="inlineStr">
         <is>
-          <t>11f3</t>
+          <t>11f2b</t>
         </is>
       </c>
       <c r="B60" s="9" t="inlineStr">
         <is>
-          <t>appgw_tls_key_vault_secret_id</t>
+          <t>appgw_tls_mode</t>
         </is>
       </c>
       <c r="C60" s="9" t="inlineStr">
         <is>
-          <t>Optional. Key Vault secret ID of the TLS certificate for the Application Gateway HTTPS:443 listener (also adds an HTTP→HTTPS redirect). The gateway reads it with the AKS identity. Leave blank to serve HTTP:80 only; you can add TLS later.</t>
+          <t>How the Application Gateway terminates TLS at the internet edge. 'keyvault' = you bring your own certificate (RECOMMENDED for production; a customer-owned certificate must be used in production per Microsoft guidance and PCI-DSS). 'self_signed' = the accelerator generates a certificate inside Key Vault (the private key never leaves Key Vault and is never stored in the repo or state) — DEV/TEST only and blocked for production environments. 'disabled' = HTTP:80 only, no TLS. TLS 1.2 is always the minimum whenever TLS is on. Setting appgw_tls_key_vault_secret_id (11f3) automatically forces 'keyvault'.</t>
         </is>
       </c>
       <c r="D60" s="9" t="inlineStr">
         <is>
-          <t>Key Vault secret URI, or blank</t>
+          <t>keyvault | self_signed | disabled</t>
         </is>
       </c>
       <c r="E60" s="9" t="inlineStr">
         <is>
-          <t>(blank = HTTP:80 only)</t>
+          <t>self_signed  (keyvault required for production)</t>
         </is>
       </c>
       <c r="F60" s="10" t="inlineStr"/>
@@ -2528,27 +2528,27 @@
     <row r="61">
       <c r="A61" s="8" t="inlineStr">
         <is>
-          <t>11p</t>
+          <t>11f3</t>
         </is>
       </c>
       <c r="B61" s="9" t="inlineStr">
         <is>
-          <t>enable_agc</t>
+          <t>appgw_tls_key_vault_secret_id</t>
         </is>
       </c>
       <c r="C61" s="9" t="inlineStr">
         <is>
-          <t>Application Gateway for Containers (ALB). Provisions a delegated subnet (5h) + NSG; the in-cluster ALB Controller manages the gateway. Coexists with enable_app_gateway.</t>
+          <t>Customer-provided TLS certificate for the HTTPS:443 listener — used when appgw_tls_mode (11f2b) is 'keyvault'. Provide the Key Vault secret ID (URL) only; the certificate and its private key are never stored in the repo or Terraform state, and the gateway reads the cert with the AKS identity over the private endpoint. Setting this automatically selects 'keyvault' mode. Leave blank for self_signed / disabled.</t>
         </is>
       </c>
       <c r="D61" s="9" t="inlineStr">
         <is>
-          <t>true | false</t>
+          <t>Key Vault secret URI, or blank</t>
         </is>
       </c>
       <c r="E61" s="9" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>(blank; required for production)</t>
         </is>
       </c>
       <c r="F61" s="10" t="inlineStr"/>
@@ -2562,17 +2562,17 @@
     <row r="62">
       <c r="A62" s="8" t="inlineStr">
         <is>
-          <t>11g</t>
+          <t>11f4</t>
         </is>
       </c>
       <c r="B62" s="9" t="inlineStr">
         <is>
-          <t>enable_keda</t>
+          <t>appgw_https_only</t>
         </is>
       </c>
       <c r="C62" s="9" t="inlineStr">
         <is>
-          <t>Auto-scales pods based on events (queue length, HTTP requests, etc.).</t>
+          <t>Serve HTTPS only and drop the HTTP:80 listener (no HTTP→HTTPS redirect). Only used when TLS is on (11f2b keyvault or self_signed). Default false keeps HTTP:80 redirecting to HTTPS:443.</t>
         </is>
       </c>
       <c r="D62" s="9" t="inlineStr">
@@ -2582,7 +2582,7 @@
       </c>
       <c r="E62" s="9" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
       <c r="F62" s="10" t="inlineStr"/>
@@ -2596,17 +2596,17 @@
     <row r="63">
       <c r="A63" s="8" t="inlineStr">
         <is>
-          <t>11h</t>
+          <t>11p</t>
         </is>
       </c>
       <c r="B63" s="9" t="inlineStr">
         <is>
-          <t>enable_vpa</t>
+          <t>enable_agc</t>
         </is>
       </c>
       <c r="C63" s="9" t="inlineStr">
         <is>
-          <t>Auto-adjusts CPU and memory requests for pods.</t>
+          <t>Application Gateway for Containers (ALB). Provisions a delegated subnet (5h) + NSG; the in-cluster ALB Controller manages the gateway. Coexists with enable_app_gateway.</t>
         </is>
       </c>
       <c r="D63" s="9" t="inlineStr">
@@ -2616,7 +2616,7 @@
       </c>
       <c r="E63" s="9" t="inlineStr">
         <is>
-          <t>false  (true for regulated / multi-region)</t>
+          <t>false</t>
         </is>
       </c>
       <c r="F63" s="10" t="inlineStr"/>
@@ -2630,17 +2630,17 @@
     <row r="64">
       <c r="A64" s="8" t="inlineStr">
         <is>
-          <t>11i</t>
+          <t>11g</t>
         </is>
       </c>
       <c r="B64" s="9" t="inlineStr">
         <is>
-          <t>enable_node_auto_provisioning</t>
+          <t>enable_keda</t>
         </is>
       </c>
       <c r="C64" s="9" t="inlineStr">
         <is>
-          <t>Cluster creates new node sizes on demand instead of using fixed pools.</t>
+          <t>Auto-scales pods based on events (queue length, HTTP requests, etc.).</t>
         </is>
       </c>
       <c r="D64" s="9" t="inlineStr">
@@ -2650,7 +2650,7 @@
       </c>
       <c r="E64" s="9" t="inlineStr">
         <is>
-          <t>false  (true for multi-region)</t>
+          <t>true</t>
         </is>
       </c>
       <c r="F64" s="10" t="inlineStr"/>
@@ -2664,17 +2664,17 @@
     <row r="65">
       <c r="A65" s="8" t="inlineStr">
         <is>
-          <t>11j</t>
+          <t>11h</t>
         </is>
       </c>
       <c r="B65" s="9" t="inlineStr">
         <is>
-          <t>enable_istio</t>
+          <t>enable_vpa</t>
         </is>
       </c>
       <c r="C65" s="9" t="inlineStr">
         <is>
-          <t>Service mesh with mTLS between pods. Needed for some compliance standards.</t>
+          <t>Auto-adjusts CPU and memory requests for pods.</t>
         </is>
       </c>
       <c r="D65" s="9" t="inlineStr">
@@ -2684,7 +2684,7 @@
       </c>
       <c r="E65" s="9" t="inlineStr">
         <is>
-          <t>false  (true for regulated)</t>
+          <t>false  (true for regulated / multi-region)</t>
         </is>
       </c>
       <c r="F65" s="10" t="inlineStr"/>
@@ -2698,17 +2698,17 @@
     <row r="66">
       <c r="A66" s="8" t="inlineStr">
         <is>
-          <t>11k</t>
+          <t>11i</t>
         </is>
       </c>
       <c r="B66" s="9" t="inlineStr">
         <is>
-          <t>enable_flux</t>
+          <t>enable_node_auto_provisioning</t>
         </is>
       </c>
       <c r="C66" s="9" t="inlineStr">
         <is>
-          <t>GitOps — the cluster pulls its configuration from a Git repo.</t>
+          <t>Cluster creates new node sizes on demand instead of using fixed pools.</t>
         </is>
       </c>
       <c r="D66" s="9" t="inlineStr">
@@ -2732,17 +2732,17 @@
     <row r="67">
       <c r="A67" s="8" t="inlineStr">
         <is>
-          <t>11l</t>
+          <t>11j</t>
         </is>
       </c>
       <c r="B67" s="9" t="inlineStr">
         <is>
-          <t>enable_dapr</t>
+          <t>enable_istio</t>
         </is>
       </c>
       <c r="C67" s="9" t="inlineStr">
         <is>
-          <t>Building blocks for microservices (pub/sub, state, secrets).</t>
+          <t>Service mesh with mTLS between pods. Needed for some compliance standards.</t>
         </is>
       </c>
       <c r="D67" s="9" t="inlineStr">
@@ -2752,7 +2752,7 @@
       </c>
       <c r="E67" s="9" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>false  (true for regulated)</t>
         </is>
       </c>
       <c r="F67" s="10" t="inlineStr"/>
@@ -2766,17 +2766,17 @@
     <row r="68">
       <c r="A68" s="8" t="inlineStr">
         <is>
-          <t>11m</t>
+          <t>11k</t>
         </is>
       </c>
       <c r="B68" s="9" t="inlineStr">
         <is>
-          <t>enable_fips</t>
+          <t>enable_flux</t>
         </is>
       </c>
       <c r="C68" s="9" t="inlineStr">
         <is>
-          <t>Use FIPS 140-2 compliant node OS (US Federal / PCI).</t>
+          <t>GitOps — the cluster pulls its configuration from a Git repo.</t>
         </is>
       </c>
       <c r="D68" s="9" t="inlineStr">
@@ -2786,7 +2786,7 @@
       </c>
       <c r="E68" s="9" t="inlineStr">
         <is>
-          <t>false  (true for regulated)</t>
+          <t>false  (true for multi-region)</t>
         </is>
       </c>
       <c r="F68" s="10" t="inlineStr"/>
@@ -2800,17 +2800,17 @@
     <row r="69">
       <c r="A69" s="8" t="inlineStr">
         <is>
-          <t>11n</t>
+          <t>11l</t>
         </is>
       </c>
       <c r="B69" s="9" t="inlineStr">
         <is>
-          <t>enable_backup</t>
+          <t>enable_dapr</t>
         </is>
       </c>
       <c r="C69" s="9" t="inlineStr">
         <is>
-          <t>Azure Backup for cluster resources and persistent volumes.</t>
+          <t>Building blocks for microservices (pub/sub, state, secrets).</t>
         </is>
       </c>
       <c r="D69" s="9" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="E69" s="9" t="inlineStr">
         <is>
-          <t>false  (true for regulated / multi-region)</t>
+          <t>false</t>
         </is>
       </c>
       <c r="F69" s="10" t="inlineStr"/>
@@ -2834,17 +2834,17 @@
     <row r="70">
       <c r="A70" s="8" t="inlineStr">
         <is>
-          <t>11o</t>
+          <t>11m</t>
         </is>
       </c>
       <c r="B70" s="9" t="inlineStr">
         <is>
-          <t>enable_cost_analysis</t>
+          <t>enable_fips</t>
         </is>
       </c>
       <c r="C70" s="9" t="inlineStr">
         <is>
-          <t>Cost breakdown per namespace in the Azure portal.</t>
+          <t>Use FIPS 140-2 compliant node OS (US Federal / PCI).</t>
         </is>
       </c>
       <c r="D70" s="9" t="inlineStr">
@@ -2868,27 +2868,27 @@
     <row r="71">
       <c r="A71" s="8" t="inlineStr">
         <is>
-          <t>11p</t>
+          <t>11n</t>
         </is>
       </c>
       <c r="B71" s="9" t="inlineStr">
         <is>
-          <t>auto_scaler_profile</t>
+          <t>enable_backup</t>
         </is>
       </c>
       <c r="C71" s="9" t="inlineStr">
         <is>
-          <t>Day-2 (optional): fine-tune the cluster autoscaler for cost vs performance. Keep AKS defaults unless Azure Advisor flags idle nodes. See docs.</t>
+          <t>Azure Backup for cluster resources and persistent volumes.</t>
         </is>
       </c>
       <c r="D71" s="9" t="inlineStr">
         <is>
-          <t>Keep AKS defaults | tune in tfvars</t>
+          <t>true | false</t>
         </is>
       </c>
       <c r="E71" s="9" t="inlineStr">
         <is>
-          <t>Keep AKS defaults</t>
+          <t>false  (true for regulated / multi-region)</t>
         </is>
       </c>
       <c r="F71" s="10" t="inlineStr"/>
@@ -2898,6 +2898,176 @@
         </is>
       </c>
       <c r="H71" s="10" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="8" t="inlineStr">
+        <is>
+          <t>11o</t>
+        </is>
+      </c>
+      <c r="B72" s="9" t="inlineStr">
+        <is>
+          <t>enable_cost_analysis</t>
+        </is>
+      </c>
+      <c r="C72" s="9" t="inlineStr">
+        <is>
+          <t>Cost breakdown per namespace in the Azure portal.</t>
+        </is>
+      </c>
+      <c r="D72" s="9" t="inlineStr">
+        <is>
+          <t>true | false</t>
+        </is>
+      </c>
+      <c r="E72" s="9" t="inlineStr">
+        <is>
+          <t>false  (true for regulated)</t>
+        </is>
+      </c>
+      <c r="F72" s="10" t="inlineStr"/>
+      <c r="G72" s="11" t="inlineStr">
+        <is>
+          <t>Microsoft Learn ↗</t>
+        </is>
+      </c>
+      <c r="H72" s="10" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="8" t="inlineStr">
+        <is>
+          <t>11q</t>
+        </is>
+      </c>
+      <c r="B73" s="9" t="inlineStr">
+        <is>
+          <t>enable_management_jumpbox</t>
+        </is>
+      </c>
+      <c r="C73" s="9" t="inlineStr">
+        <is>
+          <t>Opt-in Azure Bastion + hardened no-public-IP jumpbox VM for private-cluster access (standalone only; ALZ hubs provide Bastion/VPN).</t>
+        </is>
+      </c>
+      <c r="D73" s="9" t="inlineStr">
+        <is>
+          <t>true | false</t>
+        </is>
+      </c>
+      <c r="E73" s="9" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="F73" s="10" t="inlineStr"/>
+      <c r="G73" s="11" t="inlineStr">
+        <is>
+          <t>Microsoft Learn ↗</t>
+        </is>
+      </c>
+      <c r="H73" s="10" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="8" t="inlineStr">
+        <is>
+          <t>11r</t>
+        </is>
+      </c>
+      <c r="B74" s="9" t="inlineStr">
+        <is>
+          <t>jumpbox_vm_size</t>
+        </is>
+      </c>
+      <c r="C74" s="9" t="inlineStr">
+        <is>
+          <t>VM size for the management jumpbox (any valid Azure VM size). Applies only when enable_management_jumpbox = true.</t>
+        </is>
+      </c>
+      <c r="D74" s="9" t="inlineStr">
+        <is>
+          <t>Standard_B2s_v2 | Standard_D2s_v5 | any Azure VM size</t>
+        </is>
+      </c>
+      <c r="E74" s="9" t="inlineStr">
+        <is>
+          <t>Standard_B2s_v2</t>
+        </is>
+      </c>
+      <c r="F74" s="10" t="inlineStr"/>
+      <c r="G74" s="11" t="inlineStr">
+        <is>
+          <t>Microsoft Learn ↗</t>
+        </is>
+      </c>
+      <c r="H74" s="10" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="8" t="inlineStr">
+        <is>
+          <t>11s</t>
+        </is>
+      </c>
+      <c r="B75" s="9" t="inlineStr">
+        <is>
+          <t>bastion_sku</t>
+        </is>
+      </c>
+      <c r="C75" s="9" t="inlineStr">
+        <is>
+          <t>Azure Bastion SKU for jumpbox access. Standard enables native-client SSH/tunneling; Basic is browser-only. Applies only when enable_management_jumpbox = true.</t>
+        </is>
+      </c>
+      <c r="D75" s="9" t="inlineStr">
+        <is>
+          <t>Standard | Basic</t>
+        </is>
+      </c>
+      <c r="E75" s="9" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="F75" s="10" t="inlineStr"/>
+      <c r="G75" s="11" t="inlineStr">
+        <is>
+          <t>Microsoft Learn ↗</t>
+        </is>
+      </c>
+      <c r="H75" s="10" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="8" t="inlineStr">
+        <is>
+          <t>11p</t>
+        </is>
+      </c>
+      <c r="B76" s="9" t="inlineStr">
+        <is>
+          <t>auto_scaler_profile</t>
+        </is>
+      </c>
+      <c r="C76" s="9" t="inlineStr">
+        <is>
+          <t>Day-2 (optional): fine-tune the cluster autoscaler for cost vs performance. Keep AKS defaults unless Azure Advisor flags idle nodes. See docs.</t>
+        </is>
+      </c>
+      <c r="D76" s="9" t="inlineStr">
+        <is>
+          <t>Keep AKS defaults | tune in tfvars</t>
+        </is>
+      </c>
+      <c r="E76" s="9" t="inlineStr">
+        <is>
+          <t>Keep AKS defaults</t>
+        </is>
+      </c>
+      <c r="F76" s="10" t="inlineStr"/>
+      <c r="G76" s="11" t="inlineStr">
+        <is>
+          <t>Microsoft Learn ↗</t>
+        </is>
+      </c>
+      <c r="H76" s="10" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="13">
@@ -2915,7 +3085,7 @@
     <mergeCell ref="B5:H5"/>
     <mergeCell ref="B31:H31"/>
   </mergeCells>
-  <dataValidations count="28">
+  <dataValidations count="31">
     <dataValidation sqref="F6" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"single_region_baseline,multi_region_baseline,single_region_regulated,multi_region_regulated"</formula1>
     </dataValidation>
@@ -2970,8 +3140,8 @@
     <dataValidation sqref="F59" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"istio,manual"</formula1>
     </dataValidation>
-    <dataValidation sqref="F61" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"true,false"</formula1>
+    <dataValidation sqref="F60" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"keyvault,self_signed,disabled"</formula1>
     </dataValidation>
     <dataValidation sqref="F62" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"true,false"</formula1>
@@ -2998,6 +3168,15 @@
       <formula1>"true,false"</formula1>
     </dataValidation>
     <dataValidation sqref="F70" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"true,false"</formula1>
+    </dataValidation>
+    <dataValidation sqref="F71" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"true,false"</formula1>
+    </dataValidation>
+    <dataValidation sqref="F72" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"true,false"</formula1>
+    </dataValidation>
+    <dataValidation sqref="F73" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"true,false"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3058,6 +3237,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G69" r:id="rId54"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G70" r:id="rId55"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G71" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G72" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G73" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G74" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G75" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G76" r:id="rId61"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
